--- a/apps/intake-demo/public/data/UAE_Startups_Funders_200_AR.xlsx
+++ b/apps/intake-demo/public/data/UAE_Startups_Funders_200_AR.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="1" r:id="R6f64226fa6a3469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الشركات الناشئة" sheetId="2" r:id="R0bb474002f424570"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جهات التمويل والدعم" sheetId="3" r:id="R3c749b00c9b148a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التعريفات والمنهجية" sheetId="4" r:id="R5876010644974219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="1" r:id="R8856e410eb8548df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الشركات الناشئة" sheetId="2" r:id="R282c998362b44b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جهات التمويل والدعم" sheetId="3" r:id="R4352b8e829624a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التعريفات والمنهجية" sheetId="4" r:id="R6c5ef0795ce248df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -190,7 +190,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -200,7 +200,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -210,7 +210,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -220,7 +220,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -230,7 +230,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -240,7 +240,7 @@
         <x:color rgb="FF8A5D12"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4DF"/>
         </x:patternFill>
       </x:fill>
@@ -1067,9 +1067,8 @@
       <x:c r="I6" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="e">
-        <x:f>HYPERLINK("https://alaan.com","alaan.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://alaan.com, friendlyName=alaan.com</x:v>
+      <x:c r="J6" s="14" t="str">
+        <x:v>https://alaan.com</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1096,30 +1095,26 @@
       <x:c r="S6" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T6" s="14" t="e">
-        <x:f>HYPERLINK("https://alainfinance.ae/wp-content/uploads/2021/01/CSC-AAF.pdf","alainfinance.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://alainfinance.ae/wp-content/uploads/2021/01/CSC-AAF.pdf, friendlyName=alainfinance.ae</x:v>
+      <x:c r="T6" s="14" t="str">
+        <x:v>https://www.alaan.com/press-releases/alaan-raises-48-million
+https://www.sme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U6" s="14" t="str">
         <x:v>https://www.alaan.com/press-releases/alaan-raises-48-million
 https://www.alaan.com/blog/introduction-to-alaan
 https://www.wamda.com/index.php/en/2025/08/alaan-raises-48-million-series-transform-spend-management-mena</x:v>
       </x:c>
-      <x:c r="V6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.alaan.com/press-releases/alaan-raises-48-million","alaan.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.alaan.com/press-releases/alaan-raises-48-million, friendlyName=alaan.com</x:v>
-      </x:c>
-      <x:c r="W6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.alaan.com/contact-us","alaan.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.alaan.com/contact-us, friendlyName=alaan.com</x:v>
-      </x:c>
-      <x:c r="X6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.alaan.com/contact-us","alaan.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.alaan.com/contact-us, friendlyName=alaan.com</x:v>
-      </x:c>
-      <x:c r="Y6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.alaan.com/contact-us","alaan.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.alaan.com/contact-us, friendlyName=alaan.com</x:v>
+      <x:c r="V6" s="14" t="str">
+        <x:v>https://www.alaan.com/press-releases/alaan-raises-48-million</x:v>
+      </x:c>
+      <x:c r="W6" s="14" t="str">
+        <x:v>https://www.alaan.com/contact-us</x:v>
+      </x:c>
+      <x:c r="X6" s="14" t="str">
+        <x:v>https://www.alaan.com/contact-us</x:v>
+      </x:c>
+      <x:c r="Y6" s="14" t="str">
+        <x:v>https://www.alaan.com/contact-us</x:v>
       </x:c>
       <x:c r="Z6" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1156,9 +1151,8 @@
       <x:c r="I7" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="e">
-        <x:f>HYPERLINK("https://appro.ae","appro.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://appro.ae, friendlyName=appro.ae</x:v>
+      <x:c r="J7" s="14" t="str">
+        <x:v>https://appro.ae</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1185,9 +1179,8 @@
       <x:c r="S7" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T7" s="14" t="e">
-        <x:f>HYPERLINK("https://appro.ae/","appro.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://appro.ae/, friendlyName=appro.ae</x:v>
+      <x:c r="T7" s="14" t="str">
+        <x:v>https://appro.ae/</x:v>
       </x:c>
       <x:c r="U7" s="14" t="str">
         <x:v>https://uaefintech.co/company/appro/
@@ -1197,17 +1190,14 @@
       <x:c r="V7" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W7" s="14" t="e">
-        <x:f>HYPERLINK("https://appro.ae/contact","appro.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://appro.ae/contact, friendlyName=appro.ae</x:v>
-      </x:c>
-      <x:c r="X7" s="14" t="e">
-        <x:f>HYPERLINK("https://appro.ae/contact","appro.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://appro.ae/contact, friendlyName=appro.ae</x:v>
-      </x:c>
-      <x:c r="Y7" s="14" t="e">
-        <x:f>HYPERLINK("https://appro.ae/contact","appro.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://appro.ae/contact, friendlyName=appro.ae</x:v>
+      <x:c r="W7" s="14" t="str">
+        <x:v>https://appro.ae/contact</x:v>
+      </x:c>
+      <x:c r="X7" s="14" t="str">
+        <x:v>https://appro.ae/contact</x:v>
+      </x:c>
+      <x:c r="Y7" s="14" t="str">
+        <x:v>https://appro.ae/contact</x:v>
       </x:c>
       <x:c r="Z7" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1244,9 +1234,8 @@
       <x:c r="I8" s="6" t="str">
         <x:v>إعلام؛ اطلب تحويلك للفريق المختص</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="e">
-        <x:f>HYPERLINK("https://biosapien.com","biosapien.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://biosapien.com, friendlyName=biosapien.com</x:v>
+      <x:c r="J8" s="14" t="str">
+        <x:v>https://biosapien.com</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1273,29 +1262,25 @@
       <x:c r="S8" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T8" s="14" t="e">
-        <x:f>HYPERLINK("https://dharab.com/dbentry/biosapien/","dharab.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dharab.com/dbentry/biosapien/, friendlyName=dharab.com</x:v>
+      <x:c r="T8" s="14" t="str">
+        <x:v>https://dharab.com/dbentry/biosapien/</x:v>
       </x:c>
       <x:c r="U8" s="14" t="str">
         <x:v>https://fintechnews.media/2025/07/uaes-biosapien-extends-pre-series-a-funding-round-to-over-8mln-with-new-investment-from-globivest/
 https://pmes.app.swapcard.com/event/precisionmed-exhibition-and-summit-2024/exhibitor/RXhoaWJpdG9yXzE2OTY3MDA%3D
 https://www.biosapien.com/news/uae-biotech-startup-biosapien-raises-7-million-pre-series-a-for-cancer-treatment-platform</x:v>
       </x:c>
-      <x:c r="V8" s="14" t="e">
-        <x:f>HYPERLINK("https://www.biosapien.com/news/uae-biotech-startup-biosapien-raises-7-million-pre-series-a-for-cancer-treatment-platform","biosapien.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.biosapien.com/news/uae-biotech-startup-biosapien-raises-7-million-pre-series-a-for-cancer-treatment-platform, friendlyName=biosapien.com</x:v>
-      </x:c>
-      <x:c r="W8" s="14" t="e">
-        <x:f>HYPERLINK("https://www.biosapien.com/terms-and-conditions","biosapien.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.biosapien.com/terms-and-conditions, friendlyName=biosapien.com</x:v>
+      <x:c r="V8" s="14" t="str">
+        <x:v>https://www.biosapien.com/news/uae-biotech-startup-biosapien-raises-7-million-pre-series-a-for-cancer-treatment-platform</x:v>
+      </x:c>
+      <x:c r="W8" s="14" t="str">
+        <x:v>https://www.biosapien.com/terms-and-conditions</x:v>
       </x:c>
       <x:c r="X8" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y8" s="14" t="e">
-        <x:f>HYPERLINK("https://www.biosapien.com/","biosapien.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.biosapien.com/, friendlyName=biosapien.com</x:v>
+      <x:c r="Y8" s="14" t="str">
+        <x:v>https://www.biosapien.com/</x:v>
       </x:c>
       <x:c r="Z8" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1332,9 +1317,8 @@
       <x:c r="I9" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="e">
-        <x:f>HYPERLINK("https://disrupt-x.io","disrupt-x.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://disrupt-x.io, friendlyName=disrupt-x.io</x:v>
+      <x:c r="J9" s="14" t="str">
+        <x:v>https://disrupt-x.io</x:v>
       </x:c>
       <x:c r="K9" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1361,9 +1345,8 @@
       <x:c r="S9" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T9" s="14" t="e">
-        <x:f>HYPERLINK("https://www.caplight.com/company/disrupt-x","caplight.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.caplight.com/company/disrupt-x, friendlyName=caplight.com</x:v>
+      <x:c r="T9" s="14" t="str">
+        <x:v>https://www.caplight.com/company/disrupt-x</x:v>
       </x:c>
       <x:c r="U9" s="14" t="str">
         <x:v>https://www.linkedin.com/posts/disruptxio_manholemonitoring-smartinfrastructure-activity-7215952843206250497-58fJ
@@ -1373,17 +1356,14 @@
       <x:c r="V9" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W9" s="14" t="e">
-        <x:f>HYPERLINK("https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf","disrupt-x.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf, friendlyName=disrupt-x.io</x:v>
-      </x:c>
-      <x:c r="X9" s="14" t="e">
-        <x:f>HYPERLINK("https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf","disrupt-x.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf, friendlyName=disrupt-x.io</x:v>
-      </x:c>
-      <x:c r="Y9" s="14" t="e">
-        <x:f>HYPERLINK("https://disrupt-x.io/contact-us/","disrupt-x.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://disrupt-x.io/contact-us/, friendlyName=disrupt-x.io</x:v>
+      <x:c r="W9" s="14" t="str">
+        <x:v>https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf</x:v>
+      </x:c>
+      <x:c r="X9" s="14" t="str">
+        <x:v>https://disrupt-x.io/pdf/DX_CompanyDeckProfile_2025.pdf</x:v>
+      </x:c>
+      <x:c r="Y9" s="14" t="str">
+        <x:v>https://disrupt-x.io/contact-us/</x:v>
       </x:c>
       <x:c r="Z9" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1420,9 +1400,8 @@
       <x:c r="I10" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="e">
-        <x:f>HYPERLINK("https://eanan.ae","eanan.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eanan.ae, friendlyName=eanan.ae</x:v>
+      <x:c r="J10" s="14" t="str">
+        <x:v>https://eanan.ae</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1449,9 +1428,8 @@
       <x:c r="S10" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T10" s="14" t="e">
-        <x:f>HYPERLINK("https://ai.paytabs.com/wp-content/uploads/2017/05/Future-100-1.pdf","ai.paytabs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ai.paytabs.com/wp-content/uploads/2017/05/Future-100-1.pdf, friendlyName=ai.paytabs.com</x:v>
+      <x:c r="T10" s="14" t="str">
+        <x:v>https://ai.paytabs.com/wp-content/uploads/2017/05/Future-100-1.pdf</x:v>
       </x:c>
       <x:c r="U10" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -1459,17 +1437,14 @@
       <x:c r="V10" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W10" s="14" t="e">
-        <x:f>HYPERLINK("https://eanan.ae/contact/","eanan.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eanan.ae/contact/, friendlyName=eanan.ae</x:v>
-      </x:c>
-      <x:c r="X10" s="14" t="e">
-        <x:f>HYPERLINK("https://eanan.ae/contact/","eanan.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eanan.ae/contact/, friendlyName=eanan.ae</x:v>
-      </x:c>
-      <x:c r="Y10" s="14" t="e">
-        <x:f>HYPERLINK("https://eanan.ae/contact/","eanan.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eanan.ae/contact/, friendlyName=eanan.ae</x:v>
+      <x:c r="W10" s="14" t="str">
+        <x:v>https://eanan.ae/contact/</x:v>
+      </x:c>
+      <x:c r="X10" s="14" t="str">
+        <x:v>https://eanan.ae/contact/</x:v>
+      </x:c>
+      <x:c r="Y10" s="14" t="str">
+        <x:v>https://eanan.ae/contact/</x:v>
       </x:c>
       <x:c r="Z10" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1506,9 +1481,8 @@
       <x:c r="I11" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="e">
-        <x:f>HYPERLINK("https://egrobots.com","egrobots.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://egrobots.com, friendlyName=egrobots.com</x:v>
+      <x:c r="J11" s="14" t="str">
+        <x:v>https://egrobots.com</x:v>
       </x:c>
       <x:c r="K11" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1537,9 +1511,8 @@
       <x:c r="S11" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T11" s="14" t="e">
-        <x:f>HYPERLINK("https://robottoday.com/suppliers-discovery/egrobots","robottoday.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://robottoday.com/suppliers-discovery/egrobots, friendlyName=robottoday.com</x:v>
+      <x:c r="T11" s="14" t="str">
+        <x:v>https://robottoday.com/suppliers-discovery/egrobots</x:v>
       </x:c>
       <x:c r="U11" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -1547,16 +1520,14 @@
       <x:c r="V11" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W11" s="14" t="e">
-        <x:f>HYPERLINK("https://egrobots.com/en","egrobots.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://egrobots.com/en, friendlyName=egrobots.com</x:v>
+      <x:c r="W11" s="14" t="str">
+        <x:v>https://egrobots.com/en</x:v>
       </x:c>
       <x:c r="X11" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y11" s="14" t="e">
-        <x:f>HYPERLINK("https://egrobots.com/en","egrobots.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://egrobots.com/en, friendlyName=egrobots.com</x:v>
+      <x:c r="Y11" s="14" t="str">
+        <x:v>https://egrobots.com/en</x:v>
       </x:c>
       <x:c r="Z11" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1593,9 +1564,8 @@
       <x:c r="I12" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="e">
-        <x:f>HYPERLINK("https://ejaby.io","ejaby.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ejaby.io, friendlyName=ejaby.io</x:v>
+      <x:c r="J12" s="14" t="str">
+        <x:v>https://ejaby.io</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1622,9 +1592,8 @@
       <x:c r="S12" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T12" s="14" t="e">
-        <x:f>HYPERLINK("https://www.linkedin.com/company/tekeya","linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.linkedin.com/company/tekeya, friendlyName=linkedin.com</x:v>
+      <x:c r="T12" s="14" t="str">
+        <x:v>https://www.linkedin.com/company/tekeya</x:v>
       </x:c>
       <x:c r="U12" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/tekeya
@@ -1634,17 +1603,14 @@
       <x:c r="V12" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W12" s="14" t="e">
-        <x:f>HYPERLINK("https://ejaby.io/terms","ejaby.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ejaby.io/terms, friendlyName=ejaby.io</x:v>
-      </x:c>
-      <x:c r="X12" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=io.tekeya","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=io.tekeya, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="Y12" s="14" t="e">
-        <x:f>HYPERLINK("https://ejaby.io/terms","ejaby.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ejaby.io/terms, friendlyName=ejaby.io</x:v>
+      <x:c r="W12" s="14" t="str">
+        <x:v>https://ejaby.io/terms</x:v>
+      </x:c>
+      <x:c r="X12" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=io.tekeya</x:v>
+      </x:c>
+      <x:c r="Y12" s="14" t="str">
+        <x:v>https://ejaby.io/terms</x:v>
       </x:c>
       <x:c r="Z12" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1681,9 +1647,8 @@
       <x:c r="I13" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="e">
-        <x:f>HYPERLINK("https://emotech.ai","emotech.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emotech.ai, friendlyName=emotech.ai</x:v>
+      <x:c r="J13" s="14" t="str">
+        <x:v>https://emotech.ai</x:v>
       </x:c>
       <x:c r="K13" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1710,9 +1675,8 @@
       <x:c r="S13" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T13" s="14" t="e">
-        <x:f>HYPERLINK("https://www.uaesme.gov.ae/en/future-100-list","uaesme.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.uaesme.gov.ae/en/future-100-list, friendlyName=uaesme.gov.ae</x:v>
+      <x:c r="T13" s="14" t="str">
+        <x:v>https://www.uaesme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U13" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -1720,16 +1684,14 @@
       <x:c r="V13" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W13" s="14" t="e">
-        <x:f>HYPERLINK("https://emotech.ai/contact","emotech.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emotech.ai/contact, friendlyName=emotech.ai</x:v>
+      <x:c r="W13" s="14" t="str">
+        <x:v>https://emotech.ai/contact</x:v>
       </x:c>
       <x:c r="X13" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y13" s="14" t="e">
-        <x:f>HYPERLINK("https://emotech.ai/contact","emotech.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emotech.ai/contact, friendlyName=emotech.ai</x:v>
+      <x:c r="Y13" s="14" t="str">
+        <x:v>https://emotech.ai/contact</x:v>
       </x:c>
       <x:c r="Z13" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1766,9 +1728,8 @@
       <x:c r="I14" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="e">
-        <x:f>HYPERLINK("https://empe.io","empe.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://empe.io, friendlyName=empe.io</x:v>
+      <x:c r="J14" s="14" t="str">
+        <x:v>https://empe.io</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1795,9 +1756,8 @@
       <x:c r="S14" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T14" s="14" t="e">
-        <x:f>HYPERLINK("https://future100.ae/report-2024","future100.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://future100.ae/report-2024, friendlyName=future100.ae</x:v>
+      <x:c r="T14" s="14" t="str">
+        <x:v>https://future100.ae/report-2024</x:v>
       </x:c>
       <x:c r="U14" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -1805,16 +1765,14 @@
       <x:c r="V14" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W14" s="14" t="e">
-        <x:f>HYPERLINK("https://exhibitor-manual-004.s3.ap-south-1.amazonaws.com/Production/exb_doc/2029/44369/Press_Release_Digita_Trust_API_Empeiria.pdf","exhibitor-manual-004.s3.ap-south-1.amazonaws.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://exhibitor-manual-004.s3.ap-south-1.amazonaws.com/Production/exb_doc/2029/44369/Press_Release_Digita_Trust_API_Empeiria.pdf, friendlyName=exhibitor-manual-004.s3.ap-south-1.amazonaws.com</x:v>
+      <x:c r="W14" s="14" t="str">
+        <x:v>https://exhibitor-manual-004.s3.ap-south-1.amazonaws.com/Production/exb_doc/2029/44369/Press_Release_Digita_Trust_API_Empeiria.pdf</x:v>
       </x:c>
       <x:c r="X14" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y14" s="14" t="e">
-        <x:f>HYPERLINK("https://empe.io/","empe.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://empe.io/, friendlyName=empe.io</x:v>
+      <x:c r="Y14" s="14" t="str">
+        <x:v>https://empe.io/</x:v>
       </x:c>
       <x:c r="Z14" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -1851,9 +1809,8 @@
       <x:c r="I15" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="e">
-        <x:f>HYPERLINK("https://ennoventure.com","ennoventure.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ennoventure.com, friendlyName=ennoventure.com</x:v>
+      <x:c r="J15" s="14" t="str">
+        <x:v>https://ennoventure.com</x:v>
       </x:c>
       <x:c r="K15" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1882,9 +1839,8 @@
       <x:c r="S15" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T15" s="14" t="e">
-        <x:f>HYPERLINK("https://www.padmakumarnair.com/","padmakumarnair.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.padmakumarnair.com/, friendlyName=padmakumarnair.com</x:v>
+      <x:c r="T15" s="14" t="str">
+        <x:v>https://www.padmakumarnair.com/</x:v>
       </x:c>
       <x:c r="U15" s="14" t="str">
         <x:v>https://www.padmakumarnair.com/
@@ -1894,16 +1850,14 @@
       <x:c r="V15" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W15" s="14" t="e">
-        <x:f>HYPERLINK("https://www.padmakumarnair.com/","padmakumarnair.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.padmakumarnair.com/, friendlyName=padmakumarnair.com</x:v>
+      <x:c r="W15" s="14" t="str">
+        <x:v>https://www.padmakumarnair.com/</x:v>
       </x:c>
       <x:c r="X15" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y15" s="14" t="e">
-        <x:f>HYPERLINK("https://ennoventure.com/contact","ennoventure.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ennoventure.com/contact, friendlyName=ennoventure.com</x:v>
+      <x:c r="Y15" s="14" t="str">
+        <x:v>https://ennoventure.com/contact</x:v>
       </x:c>
       <x:c r="Z15" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -1940,9 +1894,8 @@
       <x:c r="I16" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J16" s="14" t="e">
-        <x:f>HYPERLINK("https://enrichly.world","enrichly.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://enrichly.world, friendlyName=enrichly.world</x:v>
+      <x:c r="J16" s="14" t="str">
+        <x:v>https://enrichly.world</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -1971,9 +1924,8 @@
       <x:c r="S16" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T16" s="14" t="e">
-        <x:f>HYPERLINK("https://future100.ae/report-2024","future100.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://future100.ae/report-2024, friendlyName=future100.ae</x:v>
+      <x:c r="T16" s="14" t="str">
+        <x:v>https://future100.ae/report-2024</x:v>
       </x:c>
       <x:c r="U16" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -1981,16 +1933,14 @@
       <x:c r="V16" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W16" s="14" t="e">
-        <x:f>HYPERLINK("https://www.enrichly.world/contact-4","enrichly.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.enrichly.world/contact-4, friendlyName=enrichly.world</x:v>
+      <x:c r="W16" s="14" t="str">
+        <x:v>https://www.enrichly.world/contact-4</x:v>
       </x:c>
       <x:c r="X16" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y16" s="14" t="e">
-        <x:f>HYPERLINK("https://www.enrichly.world/contact-4","enrichly.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.enrichly.world/contact-4, friendlyName=enrichly.world</x:v>
+      <x:c r="Y16" s="14" t="str">
+        <x:v>https://www.enrichly.world/contact-4</x:v>
       </x:c>
       <x:c r="Z16" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2027,9 +1977,8 @@
       <x:c r="I17" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="e">
-        <x:f>HYPERLINK("https://remotepass.com","remotepass.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://remotepass.com, friendlyName=remotepass.com</x:v>
+      <x:c r="J17" s="14" t="str">
+        <x:v>https://remotepass.com</x:v>
       </x:c>
       <x:c r="K17" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2058,29 +2007,25 @@
       <x:c r="S17" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T17" s="14" t="e">
-        <x:f>HYPERLINK("https://newsroom.remotepass.com/about/","newsroom.remotepass.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://newsroom.remotepass.com/about/, friendlyName=newsroom.remotepass.com</x:v>
+      <x:c r="T17" s="14" t="str">
+        <x:v>https://newsroom.remotepass.com/about/</x:v>
       </x:c>
       <x:c r="U17" s="14" t="str">
         <x:v>https://newsroom.remotepass.com/238166-remotepass-simplifies-hr-and-payroll-for-uae-companies-with-new-direct-employee-feature/
 https://newsroom.remotepass.com/about/
 https://www.remotepass.com/about-us</x:v>
       </x:c>
-      <x:c r="V17" s="14" t="e">
-        <x:f>HYPERLINK("https://newsroom.remotepass.com/about/","newsroom.remotepass.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://newsroom.remotepass.com/about/, friendlyName=newsroom.remotepass.com</x:v>
-      </x:c>
-      <x:c r="W17" s="14" t="e">
-        <x:f>HYPERLINK("https://app.remotepass.com/","app.remotepass.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://app.remotepass.com/, friendlyName=app.remotepass.com</x:v>
+      <x:c r="V17" s="14" t="str">
+        <x:v>https://newsroom.remotepass.com/about/</x:v>
+      </x:c>
+      <x:c r="W17" s="14" t="str">
+        <x:v>https://app.remotepass.com/</x:v>
       </x:c>
       <x:c r="X17" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y17" s="14" t="e">
-        <x:f>HYPERLINK("https://newsroom.remotepass.com/contact/","newsroom.remotepass.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://newsroom.remotepass.com/contact/, friendlyName=newsroom.remotepass.com</x:v>
+      <x:c r="Y17" s="14" t="str">
+        <x:v>https://newsroom.remotepass.com/contact/</x:v>
       </x:c>
       <x:c r="Z17" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2117,9 +2062,8 @@
       <x:c r="I18" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J18" s="14" t="e">
-        <x:f>HYPERLINK("https://revibe.ae","revibe.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://revibe.ae, friendlyName=revibe.ae</x:v>
+      <x:c r="J18" s="14" t="str">
+        <x:v>https://revibe.ae</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2146,28 +2090,24 @@
       <x:c r="S18" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T18" s="14" t="e">
-        <x:f>HYPERLINK("https://revibemd.com/wp-content/uploads/2022/09/RevibeMD-Mens-Health-Manual-09-19-2022.pdf","revibemd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://revibemd.com/wp-content/uploads/2022/09/RevibeMD-Mens-Health-Manual-09-19-2022.pdf, friendlyName=revibemd.com</x:v>
+      <x:c r="T18" s="14" t="str">
+        <x:v>https://www.revibe.ae/pages/contact-us
+https://www.sme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U18" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/en/2024/12/revibe-secures-7-million-series-a-expand-emerging-markets","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/en/2024/12/revibe-secures-7-million-series-a-expand-emerging-markets, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.revibe.ae/pages/contact-us","revibe.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.revibe.ae/pages/contact-us, friendlyName=revibe.ae</x:v>
-      </x:c>
-      <x:c r="X18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.revibe.ae/pages/contact-us","revibe.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.revibe.ae/pages/contact-us, friendlyName=revibe.ae</x:v>
-      </x:c>
-      <x:c r="Y18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.revibe.ae/pages/contact-us","revibe.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.revibe.ae/pages/contact-us, friendlyName=revibe.ae</x:v>
+      <x:c r="V18" s="14" t="str">
+        <x:v>https://www.wamda.com/en/2024/12/revibe-secures-7-million-series-a-expand-emerging-markets</x:v>
+      </x:c>
+      <x:c r="W18" s="14" t="str">
+        <x:v>https://www.revibe.ae/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="X18" s="14" t="str">
+        <x:v>https://www.revibe.ae/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="Y18" s="14" t="str">
+        <x:v>https://www.revibe.ae/pages/contact-us</x:v>
       </x:c>
       <x:c r="Z18" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2204,9 +2144,8 @@
       <x:c r="I19" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J19" s="14" t="e">
-        <x:f>HYPERLINK("https://sav.money","sav.money")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sav.money, friendlyName=sav.money</x:v>
+      <x:c r="J19" s="14" t="str">
+        <x:v>https://sav.money</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2235,30 +2174,25 @@
       <x:c r="S19" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T19" s="14" t="e">
-        <x:f>HYPERLINK("https://sav.money/contact-us","sav.money")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sav.money/contact-us, friendlyName=sav.money</x:v>
+      <x:c r="T19" s="14" t="str">
+        <x:v>https://sav.money/contact-us</x:v>
       </x:c>
       <x:c r="U19" s="14" t="str">
         <x:v>https://www.wamda.com/index.php/en/2026/09/phoenix-venture-partners-leads-3-5-million-round-uae-fintech-sav
 https://www.wamda.com/en/2023/03/uae-sav-raises-75000-pre-seed-round
 https://en.incarabia.com/uae-fintech-sav-raises-us35-million-to-grow-its-product-offering-and-regional-footprint-890085.html</x:v>
       </x:c>
-      <x:c r="V19" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/index.php/en/2026/09/phoenix-venture-partners-leads-3-5-million-round-uae-fintech-sav","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/index.php/en/2026/09/phoenix-venture-partners-leads-3-5-million-round-uae-fintech-sav, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W19" s="14" t="e">
-        <x:f>HYPERLINK("https://sav.money/contact-us","sav.money")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sav.money/contact-us, friendlyName=sav.money</x:v>
-      </x:c>
-      <x:c r="X19" s="14" t="e">
-        <x:f>HYPERLINK("https://sav.money/contact-us","sav.money")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sav.money/contact-us, friendlyName=sav.money</x:v>
-      </x:c>
-      <x:c r="Y19" s="14" t="e">
-        <x:f>HYPERLINK("https://sav.money/contact-us","sav.money")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sav.money/contact-us, friendlyName=sav.money</x:v>
+      <x:c r="V19" s="14" t="str">
+        <x:v>https://www.wamda.com/index.php/en/2026/09/phoenix-venture-partners-leads-3-5-million-round-uae-fintech-sav</x:v>
+      </x:c>
+      <x:c r="W19" s="14" t="str">
+        <x:v>https://sav.money/contact-us</x:v>
+      </x:c>
+      <x:c r="X19" s="14" t="str">
+        <x:v>https://sav.money/contact-us</x:v>
+      </x:c>
+      <x:c r="Y19" s="14" t="str">
+        <x:v>https://sav.money/contact-us</x:v>
       </x:c>
       <x:c r="Z19" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2295,9 +2229,8 @@
       <x:c r="I20" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J20" s="14" t="e">
-        <x:f>HYPERLINK("https://seramic.eco","seramic.eco")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://seramic.eco, friendlyName=seramic.eco</x:v>
+      <x:c r="J20" s="14" t="str">
+        <x:v>https://seramic.eco</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2324,9 +2257,8 @@
       <x:c r="S20" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T20" s="14" t="e">
-        <x:f>HYPERLINK("https://seramic.eco/","seramic.eco")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://seramic.eco/, friendlyName=seramic.eco</x:v>
+      <x:c r="T20" s="14" t="str">
+        <x:v>https://seramic.eco/</x:v>
       </x:c>
       <x:c r="U20" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -2334,17 +2266,14 @@
       <x:c r="V20" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W20" s="14" t="e">
-        <x:f>HYPERLINK("https://seramic.eco/contact/","seramic.eco")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://seramic.eco/contact/, friendlyName=seramic.eco</x:v>
-      </x:c>
-      <x:c r="X20" s="14" t="e">
-        <x:f>HYPERLINK("https://make.works/companies/seramic-materials-limited_uae","make.works")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://make.works/companies/seramic-materials-limited_uae, friendlyName=make.works</x:v>
-      </x:c>
-      <x:c r="Y20" s="14" t="e">
-        <x:f>HYPERLINK("https://seramic.eco/contact/","seramic.eco")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://seramic.eco/contact/, friendlyName=seramic.eco</x:v>
+      <x:c r="W20" s="14" t="str">
+        <x:v>https://seramic.eco/contact/</x:v>
+      </x:c>
+      <x:c r="X20" s="14" t="str">
+        <x:v>https://make.works/companies/seramic-materials-limited_uae</x:v>
+      </x:c>
+      <x:c r="Y20" s="14" t="str">
+        <x:v>https://seramic.eco/contact/</x:v>
       </x:c>
       <x:c r="Z20" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2381,9 +2310,8 @@
       <x:c r="I21" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J21" s="14" t="e">
-        <x:f>HYPERLINK("https://silainsights.com","silainsights.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://silainsights.com, friendlyName=silainsights.com</x:v>
+      <x:c r="J21" s="14" t="str">
+        <x:v>https://silainsights.com</x:v>
       </x:c>
       <x:c r="K21" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2410,9 +2338,8 @@
       <x:c r="S21" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T21" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silainsights.com/about","silainsights.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silainsights.com/about, friendlyName=silainsights.com</x:v>
+      <x:c r="T21" s="14" t="str">
+        <x:v>https://www.silainsights.com/about</x:v>
       </x:c>
       <x:c r="U21" s="14" t="str">
         <x:v>https://www.silainsights.com/about
@@ -2422,16 +2349,14 @@
       <x:c r="V21" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W21" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silainsights.com/contact-sila/","silainsights.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silainsights.com/contact-sila/, friendlyName=silainsights.com</x:v>
+      <x:c r="W21" s="14" t="str">
+        <x:v>https://www.silainsights.com/contact-sila/</x:v>
       </x:c>
       <x:c r="X21" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y21" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silainsights.com/contact-sila/","silainsights.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silainsights.com/contact-sila/, friendlyName=silainsights.com</x:v>
+      <x:c r="Y21" s="14" t="str">
+        <x:v>https://www.silainsights.com/contact-sila/</x:v>
       </x:c>
       <x:c r="Z21" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2468,9 +2393,8 @@
       <x:c r="I22" s="6" t="str">
         <x:v>حجوزات؛ اطلب تحويلك للفريق المختص</x:v>
       </x:c>
-      <x:c r="J22" s="14" t="e">
-        <x:f>HYPERLINK("https://silkhaus.com","silkhaus.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://silkhaus.com, friendlyName=silkhaus.com</x:v>
+      <x:c r="J22" s="14" t="str">
+        <x:v>https://silkhaus.com</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2497,30 +2421,25 @@
       <x:c r="S22" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T22" s="14" t="e">
-        <x:f>HYPERLINK("https://www.linkedin.com/company/wearesilkhaus/","linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.linkedin.com/company/wearesilkhaus/, friendlyName=linkedin.com</x:v>
+      <x:c r="T22" s="14" t="str">
+        <x:v>https://www.linkedin.com/company/wearesilkhaus/</x:v>
       </x:c>
       <x:c r="U22" s="14" t="str">
         <x:v>https://www.wamda.com/2025/01/silkhaus-fuel-ksa-expansion-seven-figure-growth-round
 https://app.dealroom.co/companies/silkhaus
 https://www.wamda.com/2024/01/silkhaus-closes-pre-series-round-accelerate-expansion-plans</x:v>
       </x:c>
-      <x:c r="V22" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/2025/01/silkhaus-fuel-ksa-expansion-seven-figure-growth-round","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/2025/01/silkhaus-fuel-ksa-expansion-seven-figure-growth-round, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W22" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silkhaus.com/","silkhaus.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silkhaus.com/, friendlyName=silkhaus.com</x:v>
-      </x:c>
-      <x:c r="X22" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silkhaus.com/","silkhaus.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silkhaus.com/, friendlyName=silkhaus.com</x:v>
-      </x:c>
-      <x:c r="Y22" s="14" t="e">
-        <x:f>HYPERLINK("https://www.silkhaus.com/","silkhaus.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.silkhaus.com/, friendlyName=silkhaus.com</x:v>
+      <x:c r="V22" s="14" t="str">
+        <x:v>https://www.wamda.com/2025/01/silkhaus-fuel-ksa-expansion-seven-figure-growth-round</x:v>
+      </x:c>
+      <x:c r="W22" s="14" t="str">
+        <x:v>https://www.silkhaus.com/</x:v>
+      </x:c>
+      <x:c r="X22" s="14" t="str">
+        <x:v>https://www.silkhaus.com/</x:v>
+      </x:c>
+      <x:c r="Y22" s="14" t="str">
+        <x:v>https://www.silkhaus.com/</x:v>
       </x:c>
       <x:c r="Z22" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2557,9 +2476,8 @@
       <x:c r="I23" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J23" s="14" t="e">
-        <x:f>HYPERLINK("https://getstake.com","getstake.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://getstake.com, friendlyName=getstake.com</x:v>
+      <x:c r="J23" s="14" t="str">
+        <x:v>https://getstake.com</x:v>
       </x:c>
       <x:c r="K23" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2588,29 +2506,25 @@
       <x:c r="S23" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T23" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/, friendlyName=techcrunch.com</x:v>
+      <x:c r="T23" s="14" t="str">
+        <x:v>https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/</x:v>
       </x:c>
       <x:c r="U23" s="14" t="str">
         <x:v>https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/
 https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/stake-2/
 https://www.thenationalnews.com/business/property/dubai-property-crowdfunding-platform-stake-raises-4m-in-seed-funding-1.1232425</x:v>
       </x:c>
-      <x:c r="V23" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/, friendlyName=techcrunch.com</x:v>
-      </x:c>
-      <x:c r="W23" s="14" t="e">
-        <x:f>HYPERLINK("https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf","cdn.getstake.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf, friendlyName=cdn.getstake.com</x:v>
+      <x:c r="V23" s="14" t="str">
+        <x:v>https://techcrunch.com/2022/08/29/dubai-based-stake-raises-8-million-to-let-people-across-the-globe-invest-in-local-properties/</x:v>
+      </x:c>
+      <x:c r="W23" s="14" t="str">
+        <x:v>https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf</x:v>
       </x:c>
       <x:c r="X23" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y23" s="14" t="e">
-        <x:f>HYPERLINK("https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf","cdn.getstake.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf, friendlyName=cdn.getstake.com</x:v>
+      <x:c r="Y23" s="14" t="str">
+        <x:v>https://cdn.getstake.com/www.getstake.com/Stake_Investor_Report_2025.pdf</x:v>
       </x:c>
       <x:c r="Z23" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2647,9 +2561,8 @@
       <x:c r="I24" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J24" s="14" t="e">
-        <x:f>HYPERLINK("https://takalamhere.com","takalamhere.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://takalamhere.com, friendlyName=takalamhere.com</x:v>
+      <x:c r="J24" s="14" t="str">
+        <x:v>https://takalamhere.com</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2676,30 +2589,25 @@
       <x:c r="S24" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T24" s="14" t="e">
-        <x:f>HYPERLINK("https://www.gulfleads.ae/company/takalam-e337ae","gulfleads.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.gulfleads.ae/company/takalam-e337ae, friendlyName=gulfleads.ae</x:v>
+      <x:c r="T24" s="14" t="str">
+        <x:v>https://www.gulfleads.ae/company/takalam-e337ae</x:v>
       </x:c>
       <x:c r="U24" s="14" t="str">
         <x:v>https://www.gulfleads.ae/company/takalam-e337ae
 https://prospeo.io/c/takalam
 https://www.wamda.com/en/2022/01/uae-based-takalam-raises-1-million-pre-seed-round</x:v>
       </x:c>
-      <x:c r="V24" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/en/2022/01/uae-based-takalam-raises-1-million-pre-seed-round","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/en/2022/01/uae-based-takalam-raises-1-million-pre-seed-round, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W24" s="14" t="e">
-        <x:f>HYPERLINK("https://business.takalamhere.com/","business.takalamhere.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://business.takalamhere.com/, friendlyName=business.takalamhere.com</x:v>
-      </x:c>
-      <x:c r="X24" s="14" t="e">
-        <x:f>HYPERLINK("https://business.takalamhere.com/","business.takalamhere.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://business.takalamhere.com/, friendlyName=business.takalamhere.com</x:v>
-      </x:c>
-      <x:c r="Y24" s="14" t="e">
-        <x:f>HYPERLINK("https://stagingvm.takalamhere.com/ar/contact-us","stagingvm.takalamhere.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://stagingvm.takalamhere.com/ar/contact-us, friendlyName=stagingvm.takalamhere.com</x:v>
+      <x:c r="V24" s="14" t="str">
+        <x:v>https://www.wamda.com/en/2022/01/uae-based-takalam-raises-1-million-pre-seed-round</x:v>
+      </x:c>
+      <x:c r="W24" s="14" t="str">
+        <x:v>https://business.takalamhere.com/</x:v>
+      </x:c>
+      <x:c r="X24" s="14" t="str">
+        <x:v>https://business.takalamhere.com/</x:v>
+      </x:c>
+      <x:c r="Y24" s="14" t="str">
+        <x:v>https://stagingvm.takalamhere.com/ar/contact-us</x:v>
       </x:c>
       <x:c r="Z24" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2736,9 +2644,8 @@
       <x:c r="I25" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J25" s="14" t="e">
-        <x:f>HYPERLINK("https://tarjama.com","tarjama.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarjama.com, friendlyName=tarjama.com</x:v>
+      <x:c r="J25" s="14" t="str">
+        <x:v>https://tarjama.com</x:v>
       </x:c>
       <x:c r="K25" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2767,30 +2674,25 @@
       <x:c r="S25" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T25" s="14" t="e">
-        <x:f>HYPERLINK("https://tarjama.com/contact-us/","tarjama.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarjama.com/contact-us/, friendlyName=tarjama.com</x:v>
+      <x:c r="T25" s="14" t="str">
+        <x:v>https://tarjama.com/contact-us/</x:v>
       </x:c>
       <x:c r="U25" s="14" t="str">
         <x:v>https://www.gulfleads.ae/company/tarjama-0dac60
 https://www.al-monitor.com/originals/2025/08/how-arabic-translation-firm-jordan-became-gulf-ai-player
 https://www.wamda.com/2025/05/wamda-capital-joins-tarjama-15-million-series-a</x:v>
       </x:c>
-      <x:c r="V25" s="14" t="e">
-        <x:f>HYPERLINK("https://www.al-monitor.com/originals/2025/08/how-arabic-translation-firm-jordan-became-gulf-ai-player","al-monitor.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.al-monitor.com/originals/2025/08/how-arabic-translation-firm-jordan-became-gulf-ai-player, friendlyName=al-monitor.com</x:v>
-      </x:c>
-      <x:c r="W25" s="14" t="e">
-        <x:f>HYPERLINK("https://tarjama.com/contact-us/","tarjama.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarjama.com/contact-us/, friendlyName=tarjama.com</x:v>
-      </x:c>
-      <x:c r="X25" s="14" t="e">
-        <x:f>HYPERLINK("https://tarjama.com/contact-us/","tarjama.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarjama.com/contact-us/, friendlyName=tarjama.com</x:v>
-      </x:c>
-      <x:c r="Y25" s="14" t="e">
-        <x:f>HYPERLINK("https://tarjama.com/contact-us/","tarjama.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarjama.com/contact-us/, friendlyName=tarjama.com</x:v>
+      <x:c r="V25" s="14" t="str">
+        <x:v>https://www.al-monitor.com/originals/2025/08/how-arabic-translation-firm-jordan-became-gulf-ai-player</x:v>
+      </x:c>
+      <x:c r="W25" s="14" t="str">
+        <x:v>https://tarjama.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="X25" s="14" t="str">
+        <x:v>https://tarjama.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="Y25" s="14" t="str">
+        <x:v>https://tarjama.com/contact-us/</x:v>
       </x:c>
       <x:c r="Z25" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2827,9 +2729,8 @@
       <x:c r="I26" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="J26" s="14" t="e">
-        <x:f>HYPERLINK("https://telr.com","telr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://telr.com, friendlyName=telr.com</x:v>
+      <x:c r="J26" s="14" t="str">
+        <x:v>https://telr.com</x:v>
       </x:c>
       <x:c r="K26" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2856,9 +2757,8 @@
       <x:c r="S26" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T26" s="14" t="e">
-        <x:f>HYPERLINK("https://www.gulfstartupmap.com/startups/telr","gulfstartupmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.gulfstartupmap.com/startups/telr, friendlyName=gulfstartupmap.com</x:v>
+      <x:c r="T26" s="14" t="str">
+        <x:v>https://www.gulfstartupmap.com/startups/telr</x:v>
       </x:c>
       <x:c r="U26" s="14" t="str">
         <x:v>https://www.gulfstartupmap.com/startups/telr
@@ -2868,17 +2768,14 @@
       <x:c r="V26" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W26" s="14" t="e">
-        <x:f>HYPERLINK("https://telr.com/contact-us","telr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://telr.com/contact-us, friendlyName=telr.com</x:v>
-      </x:c>
-      <x:c r="X26" s="14" t="e">
-        <x:f>HYPERLINK("https://telr.com/contact-us","telr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://telr.com/contact-us, friendlyName=telr.com</x:v>
-      </x:c>
-      <x:c r="Y26" s="14" t="e">
-        <x:f>HYPERLINK("https://telr.com/contact-us","telr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://telr.com/contact-us, friendlyName=telr.com</x:v>
+      <x:c r="W26" s="14" t="str">
+        <x:v>https://telr.com/contact-us</x:v>
+      </x:c>
+      <x:c r="X26" s="14" t="str">
+        <x:v>https://telr.com/contact-us</x:v>
+      </x:c>
+      <x:c r="Y26" s="14" t="str">
+        <x:v>https://telr.com/contact-us</x:v>
       </x:c>
       <x:c r="Z26" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -2915,9 +2812,8 @@
       <x:c r="I27" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J27" s="14" t="e">
-        <x:f>HYPERLINK("https://terrax.world","terrax.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://terrax.world, friendlyName=terrax.world</x:v>
+      <x:c r="J27" s="14" t="str">
+        <x:v>https://terrax.world</x:v>
       </x:c>
       <x:c r="K27" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -2946,9 +2842,8 @@
       <x:c r="S27" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T27" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pwc.com/m1/en/esg/images/future50/docs/industry/Terrax-Environmental-Limited.pdf","pwc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pwc.com/m1/en/esg/images/future50/docs/industry/Terrax-Environmental-Limited.pdf, friendlyName=pwc.com</x:v>
+      <x:c r="T27" s="14" t="str">
+        <x:v>https://www.pwc.com/m1/en/esg/images/future50/docs/industry/Terrax-Environmental-Limited.pdf</x:v>
       </x:c>
       <x:c r="U27" s="14" t="str">
         <x:v>https://www.linkedin.com/company/terraxworld/
@@ -2958,17 +2853,14 @@
       <x:c r="V27" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W27" s="14" t="e">
-        <x:f>HYPERLINK("https://terrax.world/","terrax.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://terrax.world/, friendlyName=terrax.world</x:v>
-      </x:c>
-      <x:c r="X27" s="14" t="e">
-        <x:f>HYPERLINK("https://terrax.world/","terrax.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://terrax.world/, friendlyName=terrax.world</x:v>
-      </x:c>
-      <x:c r="Y27" s="14" t="e">
-        <x:f>HYPERLINK("https://terrax.world/","terrax.world")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://terrax.world/, friendlyName=terrax.world</x:v>
+      <x:c r="W27" s="14" t="str">
+        <x:v>https://terrax.world/</x:v>
+      </x:c>
+      <x:c r="X27" s="14" t="str">
+        <x:v>https://terrax.world/</x:v>
+      </x:c>
+      <x:c r="Y27" s="14" t="str">
+        <x:v>https://terrax.world/</x:v>
       </x:c>
       <x:c r="Z27" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3005,9 +2897,8 @@
       <x:c r="I28" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J28" s="14" t="e">
-        <x:f>HYPERLINK("https://watermelon.market","watermelon.market")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://watermelon.market, friendlyName=watermelon.market</x:v>
+      <x:c r="J28" s="14" t="str">
+        <x:v>https://watermelon.market</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3034,28 +2925,24 @@
       <x:c r="S28" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T28" s="14" t="e">
-        <x:f>HYPERLINK("https://en.wikipedia.org/wiki/Barcode_%28drink%29","en.wikipedia.org")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.wikipedia.org/wiki/Barcode_%28drink%29, friendlyName=en.wikipedia.org</x:v>
+      <x:c r="T28" s="14" t="str">
+        <x:v>https://watermelon.market/contact-us/
+https://www.sme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U28" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V28" s="14" t="e">
-        <x:f>HYPERLINK("https://uaerg.ae/watermelon-teams-up-with-daman-investments-for-4m-series-a/","uaerg.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://uaerg.ae/watermelon-teams-up-with-daman-investments-for-4m-series-a/, friendlyName=uaerg.ae</x:v>
-      </x:c>
-      <x:c r="W28" s="14" t="e">
-        <x:f>HYPERLINK("https://ae.linkedin.com/company/watermelonecosystem","ae.linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ae.linkedin.com/company/watermelonecosystem, friendlyName=ae.linkedin.com</x:v>
-      </x:c>
-      <x:c r="X28" s="14" t="e">
-        <x:f>HYPERLINK("https://ae.linkedin.com/company/watermelonecosystem","ae.linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ae.linkedin.com/company/watermelonecosystem, friendlyName=ae.linkedin.com</x:v>
-      </x:c>
-      <x:c r="Y28" s="14" t="e">
-        <x:f>HYPERLINK("https://watermelon.market/contact-us/","watermelon.market")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://watermelon.market/contact-us/, friendlyName=watermelon.market</x:v>
+      <x:c r="V28" s="14" t="str">
+        <x:v>https://uaerg.ae/watermelon-teams-up-with-daman-investments-for-4m-series-a/</x:v>
+      </x:c>
+      <x:c r="W28" s="14" t="str">
+        <x:v>https://ae.linkedin.com/company/watermelonecosystem</x:v>
+      </x:c>
+      <x:c r="X28" s="14" t="str">
+        <x:v>https://ae.linkedin.com/company/watermelonecosystem</x:v>
+      </x:c>
+      <x:c r="Y28" s="14" t="str">
+        <x:v>https://watermelon.market/contact-us/</x:v>
       </x:c>
       <x:c r="Z28" s="6" t="str">
         <x:v>صفحة أو منشور مهني معلن</x:v>
@@ -3092,9 +2979,8 @@
       <x:c r="I29" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J29" s="14" t="e">
-        <x:f>HYPERLINK("https://wellxai.com","wellxai.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wellxai.com, friendlyName=wellxai.com</x:v>
+      <x:c r="J29" s="14" t="str">
+        <x:v>https://wellxai.com</x:v>
       </x:c>
       <x:c r="K29" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3121,29 +3007,25 @@
       <x:c r="S29" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T29" s="14" t="e">
-        <x:f>HYPERLINK("https://uaefintech.co/company/wellx/","uaefintech.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://uaefintech.co/company/wellx/, friendlyName=uaefintech.co</x:v>
+      <x:c r="T29" s="14" t="str">
+        <x:v>https://uaefintech.co/company/wellx/</x:v>
       </x:c>
       <x:c r="U29" s="14" t="str">
         <x:v>https://www.wamda.com/2023/07/uae-wellx-raises-2-million-seed-fund-expansion
 https://www.crunchbase.com/organization/wellx-ai
 https://thestartupscene.me/MenaEcosystems/UAE-Based-Wellness-Platform-Wellx-Raises-2-Million-in-Seed-Round</x:v>
       </x:c>
-      <x:c r="V29" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/2023/07/uae-wellx-raises-2-million-seed-fund-expansion","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/2023/07/uae-wellx-raises-2-million-seed-fund-expansion, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W29" s="14" t="e">
-        <x:f>HYPERLINK("https://wellxai.com/contact","wellxai.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wellxai.com/contact, friendlyName=wellxai.com</x:v>
+      <x:c r="V29" s="14" t="str">
+        <x:v>https://www.wamda.com/2023/07/uae-wellx-raises-2-million-seed-fund-expansion</x:v>
+      </x:c>
+      <x:c r="W29" s="14" t="str">
+        <x:v>https://wellxai.com/contact</x:v>
       </x:c>
       <x:c r="X29" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y29" s="14" t="e">
-        <x:f>HYPERLINK("https://wellxai.com/contact","wellxai.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wellxai.com/contact, friendlyName=wellxai.com</x:v>
+      <x:c r="Y29" s="14" t="str">
+        <x:v>https://wellxai.com/contact</x:v>
       </x:c>
       <x:c r="Z29" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3180,9 +3062,8 @@
       <x:c r="I30" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J30" s="14" t="e">
-        <x:f>HYPERLINK("https://whiteboxhr.com","whiteboxhr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://whiteboxhr.com, friendlyName=whiteboxhr.com</x:v>
+      <x:c r="J30" s="14" t="str">
+        <x:v>https://whiteboxhr.com</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3211,9 +3092,8 @@
       <x:c r="S30" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.linkedin.com/company/whiteboxhr","linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.linkedin.com/company/whiteboxhr, friendlyName=linkedin.com</x:v>
+      <x:c r="T30" s="14" t="str">
+        <x:v>https://www.linkedin.com/company/whiteboxhr</x:v>
       </x:c>
       <x:c r="U30" s="14" t="str">
         <x:v>https://www.linkedin.com/company/whiteboxhr
@@ -3223,16 +3103,14 @@
       <x:c r="V30" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.whiteboxhr.com/privacy-policy","whiteboxhr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.whiteboxhr.com/privacy-policy, friendlyName=whiteboxhr.com</x:v>
+      <x:c r="W30" s="14" t="str">
+        <x:v>https://www.whiteboxhr.com/privacy-policy</x:v>
       </x:c>
       <x:c r="X30" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.whiteboxhr.com/contact","whiteboxhr.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.whiteboxhr.com/contact, friendlyName=whiteboxhr.com</x:v>
+      <x:c r="Y30" s="14" t="str">
+        <x:v>https://www.whiteboxhr.com/contact</x:v>
       </x:c>
       <x:c r="Z30" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3269,9 +3147,8 @@
       <x:c r="I31" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="J31" s="14" t="e">
-        <x:f>HYPERLINK("https://widebot.ai","widebot.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://widebot.ai, friendlyName=widebot.ai</x:v>
+      <x:c r="J31" s="14" t="str">
+        <x:v>https://widebot.ai</x:v>
       </x:c>
       <x:c r="K31" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3298,18 +3175,17 @@
       <x:c r="S31" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T31" s="14" t="e">
-        <x:f>HYPERLINK("https://www.aclweb.org/anthology/2020.semeval-1.298.pdf","aclweb.org")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.aclweb.org/anthology/2020.semeval-1.298.pdf, friendlyName=aclweb.org</x:v>
+      <x:c r="T31" s="14" t="str">
+        <x:v>https://widebot.ai/blog/widebot-preseriesa-rou
+https://www.sme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U31" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/widebot
 https://widebot.ai/blog/widebot-preseriesa-rou
 https://www.wamda.com/index.php/2019/06/widebot-closes-pre-series-round</x:v>
       </x:c>
-      <x:c r="V31" s="14" t="e">
-        <x:f>HYPERLINK("https://widebot.ai/blog/widebot-preseriesa-rou","widebot.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://widebot.ai/blog/widebot-preseriesa-rou, friendlyName=widebot.ai</x:v>
+      <x:c r="V31" s="14" t="str">
+        <x:v>https://widebot.ai/blog/widebot-preseriesa-rou</x:v>
       </x:c>
       <x:c r="W31" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -3317,9 +3193,8 @@
       <x:c r="X31" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y31" s="14" t="e">
-        <x:f>HYPERLINK("https://widebot.ai/solutions/customer-support","widebot.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://widebot.ai/solutions/customer-support, friendlyName=widebot.ai</x:v>
+      <x:c r="Y31" s="14" t="str">
+        <x:v>https://widebot.ai/solutions/customer-support</x:v>
       </x:c>
       <x:c r="Z31" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -3356,9 +3231,8 @@
       <x:c r="I32" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J32" s="14" t="e">
-        <x:f>HYPERLINK("https://wisewell.ae","wisewell.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wisewell.ae, friendlyName=wisewell.ae</x:v>
+      <x:c r="J32" s="14" t="str">
+        <x:v>https://wisewell.ae</x:v>
       </x:c>
       <x:c r="K32" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3385,9 +3259,8 @@
       <x:c r="S32" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T32" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wisewell.com/pages/about-us","wisewell.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wisewell.com/pages/about-us, friendlyName=wisewell.com</x:v>
+      <x:c r="T32" s="14" t="str">
+        <x:v>https://www.wisewell.com/pages/about-us</x:v>
       </x:c>
       <x:c r="U32" s="14" t="str">
         <x:v>https://www.wisewell.com/pages/about-us
@@ -3397,16 +3270,14 @@
       <x:c r="V32" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W32" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wisewell.ae/policies/terms-of-service","wisewell.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wisewell.ae/policies/terms-of-service, friendlyName=wisewell.ae</x:v>
+      <x:c r="W32" s="14" t="str">
+        <x:v>https://www.wisewell.ae/policies/terms-of-service</x:v>
       </x:c>
       <x:c r="X32" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y32" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wisewell.ae/pages/contacts","wisewell.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wisewell.ae/pages/contacts, friendlyName=wisewell.ae</x:v>
+      <x:c r="Y32" s="14" t="str">
+        <x:v>https://www.wisewell.ae/pages/contacts</x:v>
       </x:c>
       <x:c r="Z32" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3443,9 +3314,8 @@
       <x:c r="I33" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J33" s="14" t="e">
-        <x:f>HYPERLINK("https://xpanceo.com","xpanceo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://xpanceo.com, friendlyName=xpanceo.com</x:v>
+      <x:c r="J33" s="14" t="str">
+        <x:v>https://xpanceo.com</x:v>
       </x:c>
       <x:c r="K33" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3474,29 +3344,25 @@
       <x:c r="S33" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T33" s="14" t="e">
-        <x:f>HYPERLINK("https://xpanceo.com/legal/privacy.pdf","xpanceo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://xpanceo.com/legal/privacy.pdf, friendlyName=xpanceo.com</x:v>
+      <x:c r="T33" s="14" t="str">
+        <x:v>https://xpanceo.com/legal/privacy.pdf</x:v>
       </x:c>
       <x:c r="U33" s="14" t="str">
         <x:v>https://prospeo.io/c/xpanceo-email-format
 https://xpanceo.com/newsroom/xpanceo-becomes-a-unicorn-with-250m-raise
 https://www.wamda.com/en/2025/07/xpanceo-secures-250-million-series-135-billion-valuation</x:v>
       </x:c>
-      <x:c r="V33" s="14" t="e">
-        <x:f>HYPERLINK("https://xpanceo.com/newsroom/xpanceo-becomes-a-unicorn-with-250m-raise","xpanceo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://xpanceo.com/newsroom/xpanceo-becomes-a-unicorn-with-250m-raise, friendlyName=xpanceo.com</x:v>
-      </x:c>
-      <x:c r="W33" s="14" t="e">
-        <x:f>HYPERLINK("https://www.xpanceo.com/contacts","xpanceo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.xpanceo.com/contacts, friendlyName=xpanceo.com</x:v>
+      <x:c r="V33" s="14" t="str">
+        <x:v>https://xpanceo.com/newsroom/xpanceo-becomes-a-unicorn-with-250m-raise</x:v>
+      </x:c>
+      <x:c r="W33" s="14" t="str">
+        <x:v>https://www.xpanceo.com/contacts</x:v>
       </x:c>
       <x:c r="X33" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y33" s="14" t="e">
-        <x:f>HYPERLINK("https://www.xpanceo.com/contacts","xpanceo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.xpanceo.com/contacts, friendlyName=xpanceo.com</x:v>
+      <x:c r="Y33" s="14" t="str">
+        <x:v>https://www.xpanceo.com/contacts</x:v>
       </x:c>
       <x:c r="Z33" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3533,9 +3399,8 @@
       <x:c r="I34" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J34" s="14" t="e">
-        <x:f>HYPERLINK("https://zeroe.io","zeroe.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zeroe.io, friendlyName=zeroe.io</x:v>
+      <x:c r="J34" s="14" t="str">
+        <x:v>https://zeroe.io</x:v>
       </x:c>
       <x:c r="K34" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3562,29 +3427,25 @@
       <x:c r="S34" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T34" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/367839/zeroe","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/367839/zeroe, friendlyName=yello.ae</x:v>
+      <x:c r="T34" s="14" t="str">
+        <x:v>https://www.yello.ae/company/367839/zeroe</x:v>
       </x:c>
       <x:c r="U34" s="14" t="str">
         <x:v>https://www.zeroe.io/
 https://www.signalhire.com/companies/zeroe/employees
 https://www.wamda.com/en/2023/12/uae-zeroe-raises-2-2-million-seed-round</x:v>
       </x:c>
-      <x:c r="V34" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/en/2023/12/uae-zeroe-raises-2-2-million-seed-round","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/en/2023/12/uae-zeroe-raises-2-2-million-seed-round, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W34" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zeroe.io/","zeroe.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zeroe.io/, friendlyName=zeroe.io</x:v>
+      <x:c r="V34" s="14" t="str">
+        <x:v>https://www.wamda.com/en/2023/12/uae-zeroe-raises-2-2-million-seed-round</x:v>
+      </x:c>
+      <x:c r="W34" s="14" t="str">
+        <x:v>https://www.zeroe.io/</x:v>
       </x:c>
       <x:c r="X34" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y34" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zeroe.io/","zeroe.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zeroe.io/, friendlyName=zeroe.io</x:v>
+      <x:c r="Y34" s="14" t="str">
+        <x:v>https://www.zeroe.io/</x:v>
       </x:c>
       <x:c r="Z34" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3621,9 +3482,8 @@
       <x:c r="I35" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="J35" s="14" t="e">
-        <x:f>HYPERLINK("https://immensa.io","immensa.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://immensa.io, friendlyName=immensa.io</x:v>
+      <x:c r="J35" s="14" t="str">
+        <x:v>https://immensa.io</x:v>
       </x:c>
       <x:c r="K35" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3650,30 +3510,25 @@
       <x:c r="S35" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T35" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/, friendlyName=techcrunch.com</x:v>
+      <x:c r="T35" s="14" t="str">
+        <x:v>https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/</x:v>
       </x:c>
       <x:c r="U35" s="14" t="str">
         <x:v>https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/
 https://dfdf.vc/press-releases/immensa-raises-growth-capital-from-dubai-future-district-fund-and-global-ventures-to-strengthen-global-advanced-manufacturing-and-supply-chain-resilience-from-dubai/
 https://immensa.io/news/immensa-growth-capital-dubai-future-district-fund/</x:v>
       </x:c>
-      <x:c r="V35" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/, friendlyName=techcrunch.com</x:v>
-      </x:c>
-      <x:c r="W35" s="14" t="e">
-        <x:f>HYPERLINK("https://immensa.io/contact-us/","immensa.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://immensa.io/contact-us/, friendlyName=immensa.io</x:v>
-      </x:c>
-      <x:c r="X35" s="14" t="e">
-        <x:f>HYPERLINK("https://immensa.io/contact-us/","immensa.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://immensa.io/contact-us/, friendlyName=immensa.io</x:v>
-      </x:c>
-      <x:c r="Y35" s="14" t="e">
-        <x:f>HYPERLINK("https://immensa.io/contact-us/","immensa.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://immensa.io/contact-us/, friendlyName=immensa.io</x:v>
+      <x:c r="V35" s="14" t="str">
+        <x:v>https://techcrunch.com/2023/11/28/immensa-a-mena-based-additive-manufacturing-and-digital-inventory-platform-raises-20-million/</x:v>
+      </x:c>
+      <x:c r="W35" s="14" t="str">
+        <x:v>https://immensa.io/contact-us/</x:v>
+      </x:c>
+      <x:c r="X35" s="14" t="str">
+        <x:v>https://immensa.io/contact-us/</x:v>
+      </x:c>
+      <x:c r="Y35" s="14" t="str">
+        <x:v>https://immensa.io/contact-us/</x:v>
       </x:c>
       <x:c r="Z35" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3710,9 +3565,8 @@
       <x:c r="I36" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J36" s="14" t="e">
-        <x:f>HYPERLINK("https://realkeyper.com","realkeyper.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://realkeyper.com, friendlyName=realkeyper.com</x:v>
+      <x:c r="J36" s="14" t="str">
+        <x:v>https://realkeyper.com</x:v>
       </x:c>
       <x:c r="K36" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3739,30 +3593,25 @@
       <x:c r="S36" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T36" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/portfolio/keyper/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/portfolio/keyper/, friendlyName=becocapital.com</x:v>
+      <x:c r="T36" s="14" t="str">
+        <x:v>https://www.becocapital.com/portfolio/keyper/</x:v>
       </x:c>
       <x:c r="U36" s="14" t="str">
         <x:v>https://www.becocapital.com/portfolio/keyper/
 https://www.wamda.com/en/2024/05/keyper-secures-34-million-mix-equity-sukuk
 https://www.realkeyper.com/about</x:v>
       </x:c>
-      <x:c r="V36" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/portfolio/keyper/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/portfolio/keyper/, friendlyName=becocapital.com</x:v>
-      </x:c>
-      <x:c r="W36" s="14" t="e">
-        <x:f>HYPERLINK("https://www.realkeyper.com/","realkeyper.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.realkeyper.com/, friendlyName=realkeyper.com</x:v>
-      </x:c>
-      <x:c r="X36" s="14" t="e">
-        <x:f>HYPERLINK("https://www.realkeyper.com/","realkeyper.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.realkeyper.com/, friendlyName=realkeyper.com</x:v>
-      </x:c>
-      <x:c r="Y36" s="14" t="e">
-        <x:f>HYPERLINK("https://www.realkeyper.com/faq","realkeyper.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.realkeyper.com/faq, friendlyName=realkeyper.com</x:v>
+      <x:c r="V36" s="14" t="str">
+        <x:v>https://www.becocapital.com/portfolio/keyper/</x:v>
+      </x:c>
+      <x:c r="W36" s="14" t="str">
+        <x:v>https://www.realkeyper.com/</x:v>
+      </x:c>
+      <x:c r="X36" s="14" t="str">
+        <x:v>https://www.realkeyper.com/</x:v>
+      </x:c>
+      <x:c r="Y36" s="14" t="str">
+        <x:v>https://www.realkeyper.com/faq</x:v>
       </x:c>
       <x:c r="Z36" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3799,9 +3648,8 @@
       <x:c r="I37" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J37" s="14" t="e">
-        <x:f>HYPERLINK("https://nabtahealth.com","nabtahealth.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nabtahealth.com, friendlyName=nabtahealth.com</x:v>
+      <x:c r="J37" s="14" t="str">
+        <x:v>https://nabtahealth.com</x:v>
       </x:c>
       <x:c r="K37" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3828,9 +3676,8 @@
       <x:c r="S37" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T37" s="14" t="e">
-        <x:f>HYPERLINK("https://hospitecnia.com/sites/default/files/158829227031588292270.pdf","hospitecnia.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hospitecnia.com/sites/default/files/158829227031588292270.pdf, friendlyName=hospitecnia.com</x:v>
+      <x:c r="T37" s="14" t="str">
+        <x:v>https://hospitecnia.com/sites/default/files/158829227031588292270.pdf</x:v>
       </x:c>
       <x:c r="U37" s="14" t="str">
         <x:v>https://hospitecnia.com/sites/default/files/158829227031588292270.pdf
@@ -3840,17 +3687,14 @@
       <x:c r="V37" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W37" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=com.nabtahealth.nabta","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=com.nabtahealth.nabta, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="X37" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=com.nabtahealth.nabta","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=com.nabtahealth.nabta, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="Y37" s="14" t="e">
-        <x:f>HYPERLINK("https://nabtahealth.com/contact/?lang=ar","nabtahealth.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nabtahealth.com/contact/?lang=ar, friendlyName=nabtahealth.com</x:v>
+      <x:c r="W37" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=com.nabtahealth.nabta</x:v>
+      </x:c>
+      <x:c r="X37" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=com.nabtahealth.nabta</x:v>
+      </x:c>
+      <x:c r="Y37" s="14" t="str">
+        <x:v>https://nabtahealth.com/contact/?lang=ar</x:v>
       </x:c>
       <x:c r="Z37" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -3887,9 +3731,8 @@
       <x:c r="I38" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J38" s="14" t="e">
-        <x:f>HYPERLINK("https://myzoi.com","myzoi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://myzoi.com, friendlyName=myzoi.com</x:v>
+      <x:c r="J38" s="14" t="str">
+        <x:v>https://myzoi.com</x:v>
       </x:c>
       <x:c r="K38" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -3916,9 +3759,8 @@
       <x:c r="S38" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.myzoi.com/contact-us/","myzoi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.myzoi.com/contact-us/, friendlyName=myzoi.com</x:v>
+      <x:c r="T38" s="14" t="str">
+        <x:v>https://www.myzoi.com/contact-us/</x:v>
       </x:c>
       <x:c r="U38" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -3926,17 +3768,14 @@
       <x:c r="V38" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.myzoi.com/contact-us/","myzoi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.myzoi.com/contact-us/, friendlyName=myzoi.com</x:v>
-      </x:c>
-      <x:c r="X38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.myzoi.com/contact-us/","myzoi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.myzoi.com/contact-us/, friendlyName=myzoi.com</x:v>
-      </x:c>
-      <x:c r="Y38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.myzoi.com/contact-us/","myzoi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.myzoi.com/contact-us/, friendlyName=myzoi.com</x:v>
+      <x:c r="W38" s="14" t="str">
+        <x:v>https://www.myzoi.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="X38" s="14" t="str">
+        <x:v>https://www.myzoi.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="Y38" s="14" t="str">
+        <x:v>https://www.myzoi.com/contact-us/</x:v>
       </x:c>
       <x:c r="Z38" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -3973,9 +3812,8 @@
       <x:c r="I39" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="J39" s="14" t="e">
-        <x:f>HYPERLINK("https://net0.com","net0.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://net0.com, friendlyName=net0.com</x:v>
+      <x:c r="J39" s="14" t="str">
+        <x:v>https://net0.com</x:v>
       </x:c>
       <x:c r="K39" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4002,9 +3840,9 @@
       <x:c r="S39" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T39" s="14" t="e">
-        <x:f>HYPERLINK("https://cdn.asp.events/CLIENT_Innovati_94A26F7C_B3C0_752F_CC179EFAFD17992A/sites/Innovation-Zero-2023/media/2024_Innovation_Zero_Awards_Shortlisted-Candidates-and-Winners.pdf","cdn.asp.events")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cdn.asp.events/CLIENT_Innovati_94A26F7C_B3C0_752F_CC179EFAFD17992A/sites/Innovation-Zero-2023/media/2024_Innovation_Zero_Awards_Shortlisted-Candidates-and-Winners.pdf, friendlyName=cdn.asp.events</x:v>
+      <x:c r="T39" s="14" t="str">
+        <x:v>https://net0.com/contact
+https://sme.gov.ae/en/future-100-list</x:v>
       </x:c>
       <x:c r="U39" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -4018,9 +3856,8 @@
       <x:c r="X39" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y39" s="14" t="e">
-        <x:f>HYPERLINK("https://net0.com/contact","net0.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://net0.com/contact, friendlyName=net0.com</x:v>
+      <x:c r="Y39" s="14" t="str">
+        <x:v>https://net0.com/contact</x:v>
       </x:c>
       <x:c r="Z39" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -4057,9 +3894,8 @@
       <x:c r="I40" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J40" s="14" t="e">
-        <x:f>HYPERLINK("https://natrify.com","natrify.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natrify.com, friendlyName=natrify.com</x:v>
+      <x:c r="J40" s="14" t="str">
+        <x:v>https://natrify.com</x:v>
       </x:c>
       <x:c r="K40" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4088,9 +3924,8 @@
       <x:c r="S40" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T40" s="14" t="e">
-        <x:f>HYPERLINK("https://natrify.github.io/web/","natrify.github.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natrify.github.io/web/, friendlyName=natrify.github.io</x:v>
+      <x:c r="T40" s="14" t="str">
+        <x:v>https://natrify.github.io/web/</x:v>
       </x:c>
       <x:c r="U40" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -4098,16 +3933,14 @@
       <x:c r="V40" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W40" s="14" t="e">
-        <x:f>HYPERLINK("https://natrify.github.io/web/","natrify.github.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natrify.github.io/web/, friendlyName=natrify.github.io</x:v>
+      <x:c r="W40" s="14" t="str">
+        <x:v>https://natrify.github.io/web/</x:v>
       </x:c>
       <x:c r="X40" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y40" s="14" t="e">
-        <x:f>HYPERLINK("https://natrify.github.io/web/","natrify.github.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natrify.github.io/web/, friendlyName=natrify.github.io</x:v>
+      <x:c r="Y40" s="14" t="str">
+        <x:v>https://natrify.github.io/web/</x:v>
       </x:c>
       <x:c r="Z40" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4144,9 +3977,8 @@
       <x:c r="I41" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J41" s="14" t="e">
-        <x:f>HYPERLINK("https://fenixgames.com","fenixgames.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fenixgames.com, friendlyName=fenixgames.com</x:v>
+      <x:c r="J41" s="14" t="str">
+        <x:v>https://fenixgames.com</x:v>
       </x:c>
       <x:c r="K41" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4173,27 +4005,23 @@
       <x:c r="S41" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T41" s="14" t="e">
-        <x:f>HYPERLINK("https://fenixgames.com/","fenixgames.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fenixgames.com/, friendlyName=fenixgames.com</x:v>
+      <x:c r="T41" s="14" t="str">
+        <x:v>https://fenixgames.com/</x:v>
       </x:c>
       <x:c r="U41" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V41" s="14" t="e">
-        <x:f>HYPERLINK("https://yourstory.com/companies/fenix-games","yourstory.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yourstory.com/companies/fenix-games, friendlyName=yourstory.com</x:v>
-      </x:c>
-      <x:c r="W41" s="14" t="e">
-        <x:f>HYPERLINK("https://fenixgames.com/","fenixgames.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fenixgames.com/, friendlyName=fenixgames.com</x:v>
+      <x:c r="V41" s="14" t="str">
+        <x:v>https://yourstory.com/companies/fenix-games</x:v>
+      </x:c>
+      <x:c r="W41" s="14" t="str">
+        <x:v>https://fenixgames.com/</x:v>
       </x:c>
       <x:c r="X41" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y41" s="14" t="e">
-        <x:f>HYPERLINK("https://fenixgames.com/","fenixgames.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fenixgames.com/, friendlyName=fenixgames.com</x:v>
+      <x:c r="Y41" s="14" t="str">
+        <x:v>https://fenixgames.com/</x:v>
       </x:c>
       <x:c r="Z41" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4230,9 +4058,8 @@
       <x:c r="I42" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J42" s="14" t="e">
-        <x:f>HYPERLINK("https://huspy.com","huspy.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://huspy.com, friendlyName=huspy.com</x:v>
+      <x:c r="J42" s="14" t="str">
+        <x:v>https://huspy.com</x:v>
       </x:c>
       <x:c r="K42" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4259,30 +4086,25 @@
       <x:c r="S42" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T42" s="14" t="e">
-        <x:f>HYPERLINK("https://huspy.com/ae/about","huspy.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://huspy.com/ae/about, friendlyName=huspy.com</x:v>
+      <x:c r="T42" s="14" t="str">
+        <x:v>https://huspy.com/ae/about</x:v>
       </x:c>
       <x:c r="U42" s="14" t="str">
         <x:v>https://huspy.com/ae/about
 https://www.crunchbase.com/organization/huspy
 https://huspy.com/blog/huspy-series-a</x:v>
       </x:c>
-      <x:c r="V42" s="14" t="e">
-        <x:f>HYPERLINK("https://huspy.com/blog/huspy-series-a","huspy.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://huspy.com/blog/huspy-series-a, friendlyName=huspy.com</x:v>
-      </x:c>
-      <x:c r="W42" s="14" t="e">
-        <x:f>HYPERLINK("https://huspy.com/ae/about","huspy.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://huspy.com/ae/about, friendlyName=huspy.com</x:v>
-      </x:c>
-      <x:c r="X42" s="14" t="e">
-        <x:f>HYPERLINK("https://www.huspy.es/ae/content/terms-and-conditions","huspy.es")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.huspy.es/ae/content/terms-and-conditions, friendlyName=huspy.es</x:v>
-      </x:c>
-      <x:c r="Y42" s="14" t="e">
-        <x:f>HYPERLINK("https://huspy.com/ae/about","huspy.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://huspy.com/ae/about, friendlyName=huspy.com</x:v>
+      <x:c r="V42" s="14" t="str">
+        <x:v>https://huspy.com/blog/huspy-series-a</x:v>
+      </x:c>
+      <x:c r="W42" s="14" t="str">
+        <x:v>https://huspy.com/ae/about</x:v>
+      </x:c>
+      <x:c r="X42" s="14" t="str">
+        <x:v>https://www.huspy.es/ae/content/terms-and-conditions</x:v>
+      </x:c>
+      <x:c r="Y42" s="14" t="str">
+        <x:v>https://huspy.com/ae/about</x:v>
       </x:c>
       <x:c r="Z42" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4319,9 +4141,8 @@
       <x:c r="I43" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J43" s="14" t="e">
-        <x:f>HYPERLINK("https://flow48.com","flow48.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flow48.com, friendlyName=flow48.com</x:v>
+      <x:c r="J43" s="14" t="str">
+        <x:v>https://flow48.com</x:v>
       </x:c>
       <x:c r="K43" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4350,29 +4171,25 @@
       <x:c r="S43" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T43" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/FLOW-48-FORFAITING-SERVICES-L-L-C-249321","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/FLOW-48-FORFAITING-SERVICES-L-L-C-249321, friendlyName=decypha.com</x:v>
+      <x:c r="T43" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/FLOW-48-FORFAITING-SERVICES-L-L-C-249321</x:v>
       </x:c>
       <x:c r="U43" s="14" t="str">
         <x:v>https://prospeo.io/c/flow48
 https://ent.news/2025/2/2416.pdf
 https://www.crunchbase.com/organization/flow48</x:v>
       </x:c>
-      <x:c r="V43" s="14" t="e">
-        <x:f>HYPERLINK("https://uaestartupmap.com/company/flow48","uaestartupmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://uaestartupmap.com/company/flow48, friendlyName=uaestartupmap.com</x:v>
-      </x:c>
-      <x:c r="W43" s="14" t="e">
-        <x:f>HYPERLINK("https://www.flow48.com/contact","flow48.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.flow48.com/contact, friendlyName=flow48.com</x:v>
+      <x:c r="V43" s="14" t="str">
+        <x:v>https://uaestartupmap.com/company/flow48</x:v>
+      </x:c>
+      <x:c r="W43" s="14" t="str">
+        <x:v>https://www.flow48.com/contact</x:v>
       </x:c>
       <x:c r="X43" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y43" s="14" t="e">
-        <x:f>HYPERLINK("https://www.flow48.com/contact","flow48.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.flow48.com/contact, friendlyName=flow48.com</x:v>
+      <x:c r="Y43" s="14" t="str">
+        <x:v>https://www.flow48.com/contact</x:v>
       </x:c>
       <x:c r="Z43" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4409,9 +4226,8 @@
       <x:c r="I44" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J44" s="14" t="e">
-        <x:f>HYPERLINK("https://comfi.ai","comfi.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://comfi.ai, friendlyName=comfi.ai</x:v>
+      <x:c r="J44" s="14" t="str">
+        <x:v>https://comfi.ai</x:v>
       </x:c>
       <x:c r="K44" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4438,30 +4254,25 @@
       <x:c r="S44" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T44" s="14" t="e">
-        <x:f>HYPERLINK("https://prospeo.io/c/comfi-ai","prospeo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prospeo.io/c/comfi-ai, friendlyName=prospeo.io</x:v>
+      <x:c r="T44" s="14" t="str">
+        <x:v>https://prospeo.io/c/comfi-ai</x:v>
       </x:c>
       <x:c r="U44" s="14" t="str">
         <x:v>https://prospeo.io/c/comfi-ai
 https://comfi.ai/blog/comfi-raises-us-65mln-pre-series-a-round
 https://www.wamda.com/2024/06/comfi-secures-5-million-debt-facility-expedite-bnpl-plans</x:v>
       </x:c>
-      <x:c r="V44" s="14" t="e">
-        <x:f>HYPERLINK("https://comfi.ai/blog/comfi-raises-us-65mln-pre-series-a-round","comfi.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://comfi.ai/blog/comfi-raises-us-65mln-pre-series-a-round, friendlyName=comfi.ai</x:v>
-      </x:c>
-      <x:c r="W44" s="14" t="e">
-        <x:f>HYPERLINK("https://comfi.ai/contact-us","comfi.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://comfi.ai/contact-us, friendlyName=comfi.ai</x:v>
-      </x:c>
-      <x:c r="X44" s="14" t="e">
-        <x:f>HYPERLINK("https://comfi.ai/contact-us","comfi.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://comfi.ai/contact-us, friendlyName=comfi.ai</x:v>
-      </x:c>
-      <x:c r="Y44" s="14" t="e">
-        <x:f>HYPERLINK("https://comfi.ai/contact-us","comfi.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://comfi.ai/contact-us, friendlyName=comfi.ai</x:v>
+      <x:c r="V44" s="14" t="str">
+        <x:v>https://comfi.ai/blog/comfi-raises-us-65mln-pre-series-a-round</x:v>
+      </x:c>
+      <x:c r="W44" s="14" t="str">
+        <x:v>https://comfi.ai/contact-us</x:v>
+      </x:c>
+      <x:c r="X44" s="14" t="str">
+        <x:v>https://comfi.ai/contact-us</x:v>
+      </x:c>
+      <x:c r="Y44" s="14" t="str">
+        <x:v>https://comfi.ai/contact-us</x:v>
       </x:c>
       <x:c r="Z44" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4498,9 +4309,8 @@
       <x:c r="I45" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J45" s="14" t="e">
-        <x:f>HYPERLINK("https://flapkap.com","flapkap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flapkap.com, friendlyName=flapkap.com</x:v>
+      <x:c r="J45" s="14" t="str">
+        <x:v>https://flapkap.com</x:v>
       </x:c>
       <x:c r="K45" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4527,30 +4337,25 @@
       <x:c r="S45" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.flapkap.com/about-us","flapkap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.flapkap.com/about-us, friendlyName=flapkap.com</x:v>
+      <x:c r="T45" s="14" t="str">
+        <x:v>https://www.flapkap.com/about-us</x:v>
       </x:c>
       <x:c r="U45" s="14" t="str">
         <x:v>https://www.flapkap.com/about-us
 https://www.becocapital.com/portfolio/flapkap/
 https://techcrunch.com/2022/10/12/flapkap-provides-revenue-based-financing-to-e-commerce-brands-in-mena-gets-3-6m-seed-funding/</x:v>
       </x:c>
-      <x:c r="V45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/portfolio/flapkap/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/portfolio/flapkap/, friendlyName=becocapital.com</x:v>
-      </x:c>
-      <x:c r="W45" s="14" t="e">
-        <x:f>HYPERLINK("https://fk-static.flapkap.com/","fk-static.flapkap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fk-static.flapkap.com/, friendlyName=fk-static.flapkap.com</x:v>
-      </x:c>
-      <x:c r="X45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/FlapKap-249695","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/FlapKap-249695, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="Y45" s="14" t="e">
-        <x:f>HYPERLINK("https://fk-static.flapkap.com/","fk-static.flapkap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fk-static.flapkap.com/, friendlyName=fk-static.flapkap.com</x:v>
+      <x:c r="V45" s="14" t="str">
+        <x:v>https://www.becocapital.com/portfolio/flapkap/</x:v>
+      </x:c>
+      <x:c r="W45" s="14" t="str">
+        <x:v>https://fk-static.flapkap.com/</x:v>
+      </x:c>
+      <x:c r="X45" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/FlapKap-249695</x:v>
+      </x:c>
+      <x:c r="Y45" s="14" t="str">
+        <x:v>https://fk-static.flapkap.com/</x:v>
       </x:c>
       <x:c r="Z45" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4587,9 +4392,8 @@
       <x:c r="I46" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J46" s="14" t="e">
-        <x:f>HYPERLINK("https://crediblex.io","crediblex.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://crediblex.io, friendlyName=crediblex.io</x:v>
+      <x:c r="J46" s="14" t="str">
+        <x:v>https://crediblex.io</x:v>
       </x:c>
       <x:c r="K46" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4616,29 +4420,25 @@
       <x:c r="S46" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T46" s="14" t="e">
-        <x:f>HYPERLINK("https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/","crediblex.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/, friendlyName=crediblex.io</x:v>
+      <x:c r="T46" s="14" t="str">
+        <x:v>https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/</x:v>
       </x:c>
       <x:c r="U46" s="14" t="str">
         <x:v>https://mma.prnewswire.com/media/2578918/CredibleX_PressRelease.pdf?p=pdf
 https://www.prweb.com/releases/uae-based-embedded-sme-lending-startup-crediblex-raises-us55mn-in-seed-round-302330056.html
 https://crediblex.io/crediblex-blog/crediblex-unleashes-next-generation-lending-solutions-and-targets-20000-companies/</x:v>
       </x:c>
-      <x:c r="V46" s="14" t="e">
-        <x:f>HYPERLINK("https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/","crediblex.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/, friendlyName=crediblex.io</x:v>
-      </x:c>
-      <x:c r="W46" s="14" t="e">
-        <x:f>HYPERLINK("https://cdn.crediblex.io/docs/privacy-policy.pdf","cdn.crediblex.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cdn.crediblex.io/docs/privacy-policy.pdf, friendlyName=cdn.crediblex.io</x:v>
+      <x:c r="V46" s="14" t="str">
+        <x:v>https://crediblex.io/articles-published/crediblex-secures-55m-in-seed-funding-to-empower-smes/</x:v>
+      </x:c>
+      <x:c r="W46" s="14" t="str">
+        <x:v>https://cdn.crediblex.io/docs/privacy-policy.pdf</x:v>
       </x:c>
       <x:c r="X46" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y46" s="14" t="e">
-        <x:f>HYPERLINK("https://crediblex.io/company/contact-us/","crediblex.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://crediblex.io/company/contact-us/, friendlyName=crediblex.io</x:v>
+      <x:c r="Y46" s="14" t="str">
+        <x:v>https://crediblex.io/company/contact-us/</x:v>
       </x:c>
       <x:c r="Z46" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4675,9 +4475,8 @@
       <x:c r="I47" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J47" s="14" t="e">
-        <x:f>HYPERLINK("https://vuz.com","vuz.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://vuz.com, friendlyName=vuz.com</x:v>
+      <x:c r="J47" s="14" t="str">
+        <x:v>https://vuz.com</x:v>
       </x:c>
       <x:c r="K47" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4706,29 +4505,25 @@
       <x:c r="S47" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T47" s="14" t="e">
-        <x:f>HYPERLINK("https://www.vuz.com/","vuz.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.vuz.com/, friendlyName=vuz.com</x:v>
+      <x:c r="T47" s="14" t="str">
+        <x:v>https://www.vuz.com/</x:v>
       </x:c>
       <x:c r="U47" s="14" t="str">
         <x:v>https://techcrunch.com/2022/10/13/vuz-raises-20-million-to-scale-its-immersive-social-app/
 https://www.arabnews.com/business/uaes-social-app-vuz-raises-20m-series-b-to-fund-expansion-2180991
 https://www.prnewswire.com/ae/news-releases/vuz-the-leading-immersive-social-app-raises-20m-in-series-b-round-301649823.html</x:v>
       </x:c>
-      <x:c r="V47" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2022/10/13/vuz-raises-20-million-to-scale-its-immersive-social-app/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2022/10/13/vuz-raises-20-million-to-scale-its-immersive-social-app/, friendlyName=techcrunch.com</x:v>
-      </x:c>
-      <x:c r="W47" s="14" t="e">
-        <x:f>HYPERLINK("https://www.vuz.com/terms-conditions","vuz.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.vuz.com/terms-conditions, friendlyName=vuz.com</x:v>
+      <x:c r="V47" s="14" t="str">
+        <x:v>https://techcrunch.com/2022/10/13/vuz-raises-20-million-to-scale-its-immersive-social-app/</x:v>
+      </x:c>
+      <x:c r="W47" s="14" t="str">
+        <x:v>https://www.vuz.com/terms-conditions</x:v>
       </x:c>
       <x:c r="X47" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y47" s="14" t="e">
-        <x:f>HYPERLINK("https://www.vuz.com/","vuz.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.vuz.com/, friendlyName=vuz.com</x:v>
+      <x:c r="Y47" s="14" t="str">
+        <x:v>https://www.vuz.com/</x:v>
       </x:c>
       <x:c r="Z47" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4765,9 +4560,8 @@
       <x:c r="I48" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J48" s="14" t="e">
-        <x:f>HYPERLINK("https://nymcard.com","nymcard.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nymcard.com, friendlyName=nymcard.com</x:v>
+      <x:c r="J48" s="14" t="str">
+        <x:v>https://nymcard.com</x:v>
       </x:c>
       <x:c r="K48" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4794,9 +4588,8 @@
       <x:c r="S48" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.nymcard.com/ae/company/about","nymcard.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.nymcard.com/ae/company/about, friendlyName=nymcard.com</x:v>
+      <x:c r="T48" s="14" t="str">
+        <x:v>https://www.nymcard.com/ae/company/about</x:v>
       </x:c>
       <x:c r="U48" s="14" t="str">
         <x:v>https://www.nymcard.com/ae/company/about
@@ -4806,17 +4599,14 @@
       <x:c r="V48" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.nymcard.com/company/contact","nymcard.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.nymcard.com/company/contact, friendlyName=nymcard.com</x:v>
-      </x:c>
-      <x:c r="X48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.nymcard.com/ae/help-and-support","nymcard.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.nymcard.com/ae/help-and-support, friendlyName=nymcard.com</x:v>
-      </x:c>
-      <x:c r="Y48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.nymcard.com/ae/help-and-support","nymcard.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.nymcard.com/ae/help-and-support, friendlyName=nymcard.com</x:v>
+      <x:c r="W48" s="14" t="str">
+        <x:v>https://www.nymcard.com/company/contact</x:v>
+      </x:c>
+      <x:c r="X48" s="14" t="str">
+        <x:v>https://www.nymcard.com/ae/help-and-support</x:v>
+      </x:c>
+      <x:c r="Y48" s="14" t="str">
+        <x:v>https://www.nymcard.com/ae/help-and-support</x:v>
       </x:c>
       <x:c r="Z48" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -4853,9 +4643,8 @@
       <x:c r="I49" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="J49" s="14" t="e">
-        <x:f>HYPERLINK("https://leantech.me","leantech.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://leantech.me, friendlyName=leantech.me</x:v>
+      <x:c r="J49" s="14" t="str">
+        <x:v>https://leantech.me</x:v>
       </x:c>
       <x:c r="K49" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4882,9 +4671,8 @@
       <x:c r="S49" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T49" s="14" t="e">
-        <x:f>HYPERLINK("https://leantech.me/uae/en/company/about","leantech.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://leantech.me/uae/en/company/about, friendlyName=leantech.me</x:v>
+      <x:c r="T49" s="14" t="str">
+        <x:v>https://leantech.me/uae/en/company/about</x:v>
       </x:c>
       <x:c r="U49" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -4898,9 +4686,8 @@
       <x:c r="X49" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y49" s="14" t="e">
-        <x:f>HYPERLINK("https://www.leantech.me/ksa/en/contact","leantech.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.leantech.me/ksa/en/contact, friendlyName=leantech.me</x:v>
+      <x:c r="Y49" s="14" t="str">
+        <x:v>https://www.leantech.me/ksa/en/contact</x:v>
       </x:c>
       <x:c r="Z49" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -4937,9 +4724,8 @@
       <x:c r="I50" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J50" s="14" t="e">
-        <x:f>HYPERLINK("https://tarabut.com","tarabut.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarabut.com, friendlyName=tarabut.com</x:v>
+      <x:c r="J50" s="14" t="str">
+        <x:v>https://tarabut.com</x:v>
       </x:c>
       <x:c r="K50" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -4966,9 +4752,8 @@
       <x:c r="S50" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T50" s="14" t="e">
-        <x:f>HYPERLINK("https://prospeo.io/c/tarabut","prospeo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prospeo.io/c/tarabut, friendlyName=prospeo.io</x:v>
+      <x:c r="T50" s="14" t="str">
+        <x:v>https://prospeo.io/c/tarabut</x:v>
       </x:c>
       <x:c r="U50" s="14" t="str">
         <x:v>https://uaestartupmap.com/company/tarabut
@@ -4978,17 +4763,14 @@
       <x:c r="V50" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W50" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Tarabut-Holding-Limited-182233","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Tarabut-Holding-Limited-182233, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="X50" s="14" t="e">
-        <x:f>HYPERLINK("https://prospeo.io/c/tarabut","prospeo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prospeo.io/c/tarabut, friendlyName=prospeo.io</x:v>
-      </x:c>
-      <x:c r="Y50" s="14" t="e">
-        <x:f>HYPERLINK("https://tarabut.com/bh/contact","tarabut.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tarabut.com/bh/contact, friendlyName=tarabut.com</x:v>
+      <x:c r="W50" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Tarabut-Holding-Limited-182233</x:v>
+      </x:c>
+      <x:c r="X50" s="14" t="str">
+        <x:v>https://prospeo.io/c/tarabut</x:v>
+      </x:c>
+      <x:c r="Y50" s="14" t="str">
+        <x:v>https://tarabut.com/bh/contact</x:v>
       </x:c>
       <x:c r="Z50" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -5025,9 +4807,8 @@
       <x:c r="I51" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J51" s="14" t="e">
-        <x:f>HYPERLINK("https://ziina.com","ziina.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ziina.com, friendlyName=ziina.com</x:v>
+      <x:c r="J51" s="14" t="str">
+        <x:v>https://ziina.com</x:v>
       </x:c>
       <x:c r="K51" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5054,27 +4835,23 @@
       <x:c r="S51" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T51" s="14" t="e">
-        <x:f>HYPERLINK("https://ziina.com/contact","ziina.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ziina.com/contact, friendlyName=ziina.com</x:v>
+      <x:c r="T51" s="14" t="str">
+        <x:v>https://ziina.com/contact</x:v>
       </x:c>
       <x:c r="U51" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V51" s="14" t="e">
-        <x:f>HYPERLINK("https://ziina.com/about","ziina.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ziina.com/about, friendlyName=ziina.com</x:v>
-      </x:c>
-      <x:c r="W51" s="14" t="e">
-        <x:f>HYPERLINK("https://intercom.help/ziina-8bdf318a7612/en/articles/6847475-how-can-i-reach-out-to-customer-support","intercom.help")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://intercom.help/ziina-8bdf318a7612/en/articles/6847475-how-can-i-reach-out-to-customer-support, friendlyName=intercom.help</x:v>
+      <x:c r="V51" s="14" t="str">
+        <x:v>https://ziina.com/about</x:v>
+      </x:c>
+      <x:c r="W51" s="14" t="str">
+        <x:v>https://intercom.help/ziina-8bdf318a7612/en/articles/6847475-how-can-i-reach-out-to-customer-support</x:v>
       </x:c>
       <x:c r="X51" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y51" s="14" t="e">
-        <x:f>HYPERLINK("https://ziina.com/contact","ziina.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ziina.com/contact, friendlyName=ziina.com</x:v>
+      <x:c r="Y51" s="14" t="str">
+        <x:v>https://ziina.com/contact</x:v>
       </x:c>
       <x:c r="Z51" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5111,9 +4888,8 @@
       <x:c r="I52" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J52" s="14" t="e">
-        <x:f>HYPERLINK("https://zenda.com","zenda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zenda.com, friendlyName=zenda.com</x:v>
+      <x:c r="J52" s="14" t="str">
+        <x:v>https://zenda.com</x:v>
       </x:c>
       <x:c r="K52" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5140,9 +4916,8 @@
       <x:c r="S52" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T52" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zenda.com/contact","zenda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zenda.com/contact, friendlyName=zenda.com</x:v>
+      <x:c r="T52" s="14" t="str">
+        <x:v>https://www.zenda.com/contact</x:v>
       </x:c>
       <x:c r="U52" s="14" t="str">
         <x:v>https://prospeo.io/c/zenda
@@ -5152,16 +4927,14 @@
       <x:c r="V52" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W52" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zenda.com/parents","zenda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zenda.com/parents, friendlyName=zenda.com</x:v>
+      <x:c r="W52" s="14" t="str">
+        <x:v>https://www.zenda.com/parents</x:v>
       </x:c>
       <x:c r="X52" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y52" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zenda.com/contact","zenda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zenda.com/contact, friendlyName=zenda.com</x:v>
+      <x:c r="Y52" s="14" t="str">
+        <x:v>https://www.zenda.com/contact</x:v>
       </x:c>
       <x:c r="Z52" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5198,9 +4971,8 @@
       <x:c r="I53" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="J53" s="14" t="e">
-        <x:f>HYPERLINK("https://pyypl.com","pyypl.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pyypl.com, friendlyName=pyypl.com</x:v>
+      <x:c r="J53" s="14" t="str">
+        <x:v>https://pyypl.com</x:v>
       </x:c>
       <x:c r="K53" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5227,9 +4999,8 @@
       <x:c r="S53" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T53" s="14" t="e">
-        <x:f>HYPERLINK("https://beta1.decypha.com/en/company-list/Pyypl-230102","beta1.decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://beta1.decypha.com/en/company-list/Pyypl-230102, friendlyName=beta1.decypha.com</x:v>
+      <x:c r="T53" s="14" t="str">
+        <x:v>https://beta1.decypha.com/en/company-list/Pyypl-230102</x:v>
       </x:c>
       <x:c r="U53" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -5243,9 +5014,8 @@
       <x:c r="X53" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y53" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pyypl.com/contact","pyypl.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pyypl.com/contact, friendlyName=pyypl.com</x:v>
+      <x:c r="Y53" s="14" t="str">
+        <x:v>https://www.pyypl.com/contact</x:v>
       </x:c>
       <x:c r="Z53" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -5282,9 +5052,8 @@
       <x:c r="I54" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J54" s="14" t="e">
-        <x:f>HYPERLINK("https://yap.com","yap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yap.com, friendlyName=yap.com</x:v>
+      <x:c r="J54" s="14" t="str">
+        <x:v>https://yap.com</x:v>
       </x:c>
       <x:c r="K54" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5313,9 +5082,8 @@
       <x:c r="S54" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T54" s="14" t="e">
-        <x:f>HYPERLINK("https://yap.com/","yap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yap.com/, friendlyName=yap.com</x:v>
+      <x:c r="T54" s="14" t="str">
+        <x:v>https://yap.com/</x:v>
       </x:c>
       <x:c r="U54" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -5323,17 +5091,14 @@
       <x:c r="V54" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W54" s="14" t="e">
-        <x:f>HYPERLINK("https://zoftwarehub.com/en-ae/products/yap/overview","zoftwarehub.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zoftwarehub.com/en-ae/products/yap/overview, friendlyName=zoftwarehub.com</x:v>
-      </x:c>
-      <x:c r="X54" s="14" t="e">
-        <x:f>HYPERLINK("https://zoftwarehub.com/en-ae/products/yap/overview","zoftwarehub.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zoftwarehub.com/en-ae/products/yap/overview, friendlyName=zoftwarehub.com</x:v>
-      </x:c>
-      <x:c r="Y54" s="14" t="e">
-        <x:f>HYPERLINK("https://yap.com/","yap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yap.com/, friendlyName=yap.com</x:v>
+      <x:c r="W54" s="14" t="str">
+        <x:v>https://zoftwarehub.com/en-ae/products/yap/overview</x:v>
+      </x:c>
+      <x:c r="X54" s="14" t="str">
+        <x:v>https://zoftwarehub.com/en-ae/products/yap/overview</x:v>
+      </x:c>
+      <x:c r="Y54" s="14" t="str">
+        <x:v>https://yap.com/</x:v>
       </x:c>
       <x:c r="Z54" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -5370,9 +5135,8 @@
       <x:c r="I55" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J55" s="14" t="e">
-        <x:f>HYPERLINK("https://verofax.com","verofax.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://verofax.com, friendlyName=verofax.com</x:v>
+      <x:c r="J55" s="14" t="str">
+        <x:v>https://verofax.com</x:v>
       </x:c>
       <x:c r="K55" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5399,9 +5163,8 @@
       <x:c r="S55" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T55" s="14" t="e">
-        <x:f>HYPERLINK("https://verofax.com/privacy-policy/","verofax.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://verofax.com/privacy-policy/, friendlyName=verofax.com</x:v>
+      <x:c r="T55" s="14" t="str">
+        <x:v>https://verofax.com/privacy-policy/</x:v>
       </x:c>
       <x:c r="U55" s="14" t="str">
         <x:v>https://www.webnewswire.com/2023/11/23/verofax-is-selected-by-pwc-middle-east-among-top-future50-climatech-start-up/
@@ -5411,16 +5174,14 @@
       <x:c r="V55" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W55" s="14" t="e">
-        <x:f>HYPERLINK("https://verofax.com/contact-us/","verofax.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://verofax.com/contact-us/, friendlyName=verofax.com</x:v>
+      <x:c r="W55" s="14" t="str">
+        <x:v>https://verofax.com/contact-us/</x:v>
       </x:c>
       <x:c r="X55" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y55" s="14" t="e">
-        <x:f>HYPERLINK("https://verofax.com/contact-us/","verofax.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://verofax.com/contact-us/, friendlyName=verofax.com</x:v>
+      <x:c r="Y55" s="14" t="str">
+        <x:v>https://verofax.com/contact-us/</x:v>
       </x:c>
       <x:c r="Z55" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5457,9 +5218,8 @@
       <x:c r="I56" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J56" s="14" t="e">
-        <x:f>HYPERLINK("https://qashio.com","qashio.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qashio.com, friendlyName=qashio.com</x:v>
+      <x:c r="J56" s="14" t="str">
+        <x:v>https://qashio.com</x:v>
       </x:c>
       <x:c r="K56" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5486,30 +5246,25 @@
       <x:c r="S56" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.qashio.com/contact-us","qashio.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.qashio.com/contact-us, friendlyName=qashio.com</x:v>
+      <x:c r="T56" s="14" t="str">
+        <x:v>https://www.qashio.com/contact-us</x:v>
       </x:c>
       <x:c r="U56" s="14" t="str">
         <x:v>https://assets.entrepreneur.com/magazine/2022-08-entrepreneur-middle-east.pdf
 https://www.thenationalnews.com/business/start-ups/2022/11/22/uae-fintech-qashio-raises-10m-to-accelerate-expansion-into-saudi-arabia/
 https://uaestartupmap.com/company/qashio</x:v>
       </x:c>
-      <x:c r="V56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/start-ups/2022/11/22/uae-fintech-qashio-raises-10m-to-accelerate-expansion-into-saudi-arabia/","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/start-ups/2022/11/22/uae-fintech-qashio-raises-10m-to-accelerate-expansion-into-saudi-arabia/, friendlyName=thenationalnews.com</x:v>
-      </x:c>
-      <x:c r="W56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.qashio.com/contact-us","qashio.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.qashio.com/contact-us, friendlyName=qashio.com</x:v>
-      </x:c>
-      <x:c r="X56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.qashio.com/contact-us","qashio.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.qashio.com/contact-us, friendlyName=qashio.com</x:v>
-      </x:c>
-      <x:c r="Y56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.qashio.com/contact-us","qashio.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.qashio.com/contact-us, friendlyName=qashio.com</x:v>
+      <x:c r="V56" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/start-ups/2022/11/22/uae-fintech-qashio-raises-10m-to-accelerate-expansion-into-saudi-arabia/</x:v>
+      </x:c>
+      <x:c r="W56" s="14" t="str">
+        <x:v>https://www.qashio.com/contact-us</x:v>
+      </x:c>
+      <x:c r="X56" s="14" t="str">
+        <x:v>https://www.qashio.com/contact-us</x:v>
+      </x:c>
+      <x:c r="Y56" s="14" t="str">
+        <x:v>https://www.qashio.com/contact-us</x:v>
       </x:c>
       <x:c r="Z56" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5546,9 +5301,8 @@
       <x:c r="I57" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J57" s="14" t="e">
-        <x:f>HYPERLINK("https://qlub.io","qlub.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qlub.io, friendlyName=qlub.io</x:v>
+      <x:c r="J57" s="14" t="str">
+        <x:v>https://qlub.io</x:v>
       </x:c>
       <x:c r="K57" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5575,28 +5329,23 @@
       <x:c r="S57" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T57" s="14" t="e">
-        <x:f>HYPERLINK("https://qlub.io/ae/en?from=AppAgg.com","qlub.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qlub.io/ae/en?from=AppAgg.com, friendlyName=qlub.io</x:v>
+      <x:c r="T57" s="14" t="str">
+        <x:v>https://qlub.io/ae/en?from=AppAgg.com</x:v>
       </x:c>
       <x:c r="U57" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V57" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/index.php/en/2023/03/uae-fintech-qlub-raises-25-million","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/index.php/en/2023/03/uae-fintech-qlub-raises-25-million, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W57" s="14" t="e">
-        <x:f>HYPERLINK("https://qlub.io/ae/en?from=AppAgg.com","qlub.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qlub.io/ae/en?from=AppAgg.com, friendlyName=qlub.io</x:v>
-      </x:c>
-      <x:c r="X57" s="14" t="e">
-        <x:f>HYPERLINK("https://qlub.io/ae/en?from=AppAgg.com","qlub.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qlub.io/ae/en?from=AppAgg.com, friendlyName=qlub.io</x:v>
-      </x:c>
-      <x:c r="Y57" s="14" t="e">
-        <x:f>HYPERLINK("https://qlub.io/ae/en?from=AppAgg.com","qlub.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://qlub.io/ae/en?from=AppAgg.com, friendlyName=qlub.io</x:v>
+      <x:c r="V57" s="14" t="str">
+        <x:v>https://www.wamda.com/index.php/en/2023/03/uae-fintech-qlub-raises-25-million</x:v>
+      </x:c>
+      <x:c r="W57" s="14" t="str">
+        <x:v>https://qlub.io/ae/en?from=AppAgg.com</x:v>
+      </x:c>
+      <x:c r="X57" s="14" t="str">
+        <x:v>https://qlub.io/ae/en?from=AppAgg.com</x:v>
+      </x:c>
+      <x:c r="Y57" s="14" t="str">
+        <x:v>https://qlub.io/ae/en?from=AppAgg.com</x:v>
       </x:c>
       <x:c r="Z57" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5633,9 +5382,8 @@
       <x:c r="I58" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J58" s="14" t="e">
-        <x:f>HYPERLINK("https://mamopay.com","mamopay.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mamopay.com, friendlyName=mamopay.com</x:v>
+      <x:c r="J58" s="14" t="str">
+        <x:v>https://mamopay.com</x:v>
       </x:c>
       <x:c r="K58" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5662,29 +5410,25 @@
       <x:c r="S58" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T58" s="14" t="e">
-        <x:f>HYPERLINK("https://rakez.com/portals/0/download/mazeed_partners_list.pdf?ver=2020-10-14-044655-690","rakez.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://rakez.com/portals/0/download/mazeed_partners_list.pdf?ver=2020-10-14-044655-690, friendlyName=rakez.com</x:v>
+      <x:c r="T58" s="14" t="str">
+        <x:v>https://rakez.com/portals/0/download/mazeed_partners_list.pdf?ver=2020-10-14-044655-690</x:v>
       </x:c>
       <x:c r="U58" s="14" t="str">
         <x:v>https://www.mamopay.com/legal/privacy
 https://rakez.com/portals/0/download/mazeed_partners_list.pdf?ver=2020-10-14-044655-690
 https://rakez.com/Portals/0/Download/Mazeed_Partners_List.pdf%3Fver%3D2020-10-14-044655-690</x:v>
       </x:c>
-      <x:c r="V58" s="14" t="e">
-        <x:f>HYPERLINK("https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2025/mamo/","forbesmiddleeast.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2025/mamo/, friendlyName=forbesmiddleeast.com</x:v>
-      </x:c>
-      <x:c r="W58" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mamopay.com/contact","mamopay.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mamopay.com/contact, friendlyName=mamopay.com</x:v>
+      <x:c r="V58" s="14" t="str">
+        <x:v>https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2025/mamo/</x:v>
+      </x:c>
+      <x:c r="W58" s="14" t="str">
+        <x:v>https://www.mamopay.com/contact</x:v>
       </x:c>
       <x:c r="X58" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y58" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mamopay.com/contact","mamopay.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mamopay.com/contact, friendlyName=mamopay.com</x:v>
+      <x:c r="Y58" s="14" t="str">
+        <x:v>https://www.mamopay.com/contact</x:v>
       </x:c>
       <x:c r="Z58" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5721,9 +5465,8 @@
       <x:c r="I59" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J59" s="14" t="e">
-        <x:f>HYPERLINK("https://yallacompare.com","yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yallacompare.com, friendlyName=yallacompare.com</x:v>
+      <x:c r="J59" s="14" t="str">
+        <x:v>https://yallacompare.com</x:v>
       </x:c>
       <x:c r="K59" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5750,28 +5493,23 @@
       <x:c r="S59" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T59" s="14" t="e">
-        <x:f>HYPERLINK("https://app.yallacompare.com/insurance/uae/en/contact-us","app.yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://app.yallacompare.com/insurance/uae/en/contact-us, friendlyName=app.yallacompare.com</x:v>
+      <x:c r="T59" s="14" t="str">
+        <x:v>https://app.yallacompare.com/insurance/uae/en/contact-us</x:v>
       </x:c>
       <x:c r="U59" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V59" s="14" t="e">
-        <x:f>HYPERLINK("https://yc3.yallacompare.com/uae/en/about-us","yc3.yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yc3.yallacompare.com/uae/en/about-us, friendlyName=yc3.yallacompare.com</x:v>
-      </x:c>
-      <x:c r="W59" s="14" t="e">
-        <x:f>HYPERLINK("https://app.yallacompare.com/insurance/uae/en/contact-us","app.yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://app.yallacompare.com/insurance/uae/en/contact-us, friendlyName=app.yallacompare.com</x:v>
-      </x:c>
-      <x:c r="X59" s="14" t="e">
-        <x:f>HYPERLINK("https://yc3.yallacompare.com/uae/en/contact","yc3.yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yc3.yallacompare.com/uae/en/contact, friendlyName=yc3.yallacompare.com</x:v>
-      </x:c>
-      <x:c r="Y59" s="14" t="e">
-        <x:f>HYPERLINK("https://app.yallacompare.com/insurance/uae/en/contact-us","app.yallacompare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://app.yallacompare.com/insurance/uae/en/contact-us, friendlyName=app.yallacompare.com</x:v>
+      <x:c r="V59" s="14" t="str">
+        <x:v>https://yc3.yallacompare.com/uae/en/about-us</x:v>
+      </x:c>
+      <x:c r="W59" s="14" t="str">
+        <x:v>https://app.yallacompare.com/insurance/uae/en/contact-us</x:v>
+      </x:c>
+      <x:c r="X59" s="14" t="str">
+        <x:v>https://yc3.yallacompare.com/uae/en/contact</x:v>
+      </x:c>
+      <x:c r="Y59" s="14" t="str">
+        <x:v>https://app.yallacompare.com/insurance/uae/en/contact-us</x:v>
       </x:c>
       <x:c r="Z59" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5808,9 +5546,8 @@
       <x:c r="I60" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J60" s="14" t="e">
-        <x:f>HYPERLINK("https://bayzat.com","bayzat.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bayzat.com, friendlyName=bayzat.com</x:v>
+      <x:c r="J60" s="14" t="str">
+        <x:v>https://bayzat.com</x:v>
       </x:c>
       <x:c r="K60" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5837,9 +5574,8 @@
       <x:c r="S60" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T60" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bayzat.com/","bayzat.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bayzat.com/, friendlyName=bayzat.com</x:v>
+      <x:c r="T60" s="14" t="str">
+        <x:v>https://www.bayzat.com/</x:v>
       </x:c>
       <x:c r="U60" s="14" t="str">
         <x:v>https://assets.entrepreneur.com/magazine/2020-09-entrepreneur-middle-east.pdf
@@ -5849,17 +5585,14 @@
       <x:c r="V60" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W60" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bayzat.com/ksa/contact","bayzat.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bayzat.com/ksa/contact, friendlyName=bayzat.com</x:v>
-      </x:c>
-      <x:c r="X60" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bayzat.com/contact","bayzat.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bayzat.com/contact, friendlyName=bayzat.com</x:v>
-      </x:c>
-      <x:c r="Y60" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bayzat.com/contact","bayzat.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bayzat.com/contact, friendlyName=bayzat.com</x:v>
+      <x:c r="W60" s="14" t="str">
+        <x:v>https://www.bayzat.com/ksa/contact</x:v>
+      </x:c>
+      <x:c r="X60" s="14" t="str">
+        <x:v>https://www.bayzat.com/contact</x:v>
+      </x:c>
+      <x:c r="Y60" s="14" t="str">
+        <x:v>https://www.bayzat.com/contact</x:v>
       </x:c>
       <x:c r="Z60" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5896,9 +5629,8 @@
       <x:c r="I61" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J61" s="14" t="e">
-        <x:f>HYPERLINK("https://nowmoney.me","nowmoney.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nowmoney.me, friendlyName=nowmoney.me</x:v>
+      <x:c r="J61" s="14" t="str">
+        <x:v>https://nowmoney.me</x:v>
       </x:c>
       <x:c r="K61" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -5925,9 +5657,8 @@
       <x:c r="S61" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T61" s="14" t="e">
-        <x:f>HYPERLINK("https://assets.entrepreneur.com/magazine/2020-02-entrepreneur-middle-east.pdf","assets.entrepreneur.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://assets.entrepreneur.com/magazine/2020-02-entrepreneur-middle-east.pdf, friendlyName=assets.entrepreneur.com</x:v>
+      <x:c r="T61" s="14" t="str">
+        <x:v>https://assets.entrepreneur.com/magazine/2020-02-entrepreneur-middle-east.pdf</x:v>
       </x:c>
       <x:c r="U61" s="14" t="str">
         <x:v>https://www.wamda.com/wamda-investments/now-money-1
@@ -5937,17 +5668,14 @@
       <x:c r="V61" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W61" s="14" t="e">
-        <x:f>HYPERLINK("https://nowmoney.me/help/","nowmoney.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nowmoney.me/help/, friendlyName=nowmoney.me</x:v>
-      </x:c>
-      <x:c r="X61" s="14" t="e">
-        <x:f>HYPERLINK("https://nowmoney.me/contact/","nowmoney.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nowmoney.me/contact/, friendlyName=nowmoney.me</x:v>
-      </x:c>
-      <x:c r="Y61" s="14" t="e">
-        <x:f>HYPERLINK("https://nowmoney.me/contact/","nowmoney.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nowmoney.me/contact/, friendlyName=nowmoney.me</x:v>
+      <x:c r="W61" s="14" t="str">
+        <x:v>https://nowmoney.me/help/</x:v>
+      </x:c>
+      <x:c r="X61" s="14" t="str">
+        <x:v>https://nowmoney.me/contact/</x:v>
+      </x:c>
+      <x:c r="Y61" s="14" t="str">
+        <x:v>https://nowmoney.me/contact/</x:v>
       </x:c>
       <x:c r="Z61" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -5984,9 +5712,8 @@
       <x:c r="I62" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J62" s="14" t="e">
-        <x:f>HYPERLINK("https://klaim.ai","klaim.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klaim.ai, friendlyName=klaim.ai</x:v>
+      <x:c r="J62" s="14" t="str">
+        <x:v>https://klaim.ai</x:v>
       </x:c>
       <x:c r="K62" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6013,30 +5740,25 @@
       <x:c r="S62" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T62" s="14" t="e">
-        <x:f>HYPERLINK("https://klaim.com/contact","klaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klaim.com/contact, friendlyName=klaim.com</x:v>
+      <x:c r="T62" s="14" t="str">
+        <x:v>https://klaim.com/contact</x:v>
       </x:c>
       <x:c r="U62" s="14" t="str">
         <x:v>https://klaim.ai/
 https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/klaim-3/
 https://www.wamda.com/en/2021/03/klaim-raises-1-million-seed-round</x:v>
       </x:c>
-      <x:c r="V62" s="14" t="e">
-        <x:f>HYPERLINK("https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/klaim-3/","forbesmiddleeast.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/klaim-3/, friendlyName=forbesmiddleeast.com</x:v>
-      </x:c>
-      <x:c r="W62" s="14" t="e">
-        <x:f>HYPERLINK("https://klaim.com/contact","klaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klaim.com/contact, friendlyName=klaim.com</x:v>
-      </x:c>
-      <x:c r="X62" s="14" t="e">
-        <x:f>HYPERLINK("https://klaim.com/contact","klaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klaim.com/contact, friendlyName=klaim.com</x:v>
-      </x:c>
-      <x:c r="Y62" s="14" t="e">
-        <x:f>HYPERLINK("https://klaim.com/contact","klaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klaim.com/contact, friendlyName=klaim.com</x:v>
+      <x:c r="V62" s="14" t="str">
+        <x:v>https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/klaim-3/</x:v>
+      </x:c>
+      <x:c r="W62" s="14" t="str">
+        <x:v>https://klaim.com/contact</x:v>
+      </x:c>
+      <x:c r="X62" s="14" t="str">
+        <x:v>https://klaim.com/contact</x:v>
+      </x:c>
+      <x:c r="Y62" s="14" t="str">
+        <x:v>https://klaim.com/contact</x:v>
       </x:c>
       <x:c r="Z62" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6073,9 +5795,8 @@
       <x:c r="I63" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J63" s="14" t="e">
-        <x:f>HYPERLINK("https://lunedata.io","lunedata.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lunedata.io, friendlyName=lunedata.io</x:v>
+      <x:c r="J63" s="14" t="str">
+        <x:v>https://lunedata.io</x:v>
       </x:c>
       <x:c r="K63" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6102,9 +5823,8 @@
       <x:c r="S63" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T63" s="14" t="e">
-        <x:f>HYPERLINK("https://www.lunedata.io/contact","lunedata.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.lunedata.io/contact, friendlyName=lunedata.io</x:v>
+      <x:c r="T63" s="14" t="str">
+        <x:v>https://www.lunedata.io/contact</x:v>
       </x:c>
       <x:c r="U63" s="14" t="str">
         <x:v>https://www.flat6labs.com/wp-content/uploads/2022/11/Abu-Dhabi-_-Demo-Day-Printings-Investor-Brief-1.pdf
@@ -6114,16 +5834,14 @@
       <x:c r="V63" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W63" s="14" t="e">
-        <x:f>HYPERLINK("https://www.lunedata.io/contact","lunedata.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.lunedata.io/contact, friendlyName=lunedata.io</x:v>
+      <x:c r="W63" s="14" t="str">
+        <x:v>https://www.lunedata.io/contact</x:v>
       </x:c>
       <x:c r="X63" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y63" s="14" t="e">
-        <x:f>HYPERLINK("https://www.lunedata.io/contact","lunedata.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.lunedata.io/contact, friendlyName=lunedata.io</x:v>
+      <x:c r="Y63" s="14" t="str">
+        <x:v>https://www.lunedata.io/contact</x:v>
       </x:c>
       <x:c r="Z63" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6160,9 +5878,8 @@
       <x:c r="I64" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J64" s="14" t="e">
-        <x:f>HYPERLINK("https://wefortis.com","wefortis.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wefortis.com, friendlyName=wefortis.com</x:v>
+      <x:c r="J64" s="14" t="str">
+        <x:v>https://wefortis.com</x:v>
       </x:c>
       <x:c r="K64" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6189,9 +5906,8 @@
       <x:c r="S64" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T64" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Fortis-Digital-Solutions-DMCC-259824","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Fortis-Digital-Solutions-DMCC-259824, friendlyName=decypha.com</x:v>
+      <x:c r="T64" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Fortis-Digital-Solutions-DMCC-259824</x:v>
       </x:c>
       <x:c r="U64" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -6199,17 +5915,14 @@
       <x:c r="V64" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W64" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wefortis.com/contact","wefortis.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wefortis.com/contact, friendlyName=wefortis.com</x:v>
-      </x:c>
-      <x:c r="X64" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wefortis.com/legal/terms-and-conditions","wefortis.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wefortis.com/legal/terms-and-conditions, friendlyName=wefortis.com</x:v>
-      </x:c>
-      <x:c r="Y64" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wefortis.com/contact","wefortis.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wefortis.com/contact, friendlyName=wefortis.com</x:v>
+      <x:c r="W64" s="14" t="str">
+        <x:v>https://www.wefortis.com/contact</x:v>
+      </x:c>
+      <x:c r="X64" s="14" t="str">
+        <x:v>https://www.wefortis.com/legal/terms-and-conditions</x:v>
+      </x:c>
+      <x:c r="Y64" s="14" t="str">
+        <x:v>https://www.wefortis.com/contact</x:v>
       </x:c>
       <x:c r="Z64" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6246,9 +5959,8 @@
       <x:c r="I65" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="J65" s="14" t="e">
-        <x:f>HYPERLINK("https://ifarm.fi","ifarm.fi")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ifarm.fi, friendlyName=ifarm.fi</x:v>
+      <x:c r="J65" s="14" t="str">
+        <x:v>https://ifarm.fi</x:v>
       </x:c>
       <x:c r="K65" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6275,9 +5987,8 @@
       <x:c r="S65" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T65" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hub71.com/startups/ifarm","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hub71.com/startups/ifarm, friendlyName=hub71.com</x:v>
+      <x:c r="T65" s="14" t="str">
+        <x:v>https://www.hub71.com/startups/ifarm</x:v>
       </x:c>
       <x:c r="U65" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -6285,16 +5996,14 @@
       <x:c r="V65" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W65" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/ifarm-project","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/ifarm-project, friendlyName=crunchbase.com</x:v>
+      <x:c r="W65" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/ifarm-project</x:v>
       </x:c>
       <x:c r="X65" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y65" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hub71.com/startups/ifarm","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hub71.com/startups/ifarm, friendlyName=hub71.com</x:v>
+      <x:c r="Y65" s="14" t="str">
+        <x:v>https://www.hub71.com/startups/ifarm</x:v>
       </x:c>
       <x:c r="Z65" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -6331,9 +6040,8 @@
       <x:c r="I66" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J66" s="14" t="e">
-        <x:f>HYPERLINK("https://pureharvestfarms.com","pureharvestfarms.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pureharvestfarms.com, friendlyName=pureharvestfarms.com</x:v>
+      <x:c r="J66" s="14" t="str">
+        <x:v>https://pureharvestfarms.com</x:v>
       </x:c>
       <x:c r="K66" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6360,9 +6068,8 @@
       <x:c r="S66" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T66" s="14" t="e">
-        <x:f>HYPERLINK("https://www.internationalblueberry.org/assets/uploads/2020/01/United-Arab-Emitares-report-JAN.2020.pdf","internationalblueberry.org")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.internationalblueberry.org/assets/uploads/2020/01/United-Arab-Emitares-report-JAN.2020.pdf, friendlyName=internationalblueberry.org</x:v>
+      <x:c r="T66" s="14" t="str">
+        <x:v>https://www.internationalblueberry.org/assets/uploads/2020/01/United-Arab-Emitares-report-JAN.2020.pdf</x:v>
       </x:c>
       <x:c r="U66" s="14" t="str">
         <x:v>https://techcrunch.com/startup-battlefield/company/pure-harvest-smart-farms/
@@ -6372,16 +6079,14 @@
       <x:c r="V66" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W66" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pureharvestfarms.com/terms-and-conditions","pureharvestfarms.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pureharvestfarms.com/terms-and-conditions, friendlyName=pureharvestfarms.com</x:v>
+      <x:c r="W66" s="14" t="str">
+        <x:v>https://www.pureharvestfarms.com/terms-and-conditions</x:v>
       </x:c>
       <x:c r="X66" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y66" s="14" t="e">
-        <x:f>HYPERLINK("https://pureharvestfarms.com/investors","pureharvestfarms.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pureharvestfarms.com/investors, friendlyName=pureharvestfarms.com</x:v>
+      <x:c r="Y66" s="14" t="str">
+        <x:v>https://pureharvestfarms.com/investors</x:v>
       </x:c>
       <x:c r="Z66" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6418,9 +6123,8 @@
       <x:c r="I67" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J67" s="14" t="e">
-        <x:f>HYPERLINK("https://madarfarms.co","madarfarms.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://madarfarms.co, friendlyName=madarfarms.co</x:v>
+      <x:c r="J67" s="14" t="str">
+        <x:v>https://madarfarms.co</x:v>
       </x:c>
       <x:c r="K67" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6447,9 +6151,8 @@
       <x:c r="S67" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T67" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/366871/madar-farms","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/366871/madar-farms, friendlyName=yello.ae</x:v>
+      <x:c r="T67" s="14" t="str">
+        <x:v>https://www.yello.ae/company/366871/madar-farms</x:v>
       </x:c>
       <x:c r="U67" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -6457,17 +6160,14 @@
       <x:c r="V67" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W67" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/madar-farms","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/madar-farms, friendlyName=crunchbase.com</x:v>
-      </x:c>
-      <x:c r="X67" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/madar-farms","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/madar-farms, friendlyName=crunchbase.com</x:v>
-      </x:c>
-      <x:c r="Y67" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/366871/madar-farms","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/366871/madar-farms, friendlyName=yello.ae</x:v>
+      <x:c r="W67" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/madar-farms</x:v>
+      </x:c>
+      <x:c r="X67" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/madar-farms</x:v>
+      </x:c>
+      <x:c r="Y67" s="14" t="str">
+        <x:v>https://www.yello.ae/company/366871/madar-farms</x:v>
       </x:c>
       <x:c r="Z67" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -6504,9 +6204,8 @@
       <x:c r="I68" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="J68" s="14" t="e">
-        <x:f>HYPERLINK("https://moneyhash.io","moneyhash.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://moneyhash.io, friendlyName=moneyhash.io</x:v>
+      <x:c r="J68" s="14" t="str">
+        <x:v>https://moneyhash.io</x:v>
       </x:c>
       <x:c r="K68" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6533,29 +6232,25 @@
       <x:c r="S68" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T68" s="14" t="e">
-        <x:f>HYPERLINK("https://app.money2020middleeast.com/event/money20-20-middle-east-2026/exhibitor/RXhoaWJpdG9yXzI1MjA5MTA%3D","app.money2020middleeast.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://app.money2020middleeast.com/event/money20-20-middle-east-2026/exhibitor/RXhoaWJpdG9yXzI1MjA5MTA%3D, friendlyName=app.money2020middleeast.com</x:v>
+      <x:c r="T68" s="14" t="str">
+        <x:v>https://app.money2020middleeast.com/event/money20-20-middle-east-2026/exhibitor/RXhoaWJpdG9yXzI1MjA5MTA%3D</x:v>
       </x:c>
       <x:c r="U68" s="14" t="str">
         <x:v>https://moneyhash.io/blog/moneyhash-named-a-uae-future-100-recognized-for-driving-innovation-in-the-payments-sector
 https://www.crunchbase.com/organization/moneyhash
 https://moneyhash.io/blog/moneyhash-seed-fundraising-announcement</x:v>
       </x:c>
-      <x:c r="V68" s="14" t="e">
-        <x:f>HYPERLINK("https://moneyhash.io/blog/news-moneyhash-raises-six-figures","moneyhash.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://moneyhash.io/blog/news-moneyhash-raises-six-figures, friendlyName=moneyhash.io</x:v>
-      </x:c>
-      <x:c r="W68" s="14" t="e">
-        <x:f>HYPERLINK("https://moneyhash.io/?trk=public_post_main-feed-card_reshare-text","moneyhash.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://moneyhash.io/?trk=public_post_main-feed-card_reshare-text, friendlyName=moneyhash.io</x:v>
+      <x:c r="V68" s="14" t="str">
+        <x:v>https://moneyhash.io/blog/news-moneyhash-raises-six-figures</x:v>
+      </x:c>
+      <x:c r="W68" s="14" t="str">
+        <x:v>https://moneyhash.io/?trk=public_post_main-feed-card_reshare-text</x:v>
       </x:c>
       <x:c r="X68" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y68" s="14" t="e">
-        <x:f>HYPERLINK("https://www.moneyhash.io/","moneyhash.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.moneyhash.io/, friendlyName=moneyhash.io</x:v>
+      <x:c r="Y68" s="14" t="str">
+        <x:v>https://www.moneyhash.io/</x:v>
       </x:c>
       <x:c r="Z68" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6592,9 +6287,8 @@
       <x:c r="I69" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J69" s="14" t="e">
-        <x:f>HYPERLINK("https://dukkantek.com","dukkantek.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dukkantek.com, friendlyName=dukkantek.com</x:v>
+      <x:c r="J69" s="14" t="str">
+        <x:v>https://dukkantek.com</x:v>
       </x:c>
       <x:c r="K69" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6621,28 +6315,23 @@
       <x:c r="S69" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T69" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/368055/dukkantek","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/368055/dukkantek, friendlyName=yello.ae</x:v>
+      <x:c r="T69" s="14" t="str">
+        <x:v>https://www.yello.ae/company/368055/dukkantek</x:v>
       </x:c>
       <x:c r="U69" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V69" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/2022/03/08/uae-tech-start-up-dukkantek-raises-52-million/","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/2022/03/08/uae-tech-start-up-dukkantek-raises-52-million/, friendlyName=thenationalnews.com</x:v>
-      </x:c>
-      <x:c r="W69" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?hl=en&amp;id=com.dukkantek.bestprice","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?hl=en&amp;id=com.dukkantek.bestprice, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="X69" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/368055/dukkantek","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/368055/dukkantek, friendlyName=yello.ae</x:v>
-      </x:c>
-      <x:c r="Y69" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/368055/dukkantek","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/368055/dukkantek, friendlyName=yello.ae</x:v>
+      <x:c r="V69" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/2022/03/08/uae-tech-start-up-dukkantek-raises-52-million/</x:v>
+      </x:c>
+      <x:c r="W69" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?hl=en&amp;id=com.dukkantek.bestprice</x:v>
+      </x:c>
+      <x:c r="X69" s="14" t="str">
+        <x:v>https://www.yello.ae/company/368055/dukkantek</x:v>
+      </x:c>
+      <x:c r="Y69" s="14" t="str">
+        <x:v>https://www.yello.ae/company/368055/dukkantek</x:v>
       </x:c>
       <x:c r="Z69" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -6679,9 +6368,8 @@
       <x:c r="I70" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="J70" s="14" t="e">
-        <x:f>HYPERLINK("https://supy.io","supy.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://supy.io, friendlyName=supy.io</x:v>
+      <x:c r="J70" s="14" t="str">
+        <x:v>https://supy.io</x:v>
       </x:c>
       <x:c r="K70" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6708,30 +6396,25 @@
       <x:c r="S70" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T70" s="14" t="e">
-        <x:f>HYPERLINK("https://supy.io/contact-us","supy.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://supy.io/contact-us, friendlyName=supy.io</x:v>
+      <x:c r="T70" s="14" t="str">
+        <x:v>https://supy.io/contact-us</x:v>
       </x:c>
       <x:c r="U70" s="14" t="str">
         <x:v>https://www.wamda.com/2021/09/supy-raises-15-million-pre-seed-round
 https://www.wamda.com/index.php/en/2022/07/supy-raises-8-million-seed-round
 https://www.crunchbase.com/organization/supy-187e</x:v>
       </x:c>
-      <x:c r="V70" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/2021/09/supy-raises-15-million-pre-seed-round","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/2021/09/supy-raises-15-million-pre-seed-round, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W70" s="14" t="e">
-        <x:f>HYPERLINK("https://supy.io/contact-us","supy.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://supy.io/contact-us, friendlyName=supy.io</x:v>
-      </x:c>
-      <x:c r="X70" s="14" t="e">
-        <x:f>HYPERLINK("https://help.foodics.com/hc/en-us/articles/7487351748764-Supy","help.foodics.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.foodics.com/hc/en-us/articles/7487351748764-Supy, friendlyName=help.foodics.com</x:v>
-      </x:c>
-      <x:c r="Y70" s="14" t="e">
-        <x:f>HYPERLINK("https://supy.io/contact-us","supy.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://supy.io/contact-us, friendlyName=supy.io</x:v>
+      <x:c r="V70" s="14" t="str">
+        <x:v>https://www.wamda.com/2021/09/supy-raises-15-million-pre-seed-round</x:v>
+      </x:c>
+      <x:c r="W70" s="14" t="str">
+        <x:v>https://supy.io/contact-us</x:v>
+      </x:c>
+      <x:c r="X70" s="14" t="str">
+        <x:v>https://help.foodics.com/hc/en-us/articles/7487351748764-Supy</x:v>
+      </x:c>
+      <x:c r="Y70" s="14" t="str">
+        <x:v>https://supy.io/contact-us</x:v>
       </x:c>
       <x:c r="Z70" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6768,9 +6451,8 @@
       <x:c r="I71" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J71" s="14" t="e">
-        <x:f>HYPERLINK("https://grubtech.com","grubtech.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://grubtech.com, friendlyName=grubtech.com</x:v>
+      <x:c r="J71" s="14" t="str">
+        <x:v>https://grubtech.com</x:v>
       </x:c>
       <x:c r="K71" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6797,27 +6479,23 @@
       <x:c r="S71" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T71" s="14" t="e">
-        <x:f>HYPERLINK("https://www.doe.gov.ae/-/media/Project/ADCCI/ADCCI/Media-Center---Publications/Business-Voice/2021/bvjan2022en.pdf","doe.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.doe.gov.ae/-/media/Project/ADCCI/ADCCI/Media-Center---Publications/Business-Voice/2021/bvjan2022en.pdf, friendlyName=doe.gov.ae</x:v>
+      <x:c r="T71" s="14" t="str">
+        <x:v>https://www.doe.gov.ae/-/media/Project/ADCCI/ADCCI/Media-Center---Publications/Business-Voice/2021/bvjan2022en.pdf</x:v>
       </x:c>
       <x:c r="U71" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V71" s="14" t="e">
-        <x:f>HYPERLINK("https://www.prnewswire.com/news-releases/grubtech-raises-15-million-302155197.html","prnewswire.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.prnewswire.com/news-releases/grubtech-raises-15-million-302155197.html, friendlyName=prnewswire.com</x:v>
-      </x:c>
-      <x:c r="W71" s="14" t="e">
-        <x:f>HYPERLINK("https://grubtech.com/en/connect-with-us","grubtech.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://grubtech.com/en/connect-with-us, friendlyName=grubtech.com</x:v>
+      <x:c r="V71" s="14" t="str">
+        <x:v>https://www.prnewswire.com/news-releases/grubtech-raises-15-million-302155197.html</x:v>
+      </x:c>
+      <x:c r="W71" s="14" t="str">
+        <x:v>https://grubtech.com/en/connect-with-us</x:v>
       </x:c>
       <x:c r="X71" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y71" s="14" t="e">
-        <x:f>HYPERLINK("https://grubtech.com/en/connect-with-us","grubtech.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://grubtech.com/en/connect-with-us, friendlyName=grubtech.com</x:v>
+      <x:c r="Y71" s="14" t="str">
+        <x:v>https://grubtech.com/en/connect-with-us</x:v>
       </x:c>
       <x:c r="Z71" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6854,9 +6532,8 @@
       <x:c r="I72" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J72" s="14" t="e">
-        <x:f>HYPERLINK("https://zbooni.com","zbooni.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zbooni.com, friendlyName=zbooni.com</x:v>
+      <x:c r="J72" s="14" t="str">
+        <x:v>https://zbooni.com</x:v>
       </x:c>
       <x:c r="K72" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6883,30 +6560,25 @@
       <x:c r="S72" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T72" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415, friendlyName=thenationalnews.com</x:v>
+      <x:c r="T72" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415</x:v>
       </x:c>
       <x:c r="U72" s="14" t="str">
         <x:v>https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415
 https://www.thenationalnews.com/business/technology/uae-tech-start-up-zbooni-raises-5m-to-fund-expansion-1.1153944
 https://www.wamda.com/index.php/en/2021/09/zbooni-closes-95-million-series-round</x:v>
       </x:c>
-      <x:c r="V72" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415, friendlyName=thenationalnews.com</x:v>
-      </x:c>
-      <x:c r="W72" s="14" t="e">
-        <x:f>HYPERLINK("https://support.zbooni.com/","support.zbooni.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://support.zbooni.com/, friendlyName=support.zbooni.com</x:v>
-      </x:c>
-      <x:c r="X72" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zbooni.com/about-us/","zbooni.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zbooni.com/about-us/, friendlyName=zbooni.com</x:v>
-      </x:c>
-      <x:c r="Y72" s="14" t="e">
-        <x:f>HYPERLINK("https://support.zbooni.com/","support.zbooni.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://support.zbooni.com/, friendlyName=support.zbooni.com</x:v>
+      <x:c r="V72" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/technology/uae-e-commerce-app-zbooni-raises-1-1m-to-fund-expansion-1.876415</x:v>
+      </x:c>
+      <x:c r="W72" s="14" t="str">
+        <x:v>https://support.zbooni.com/</x:v>
+      </x:c>
+      <x:c r="X72" s="14" t="str">
+        <x:v>https://www.zbooni.com/about-us/</x:v>
+      </x:c>
+      <x:c r="Y72" s="14" t="str">
+        <x:v>https://support.zbooni.com/</x:v>
       </x:c>
       <x:c r="Z72" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -6943,9 +6615,8 @@
       <x:c r="I73" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J73" s="14" t="e">
-        <x:f>HYPERLINK("https://quiqup.com","quiqup.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://quiqup.com, friendlyName=quiqup.com</x:v>
+      <x:c r="J73" s="14" t="str">
+        <x:v>https://quiqup.com</x:v>
       </x:c>
       <x:c r="K73" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -6972,9 +6643,8 @@
       <x:c r="S73" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T73" s="14" t="e">
-        <x:f>HYPERLINK("https://www.quiqup.com/contact-international","quiqup.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.quiqup.com/contact-international, friendlyName=quiqup.com</x:v>
+      <x:c r="T73" s="14" t="str">
+        <x:v>https://www.quiqup.com/contact-international</x:v>
       </x:c>
       <x:c r="U73" s="14" t="str">
         <x:v>https://www.thenationalnews.com/business/start-ups/2022/08/22/generation-start-up-how-ai-powered-quiqup-is-revolutionising-the-uaes-q-commerce-market/
@@ -6984,16 +6654,14 @@
       <x:c r="V73" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W73" s="14" t="e">
-        <x:f>HYPERLINK("https://www.quiqup.com/contact-international","quiqup.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.quiqup.com/contact-international, friendlyName=quiqup.com</x:v>
+      <x:c r="W73" s="14" t="str">
+        <x:v>https://www.quiqup.com/contact-international</x:v>
       </x:c>
       <x:c r="X73" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y73" s="14" t="e">
-        <x:f>HYPERLINK("https://www.quiqup.com/contact-international","quiqup.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.quiqup.com/contact-international, friendlyName=quiqup.com</x:v>
+      <x:c r="Y73" s="14" t="str">
+        <x:v>https://www.quiqup.com/contact-international</x:v>
       </x:c>
       <x:c r="Z73" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7030,9 +6698,8 @@
       <x:c r="I74" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J74" s="14" t="e">
-        <x:f>HYPERLINK("https://shipa.com","shipa.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://shipa.com, friendlyName=shipa.com</x:v>
+      <x:c r="J74" s="14" t="str">
+        <x:v>https://shipa.com</x:v>
       </x:c>
       <x:c r="K74" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7061,9 +6728,8 @@
       <x:c r="S74" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T74" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Shipa-Delivery-Services-L-L-C-237900","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Shipa-Delivery-Services-L-L-C-237900, friendlyName=decypha.com</x:v>
+      <x:c r="T74" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Shipa-Delivery-Services-L-L-C-237900</x:v>
       </x:c>
       <x:c r="U74" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -7071,17 +6737,14 @@
       <x:c r="V74" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W74" s="14" t="e">
-        <x:f>HYPERLINK("https://prod-shipa-cms-media.s3.eu-west-1.amazonaws.com/ebook_moving_online_en_6f130d0606.pdf","prod-shipa-cms-media.s3.eu-west-1.amazonaws.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prod-shipa-cms-media.s3.eu-west-1.amazonaws.com/ebook_moving_online_en_6f130d0606.pdf, friendlyName=prod-shipa-cms-media.s3.eu-west-1.amazonaws.com</x:v>
-      </x:c>
-      <x:c r="X74" s="14" t="e">
-        <x:f>HYPERLINK("https://shipa.com/help-center/","shipa.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://shipa.com/help-center/, friendlyName=shipa.com</x:v>
-      </x:c>
-      <x:c r="Y74" s="14" t="e">
-        <x:f>HYPERLINK("https://shipa.com/help-center/","shipa.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://shipa.com/help-center/, friendlyName=shipa.com</x:v>
+      <x:c r="W74" s="14" t="str">
+        <x:v>https://prod-shipa-cms-media.s3.eu-west-1.amazonaws.com/ebook_moving_online_en_6f130d0606.pdf</x:v>
+      </x:c>
+      <x:c r="X74" s="14" t="str">
+        <x:v>https://shipa.com/help-center/</x:v>
+      </x:c>
+      <x:c r="Y74" s="14" t="str">
+        <x:v>https://shipa.com/help-center/</x:v>
       </x:c>
       <x:c r="Z74" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -7118,9 +6781,8 @@
       <x:c r="I75" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J75" s="14" t="e">
-        <x:f>HYPERLINK("https://imile.com","imile.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://imile.com, friendlyName=imile.com</x:v>
+      <x:c r="J75" s="14" t="str">
+        <x:v>https://imile.com</x:v>
       </x:c>
       <x:c r="K75" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7147,30 +6809,25 @@
       <x:c r="S75" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/369070/imile","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/369070/imile, friendlyName=yello.ae</x:v>
+      <x:c r="T75" s="14" t="str">
+        <x:v>https://www.yello.ae/company/369070/imile</x:v>
       </x:c>
       <x:c r="U75" s="14" t="str">
         <x:v>https://www.forbesmiddleeast.com/lists/the-middle-easts-50-most-funded-startups/imile/
 https://www.imile.com/AE-en/AboutUs
 https://www.imile.com/IT-en/blogDetails?searchTitle=iMile-expands-its-Middle-East-footprint-to-meet-consumer-demands%2F</x:v>
       </x:c>
-      <x:c r="V75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.forbesmiddleeast.com/lists/the-middle-easts-50-most-funded-startups/imile/","forbesmiddleeast.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.forbesmiddleeast.com/lists/the-middle-easts-50-most-funded-startups/imile/, friendlyName=forbesmiddleeast.com</x:v>
-      </x:c>
-      <x:c r="W75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.imile.com/undefined/CustomerService/OfficeLocations","imile.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.imile.com/undefined/CustomerService/OfficeLocations, friendlyName=imile.com</x:v>
-      </x:c>
-      <x:c r="X75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.imile.com/undefined/CustomerService/OfficeLocations","imile.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.imile.com/undefined/CustomerService/OfficeLocations, friendlyName=imile.com</x:v>
-      </x:c>
-      <x:c r="Y75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.imile.com/undefined/CustomerService/OfficeLocations","imile.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.imile.com/undefined/CustomerService/OfficeLocations, friendlyName=imile.com</x:v>
+      <x:c r="V75" s="14" t="str">
+        <x:v>https://www.forbesmiddleeast.com/lists/the-middle-easts-50-most-funded-startups/imile/</x:v>
+      </x:c>
+      <x:c r="W75" s="14" t="str">
+        <x:v>https://www.imile.com/undefined/CustomerService/OfficeLocations</x:v>
+      </x:c>
+      <x:c r="X75" s="14" t="str">
+        <x:v>https://www.imile.com/undefined/CustomerService/OfficeLocations</x:v>
+      </x:c>
+      <x:c r="Y75" s="14" t="str">
+        <x:v>https://www.imile.com/undefined/CustomerService/OfficeLocations</x:v>
       </x:c>
       <x:c r="Z75" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7207,9 +6864,8 @@
       <x:c r="I76" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J76" s="14" t="e">
-        <x:f>HYPERLINK("https://trukker.com","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://trukker.com, friendlyName=trukker.com</x:v>
+      <x:c r="J76" s="14" t="str">
+        <x:v>https://trukker.com</x:v>
       </x:c>
       <x:c r="K76" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7236,28 +6892,23 @@
       <x:c r="S76" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T76" s="14" t="e">
-        <x:f>HYPERLINK("https://www.trukker.com/tc","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.trukker.com/tc, friendlyName=trukker.com</x:v>
+      <x:c r="T76" s="14" t="str">
+        <x:v>https://www.trukker.com/tc</x:v>
       </x:c>
       <x:c r="U76" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V76" s="14" t="e">
-        <x:f>HYPERLINK("https://trukker.com/assets/img/TruKKer-Brochure.pdf","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://trukker.com/assets/img/TruKKer-Brochure.pdf, friendlyName=trukker.com</x:v>
-      </x:c>
-      <x:c r="W76" s="14" t="e">
-        <x:f>HYPERLINK("https://www.trukker.com/privacy","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.trukker.com/privacy, friendlyName=trukker.com</x:v>
-      </x:c>
-      <x:c r="X76" s="14" t="e">
-        <x:f>HYPERLINK("https://www.trukker.com/contact-us","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.trukker.com/contact-us, friendlyName=trukker.com</x:v>
-      </x:c>
-      <x:c r="Y76" s="14" t="e">
-        <x:f>HYPERLINK("https://www.trukker.com/contact-us","trukker.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.trukker.com/contact-us, friendlyName=trukker.com</x:v>
+      <x:c r="V76" s="14" t="str">
+        <x:v>https://trukker.com/assets/img/TruKKer-Brochure.pdf</x:v>
+      </x:c>
+      <x:c r="W76" s="14" t="str">
+        <x:v>https://www.trukker.com/privacy</x:v>
+      </x:c>
+      <x:c r="X76" s="14" t="str">
+        <x:v>https://www.trukker.com/contact-us</x:v>
+      </x:c>
+      <x:c r="Y76" s="14" t="str">
+        <x:v>https://www.trukker.com/contact-us</x:v>
       </x:c>
       <x:c r="Z76" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7294,9 +6945,8 @@
       <x:c r="I77" s="6" t="str">
         <x:v>بريد عمل منشور لمسؤول بالجهة</x:v>
       </x:c>
-      <x:c r="J77" s="14" t="e">
-        <x:f>HYPERLINK("https://fero.ai","fero.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fero.ai, friendlyName=fero.ai</x:v>
+      <x:c r="J77" s="14" t="str">
+        <x:v>https://fero.ai</x:v>
       </x:c>
       <x:c r="K77" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7323,9 +6973,8 @@
       <x:c r="S77" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.fero.ai/about_us","fero.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.fero.ai/about_us, friendlyName=fero.ai</x:v>
+      <x:c r="T77" s="14" t="str">
+        <x:v>https://www.fero.ai/about_us</x:v>
       </x:c>
       <x:c r="U77" s="14" t="str">
         <x:v>https://www.fero.ai/about_us
@@ -7334,17 +6983,14 @@
       <x:c r="V77" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W77" s="14" t="e">
-        <x:f>HYPERLINK("https://ferogpt.feroai.com/contact_us","ferogpt.feroai.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ferogpt.feroai.com/contact_us, friendlyName=ferogpt.feroai.com</x:v>
-      </x:c>
-      <x:c r="X77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.fero.ai/contact_us","fero.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.fero.ai/contact_us, friendlyName=fero.ai</x:v>
-      </x:c>
-      <x:c r="Y77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.fero.ai/contact_us","fero.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.fero.ai/contact_us, friendlyName=fero.ai</x:v>
+      <x:c r="W77" s="14" t="str">
+        <x:v>https://ferogpt.feroai.com/contact_us</x:v>
+      </x:c>
+      <x:c r="X77" s="14" t="str">
+        <x:v>https://www.fero.ai/contact_us</x:v>
+      </x:c>
+      <x:c r="Y77" s="14" t="str">
+        <x:v>https://www.fero.ai/contact_us</x:v>
       </x:c>
       <x:c r="Z77" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7381,9 +7027,8 @@
       <x:c r="I78" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="J78" s="14" t="e">
-        <x:f>HYPERLINK("https://lyveglobal.com","lyveglobal.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lyveglobal.com, friendlyName=lyveglobal.com</x:v>
+      <x:c r="J78" s="14" t="str">
+        <x:v>https://lyveglobal.com</x:v>
       </x:c>
       <x:c r="K78" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7412,9 +7057,8 @@
       <x:c r="S78" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T78" s="14" t="e">
-        <x:f>HYPERLINK("https://lyveglobal.com/contact/","lyveglobal.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lyveglobal.com/contact/, friendlyName=lyveglobal.com</x:v>
+      <x:c r="T78" s="14" t="str">
+        <x:v>https://lyveglobal.com/contact/</x:v>
       </x:c>
       <x:c r="U78" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -7422,17 +7066,14 @@
       <x:c r="V78" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W78" s="14" t="e">
-        <x:f>HYPERLINK("https://lyveglobal.com/contact/","lyveglobal.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lyveglobal.com/contact/, friendlyName=lyveglobal.com</x:v>
-      </x:c>
-      <x:c r="X78" s="14" t="e">
-        <x:f>HYPERLINK("https://lyveglobal.com/contact/","lyveglobal.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lyveglobal.com/contact/, friendlyName=lyveglobal.com</x:v>
-      </x:c>
-      <x:c r="Y78" s="14" t="e">
-        <x:f>HYPERLINK("https://lyveglobal.com/contact/","lyveglobal.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lyveglobal.com/contact/, friendlyName=lyveglobal.com</x:v>
+      <x:c r="W78" s="14" t="str">
+        <x:v>https://lyveglobal.com/contact/</x:v>
+      </x:c>
+      <x:c r="X78" s="14" t="str">
+        <x:v>https://lyveglobal.com/contact/</x:v>
+      </x:c>
+      <x:c r="Y78" s="14" t="str">
+        <x:v>https://lyveglobal.com/contact/</x:v>
       </x:c>
       <x:c r="Z78" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7469,9 +7110,8 @@
       <x:c r="I79" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J79" s="14" t="e">
-        <x:f>HYPERLINK("https://jeebly.com","jeebly.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jeebly.com, friendlyName=jeebly.com</x:v>
+      <x:c r="J79" s="14" t="str">
+        <x:v>https://jeebly.com</x:v>
       </x:c>
       <x:c r="K79" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7500,9 +7140,8 @@
       <x:c r="S79" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T79" s="14" t="e">
-        <x:f>HYPERLINK("https://jeebly.com/faq/","jeebly.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jeebly.com/faq/, friendlyName=jeebly.com</x:v>
+      <x:c r="T79" s="14" t="str">
+        <x:v>https://jeebly.com/faq/</x:v>
       </x:c>
       <x:c r="U79" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/jeebly
@@ -7512,17 +7151,14 @@
       <x:c r="V79" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W79" s="14" t="e">
-        <x:f>HYPERLINK("https://jeebly.com/faq/","jeebly.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jeebly.com/faq/, friendlyName=jeebly.com</x:v>
-      </x:c>
-      <x:c r="X79" s="14" t="e">
-        <x:f>HYPERLINK("https://jeebly.com/faq/","jeebly.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jeebly.com/faq/, friendlyName=jeebly.com</x:v>
-      </x:c>
-      <x:c r="Y79" s="14" t="e">
-        <x:f>HYPERLINK("https://jeebly.com/faq/","jeebly.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jeebly.com/faq/, friendlyName=jeebly.com</x:v>
+      <x:c r="W79" s="14" t="str">
+        <x:v>https://jeebly.com/faq/</x:v>
+      </x:c>
+      <x:c r="X79" s="14" t="str">
+        <x:v>https://jeebly.com/faq/</x:v>
+      </x:c>
+      <x:c r="Y79" s="14" t="str">
+        <x:v>https://jeebly.com/faq/</x:v>
       </x:c>
       <x:c r="Z79" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7559,9 +7195,8 @@
       <x:c r="I80" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J80" s="14" t="e">
-        <x:f>HYPERLINK("https://sarwa.co","sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sarwa.co, friendlyName=sarwa.co</x:v>
+      <x:c r="J80" s="14" t="str">
+        <x:v>https://sarwa.co</x:v>
       </x:c>
       <x:c r="K80" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7588,30 +7223,25 @@
       <x:c r="S80" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T80" s="14" t="e">
-        <x:f>HYPERLINK("https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/","blog.sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/, friendlyName=blog.sarwa.co</x:v>
+      <x:c r="T80" s="14" t="str">
+        <x:v>https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/</x:v>
       </x:c>
       <x:c r="U80" s="14" t="str">
         <x:v>https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/
 https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2026/sarwa/
 https://blog.sarwa.co/press-release-uae-based-fintech-startup-sarwa-raises-84m-series-a-funding-round-led-by-kipco</x:v>
       </x:c>
-      <x:c r="V80" s="14" t="e">
-        <x:f>HYPERLINK("https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/","blog.sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/, friendlyName=blog.sarwa.co</x:v>
-      </x:c>
-      <x:c r="W80" s="14" t="e">
-        <x:f>HYPERLINK("https://help.sarwa.co/hc/en-us/requests/new","help.sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.sarwa.co/hc/en-us/requests/new, friendlyName=help.sarwa.co</x:v>
-      </x:c>
-      <x:c r="X80" s="14" t="e">
-        <x:f>HYPERLINK("https://help.sarwa.co/hc/en-us/requests/new","help.sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.sarwa.co/hc/en-us/requests/new, friendlyName=help.sarwa.co</x:v>
-      </x:c>
-      <x:c r="Y80" s="14" t="e">
-        <x:f>HYPERLINK("https://help.sarwa.co/hc/en-us/articles/13712637877661-How-do-I-update-my-contact-details-and-personal-information","help.sarwa.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.sarwa.co/hc/en-us/articles/13712637877661-How-do-I-update-my-contact-details-and-personal-information, friendlyName=help.sarwa.co</x:v>
+      <x:c r="V80" s="14" t="str">
+        <x:v>https://blog.sarwa.co/what-is-sarwa-and-how-does-it-work/</x:v>
+      </x:c>
+      <x:c r="W80" s="14" t="str">
+        <x:v>https://help.sarwa.co/hc/en-us/requests/new</x:v>
+      </x:c>
+      <x:c r="X80" s="14" t="str">
+        <x:v>https://help.sarwa.co/hc/en-us/requests/new</x:v>
+      </x:c>
+      <x:c r="Y80" s="14" t="str">
+        <x:v>https://help.sarwa.co/hc/en-us/articles/13712637877661-How-do-I-update-my-contact-details-and-personal-information</x:v>
       </x:c>
       <x:c r="Z80" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7648,9 +7278,8 @@
       <x:c r="I81" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J81" s="14" t="e">
-        <x:f>HYPERLINK("https://letswork.io","letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://letswork.io, friendlyName=letswork.io</x:v>
+      <x:c r="J81" s="14" t="str">
+        <x:v>https://letswork.io</x:v>
       </x:c>
       <x:c r="K81" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7677,30 +7306,25 @@
       <x:c r="S81" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.letswork.io/about","letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.letswork.io/about, friendlyName=letswork.io</x:v>
+      <x:c r="T81" s="14" t="str">
+        <x:v>https://www.letswork.io/about</x:v>
       </x:c>
       <x:c r="U81" s="14" t="str">
         <x:v>https://www.letswork.io/about
 https://www.crunchbase.com/organization/letswork
 https://www.wamda.com/index.php/en/2022/12/letswork-raises-2-1-million-seed-expands-saudi-arabia</x:v>
       </x:c>
-      <x:c r="V81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.letswork.io/about","letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.letswork.io/about, friendlyName=letswork.io</x:v>
-      </x:c>
-      <x:c r="W81" s="14" t="e">
-        <x:f>HYPERLINK("https://prod-web.letswork.io/contact","prod-web.letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prod-web.letswork.io/contact, friendlyName=prod-web.letswork.io</x:v>
-      </x:c>
-      <x:c r="X81" s="14" t="e">
-        <x:f>HYPERLINK("https://prod-web.letswork.io/contact","prod-web.letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prod-web.letswork.io/contact, friendlyName=prod-web.letswork.io</x:v>
-      </x:c>
-      <x:c r="Y81" s="14" t="e">
-        <x:f>HYPERLINK("https://prod-web.letswork.io/contact","prod-web.letswork.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prod-web.letswork.io/contact, friendlyName=prod-web.letswork.io</x:v>
+      <x:c r="V81" s="14" t="str">
+        <x:v>https://www.letswork.io/about</x:v>
+      </x:c>
+      <x:c r="W81" s="14" t="str">
+        <x:v>https://prod-web.letswork.io/contact</x:v>
+      </x:c>
+      <x:c r="X81" s="14" t="str">
+        <x:v>https://prod-web.letswork.io/contact</x:v>
+      </x:c>
+      <x:c r="Y81" s="14" t="str">
+        <x:v>https://prod-web.letswork.io/contact</x:v>
       </x:c>
       <x:c r="Z81" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7737,9 +7361,8 @@
       <x:c r="I82" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J82" s="14" t="e">
-        <x:f>HYPERLINK("https://hotdesk.com","hotdesk.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hotdesk.com, friendlyName=hotdesk.com</x:v>
+      <x:c r="J82" s="14" t="str">
+        <x:v>https://hotdesk.com</x:v>
       </x:c>
       <x:c r="K82" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7766,28 +7389,23 @@
       <x:c r="S82" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.streetinsider.com/Press%2BReleases/Hotdesk%2BAnnounces%2BExpansion%2Bto%2BMore%2BThan%2B2%2C500%2BWorkspaces%2BWorldwide/26668372.html","streetinsider.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.streetinsider.com/Press%2BReleases/Hotdesk%2BAnnounces%2BExpansion%2Bto%2BMore%2BThan%2B2%2C500%2BWorkspaces%2BWorldwide/26668372.html, friendlyName=streetinsider.com</x:v>
+      <x:c r="T82" s="14" t="str">
+        <x:v>https://www.streetinsider.com/Press%2BReleases/Hotdesk%2BAnnounces%2BExpansion%2Bto%2BMore%2BThan%2B2%2C500%2BWorkspaces%2BWorldwide/26668372.html</x:v>
       </x:c>
       <x:c r="U82" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V82" s="14" t="e">
-        <x:f>HYPERLINK("https://gulfstartupmap.com/startups/hotdesk","gulfstartupmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://gulfstartupmap.com/startups/hotdesk, friendlyName=gulfstartupmap.com</x:v>
-      </x:c>
-      <x:c r="W82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.provenexpert.com/en-us/hotdesk/","provenexpert.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.provenexpert.com/en-us/hotdesk/, friendlyName=provenexpert.com</x:v>
-      </x:c>
-      <x:c r="X82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hotdesk.com/contact?lang=en","hotdesk.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hotdesk.com/contact?lang=en, friendlyName=hotdesk.com</x:v>
-      </x:c>
-      <x:c r="Y82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hotdesk.com/contact?lang=en","hotdesk.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hotdesk.com/contact?lang=en, friendlyName=hotdesk.com</x:v>
+      <x:c r="V82" s="14" t="str">
+        <x:v>https://gulfstartupmap.com/startups/hotdesk</x:v>
+      </x:c>
+      <x:c r="W82" s="14" t="str">
+        <x:v>https://www.provenexpert.com/en-us/hotdesk/</x:v>
+      </x:c>
+      <x:c r="X82" s="14" t="str">
+        <x:v>https://www.hotdesk.com/contact?lang=en</x:v>
+      </x:c>
+      <x:c r="Y82" s="14" t="str">
+        <x:v>https://www.hotdesk.com/contact?lang=en</x:v>
       </x:c>
       <x:c r="Z82" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -7824,9 +7442,8 @@
       <x:c r="I83" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J83" s="14" t="e">
-        <x:f>HYPERLINK("https://tenderd.com","tenderd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tenderd.com, friendlyName=tenderd.com</x:v>
+      <x:c r="J83" s="14" t="str">
+        <x:v>https://tenderd.com</x:v>
       </x:c>
       <x:c r="K83" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -7853,9 +7470,8 @@
       <x:c r="S83" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T83" s="14" t="e">
-        <x:f>HYPERLINK("https://tenderd.com/contact-us-old/","tenderd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tenderd.com/contact-us-old/, friendlyName=tenderd.com</x:v>
+      <x:c r="T83" s="14" t="str">
+        <x:v>https://tenderd.com/contact-us-old/</x:v>
       </x:c>
       <x:c r="U83" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -7863,17 +7479,14 @@
       <x:c r="V83" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W83" s="14" t="e">
-        <x:f>HYPERLINK("https://tenderd.com/contact-us-old/","tenderd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tenderd.com/contact-us-old/, friendlyName=tenderd.com</x:v>
-      </x:c>
-      <x:c r="X83" s="14" t="e">
-        <x:f>HYPERLINK("https://tenderd.com/contact-us-old/","tenderd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tenderd.com/contact-us-old/, friendlyName=tenderd.com</x:v>
-      </x:c>
-      <x:c r="Y83" s="14" t="e">
-        <x:f>HYPERLINK("https://tenderd.com/contact-us-old/","tenderd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tenderd.com/contact-us-old/, friendlyName=tenderd.com</x:v>
+      <x:c r="W83" s="14" t="str">
+        <x:v>https://tenderd.com/contact-us-old/</x:v>
+      </x:c>
+      <x:c r="X83" s="14" t="str">
+        <x:v>https://tenderd.com/contact-us-old/</x:v>
+      </x:c>
+      <x:c r="Y83" s="14" t="str">
+        <x:v>https://tenderd.com/contact-us-old/</x:v>
       </x:c>
       <x:c r="Z83" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7910,9 +7523,8 @@
       <x:c r="I84" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J84" s="14" t="e">
-        <x:f>HYPERLINK("https://cafu.com","cafu.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cafu.com, friendlyName=cafu.com</x:v>
+      <x:c r="J84" s="14" t="str">
+        <x:v>https://cafu.com</x:v>
       </x:c>
       <x:c r="K84" s="6" t="str">
         <x:v>تقرير سابق عن بحث تمويل؛ الحالي غير مؤكد</x:v>
@@ -7939,9 +7551,8 @@
       <x:c r="S84" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T84" s="14" t="e">
-        <x:f>HYPERLINK("https://dayofdubai.com/directory/cafu-fuel-delivery-app-on-demand-fuel-delivery/","dayofdubai.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dayofdubai.com/directory/cafu-fuel-delivery-app-on-demand-fuel-delivery/, friendlyName=dayofdubai.com</x:v>
+      <x:c r="T84" s="14" t="str">
+        <x:v>https://dayofdubai.com/directory/cafu-fuel-delivery-app-on-demand-fuel-delivery/</x:v>
       </x:c>
       <x:c r="U84" s="14" t="str">
         <x:v>https://gulfnews.com/business/markets/dubai-fuel-delivery-startup-cafu-explores-first-stake-sale-1.500104324
@@ -7951,17 +7562,14 @@
       <x:c r="V84" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cafu.com/terms","cafu.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cafu.com/terms, friendlyName=cafu.com</x:v>
-      </x:c>
-      <x:c r="X84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bayut.com/mybayut/complete-guide-using-cafu-dubai/","bayut.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bayut.com/mybayut/complete-guide-using-cafu-dubai/, friendlyName=bayut.com</x:v>
-      </x:c>
-      <x:c r="Y84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cafu.com/terms","cafu.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cafu.com/terms, friendlyName=cafu.com</x:v>
+      <x:c r="W84" s="14" t="str">
+        <x:v>https://www.cafu.com/terms</x:v>
+      </x:c>
+      <x:c r="X84" s="14" t="str">
+        <x:v>https://www.bayut.com/mybayut/complete-guide-using-cafu-dubai/</x:v>
+      </x:c>
+      <x:c r="Y84" s="14" t="str">
+        <x:v>https://www.cafu.com/terms</x:v>
       </x:c>
       <x:c r="Z84" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -7998,9 +7606,8 @@
       <x:c r="I85" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J85" s="14" t="e">
-        <x:f>HYPERLINK("https://udrive.ae","udrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://udrive.ae, friendlyName=udrive.ae</x:v>
+      <x:c r="J85" s="14" t="str">
+        <x:v>https://udrive.ae</x:v>
       </x:c>
       <x:c r="K85" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8027,30 +7634,25 @@
       <x:c r="S85" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/2022/02/udrive-raises-5million","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/2022/02/udrive-raises-5million, friendlyName=wamda.com</x:v>
+      <x:c r="T85" s="14" t="str">
+        <x:v>https://www.wamda.com/2022/02/udrive-raises-5million</x:v>
       </x:c>
       <x:c r="U85" s="14" t="str">
         <x:v>https://www.tahawultech.com/wp-content/uploads/2015/09/cnme_20230828-1.pdf
 https://www.wamda.com/2022/02/udrive-raises-5million
 https://www.thenationalnews.com/business/technology/generation-start-up-udrive-revs-up-again-after-pandemic-induced-speed-bump-1.1165093</x:v>
       </x:c>
-      <x:c r="V85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/2022/02/udrive-raises-5million","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/2022/02/udrive-raises-5million, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W85" s="14" t="e">
-        <x:f>HYPERLINK("https://subscribe.udrive.ae/contact-us","subscribe.udrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://subscribe.udrive.ae/contact-us, friendlyName=subscribe.udrive.ae</x:v>
-      </x:c>
-      <x:c r="X85" s="14" t="e">
-        <x:f>HYPERLINK("https://support.udrive.ae/en/support/solutions/articles/77000576651-how-do-i-resubmit-my-documents-","support.udrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://support.udrive.ae/en/support/solutions/articles/77000576651-how-do-i-resubmit-my-documents-, friendlyName=support.udrive.ae</x:v>
-      </x:c>
-      <x:c r="Y85" s="14" t="e">
-        <x:f>HYPERLINK("https://udrive.ae/contact-us","udrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://udrive.ae/contact-us, friendlyName=udrive.ae</x:v>
+      <x:c r="V85" s="14" t="str">
+        <x:v>https://www.wamda.com/2022/02/udrive-raises-5million</x:v>
+      </x:c>
+      <x:c r="W85" s="14" t="str">
+        <x:v>https://subscribe.udrive.ae/contact-us</x:v>
+      </x:c>
+      <x:c r="X85" s="14" t="str">
+        <x:v>https://support.udrive.ae/en/support/solutions/articles/77000576651-how-do-i-resubmit-my-documents-</x:v>
+      </x:c>
+      <x:c r="Y85" s="14" t="str">
+        <x:v>https://udrive.ae/contact-us</x:v>
       </x:c>
       <x:c r="Z85" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8087,9 +7689,8 @@
       <x:c r="I86" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J86" s="14" t="e">
-        <x:f>HYPERLINK("https://ekar.me","ekar.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ekar.me, friendlyName=ekar.me</x:v>
+      <x:c r="J86" s="14" t="str">
+        <x:v>https://ekar.me</x:v>
       </x:c>
       <x:c r="K86" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8116,30 +7717,25 @@
       <x:c r="S86" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/ekar","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/ekar, friendlyName=crunchbase.com</x:v>
+      <x:c r="T86" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/ekar</x:v>
       </x:c>
       <x:c r="U86" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/ekar
 https://www.thenationalnews.com/business/technology/generation-start-up-uae-s-ekar-drives-car-share-sector-at-top-speed-1.893936
 https://yourstory.com/companies/ekar</x:v>
       </x:c>
-      <x:c r="V86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/technology/generation-start-up-uae-s-ekar-drives-car-share-sector-at-top-speed-1.893936","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/technology/generation-start-up-uae-s-ekar-drives-car-share-sector-at-top-speed-1.893936, friendlyName=thenationalnews.com</x:v>
-      </x:c>
-      <x:c r="W86" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?hl=en_NZ&amp;id=ae.ekar","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?hl=en_NZ&amp;id=ae.ekar, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="X86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaireview.ae/listing/ekar/","dubaireview.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaireview.ae/listing/ekar/, friendlyName=dubaireview.ae</x:v>
-      </x:c>
-      <x:c r="Y86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/ekar","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/ekar, friendlyName=crunchbase.com</x:v>
+      <x:c r="V86" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/technology/generation-start-up-uae-s-ekar-drives-car-share-sector-at-top-speed-1.893936</x:v>
+      </x:c>
+      <x:c r="W86" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?hl=en_NZ&amp;id=ae.ekar</x:v>
+      </x:c>
+      <x:c r="X86" s="14" t="str">
+        <x:v>https://www.dubaireview.ae/listing/ekar/</x:v>
+      </x:c>
+      <x:c r="Y86" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/ekar</x:v>
       </x:c>
       <x:c r="Z86" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -8176,9 +7772,8 @@
       <x:c r="I87" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J87" s="14" t="e">
-        <x:f>HYPERLINK("https://pemo.io","pemo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pemo.io, friendlyName=pemo.io</x:v>
+      <x:c r="J87" s="14" t="str">
+        <x:v>https://pemo.io</x:v>
       </x:c>
       <x:c r="K87" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8207,29 +7802,25 @@
       <x:c r="S87" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T87" s="14" t="e">
-        <x:f>HYPERLINK("https://help.pemo.io/en/articles/11675029-answers-to-your-pemo-questions","help.pemo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.pemo.io/en/articles/11675029-answers-to-your-pemo-questions, friendlyName=help.pemo.io</x:v>
+      <x:c r="T87" s="14" t="str">
+        <x:v>https://help.pemo.io/en/articles/11675029-answers-to-your-pemo-questions</x:v>
       </x:c>
       <x:c r="U87" s="14" t="str">
         <x:v>https://www.businessoutreach.in/wp-content/uploads/2024/11/November-Funding-Report-Dubai.pdf
 https://www.pemo.io/press-rooms/pemo-hits-aed-1-4bn-in-transactions-secures-6-5m-in-pre-series-a-led-by-augmentum-fintech-and-shorooq
 https://www.forbesmiddleeast.com/lists/the-middle-easts-fintech-50-2025/pemo/</x:v>
       </x:c>
-      <x:c r="V87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pemo.io/press-rooms/pemo-hits-aed-1-4bn-in-transactions-secures-6-5m-in-pre-series-a-led-by-augmentum-fintech-and-shorooq","pemo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pemo.io/press-rooms/pemo-hits-aed-1-4bn-in-transactions-secures-6-5m-in-pre-series-a-led-by-augmentum-fintech-and-shorooq, friendlyName=pemo.io</x:v>
-      </x:c>
-      <x:c r="W87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pemo.io/ar-ae/contact-us","pemo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pemo.io/ar-ae/contact-us, friendlyName=pemo.io</x:v>
+      <x:c r="V87" s="14" t="str">
+        <x:v>https://www.pemo.io/press-rooms/pemo-hits-aed-1-4bn-in-transactions-secures-6-5m-in-pre-series-a-led-by-augmentum-fintech-and-shorooq</x:v>
+      </x:c>
+      <x:c r="W87" s="14" t="str">
+        <x:v>https://www.pemo.io/ar-ae/contact-us</x:v>
       </x:c>
       <x:c r="X87" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.pemo.io/ar-ae/contact-us","pemo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.pemo.io/ar-ae/contact-us, friendlyName=pemo.io</x:v>
+      <x:c r="Y87" s="14" t="str">
+        <x:v>https://www.pemo.io/ar-ae/contact-us</x:v>
       </x:c>
       <x:c r="Z87" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8266,9 +7857,8 @@
       <x:c r="I88" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J88" s="14" t="e">
-        <x:f>HYPERLINK("https://selfdrive.ae","selfdrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://selfdrive.ae, friendlyName=selfdrive.ae</x:v>
+      <x:c r="J88" s="14" t="str">
+        <x:v>https://selfdrive.ae</x:v>
       </x:c>
       <x:c r="K88" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8295,9 +7885,8 @@
       <x:c r="S88" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.selfdrive.ae/contactus.php","selfdrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.selfdrive.ae/contactus.php, friendlyName=selfdrive.ae</x:v>
+      <x:c r="T88" s="14" t="str">
+        <x:v>https://www.selfdrive.ae/contactus.php</x:v>
       </x:c>
       <x:c r="U88" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/selfdrive-ae
@@ -8307,17 +7896,14 @@
       <x:c r="V88" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.selfdrive.ae/contactus.php","selfdrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.selfdrive.ae/contactus.php, friendlyName=selfdrive.ae</x:v>
-      </x:c>
-      <x:c r="X88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.selfdrive.ae/contactus.php","selfdrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.selfdrive.ae/contactus.php, friendlyName=selfdrive.ae</x:v>
-      </x:c>
-      <x:c r="Y88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.selfdrive.ae/contactus.php","selfdrive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.selfdrive.ae/contactus.php, friendlyName=selfdrive.ae</x:v>
+      <x:c r="W88" s="14" t="str">
+        <x:v>https://www.selfdrive.ae/contactus.php</x:v>
+      </x:c>
+      <x:c r="X88" s="14" t="str">
+        <x:v>https://www.selfdrive.ae/contactus.php</x:v>
+      </x:c>
+      <x:c r="Y88" s="14" t="str">
+        <x:v>https://www.selfdrive.ae/contactus.php</x:v>
       </x:c>
       <x:c r="Z88" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8354,9 +7940,8 @@
       <x:c r="I89" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="J89" s="14" t="e">
-        <x:f>HYPERLINK("https://algodriven.co","algodriven.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://algodriven.co, friendlyName=algodriven.co</x:v>
+      <x:c r="J89" s="14" t="str">
+        <x:v>https://algodriven.co</x:v>
       </x:c>
       <x:c r="K89" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8383,29 +7968,25 @@
       <x:c r="S89" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T89" s="14" t="e">
-        <x:f>HYPERLINK("https://algodriven.co/contact-us/","algodriven.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://algodriven.co/contact-us/, friendlyName=algodriven.co</x:v>
+      <x:c r="T89" s="14" t="str">
+        <x:v>https://algodriven.co/contact-us/</x:v>
       </x:c>
       <x:c r="U89" s="14" t="str">
         <x:v>https://www.gulf-insider.com/wp-content/uploads/2024/08/APRIL-2024.pdf
 https://www.thenationalnews.com/business/start-ups/2021/10/07/uae-tech-start-up-algodriven-raises-2m-in-series-a-funding/
 https://dtec.ae/ventures/news/magnitt-uae-based-automotive-data-platform-algodriven-raises-2m-series-a/</x:v>
       </x:c>
-      <x:c r="V89" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/start-ups/2021/10/07/uae-tech-start-up-algodriven-raises-2m-in-series-a-funding/","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/start-ups/2021/10/07/uae-tech-start-up-algodriven-raises-2m-in-series-a-funding/, friendlyName=thenationalnews.com</x:v>
-      </x:c>
-      <x:c r="W89" s="14" t="e">
-        <x:f>HYPERLINK("https://algodriven.co/contact-us/","algodriven.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://algodriven.co/contact-us/, friendlyName=algodriven.co</x:v>
+      <x:c r="V89" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/start-ups/2021/10/07/uae-tech-start-up-algodriven-raises-2m-in-series-a-funding/</x:v>
+      </x:c>
+      <x:c r="W89" s="14" t="str">
+        <x:v>https://algodriven.co/contact-us/</x:v>
       </x:c>
       <x:c r="X89" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y89" s="14" t="e">
-        <x:f>HYPERLINK("https://algodriven.co/contact-us/","algodriven.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://algodriven.co/contact-us/, friendlyName=algodriven.co</x:v>
+      <x:c r="Y89" s="14" t="str">
+        <x:v>https://algodriven.co/contact-us/</x:v>
       </x:c>
       <x:c r="Z89" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8442,9 +8023,8 @@
       <x:c r="I90" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J90" s="14" t="e">
-        <x:f>HYPERLINK("https://carasti.com","carasti.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://carasti.com, friendlyName=carasti.com</x:v>
+      <x:c r="J90" s="14" t="str">
+        <x:v>https://carasti.com</x:v>
       </x:c>
       <x:c r="K90" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8471,28 +8051,23 @@
       <x:c r="S90" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T90" s="14" t="e">
-        <x:f>HYPERLINK("https://prospeo.io/c/carasti-car-subscriptions","prospeo.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prospeo.io/c/carasti-car-subscriptions, friendlyName=prospeo.io</x:v>
+      <x:c r="T90" s="14" t="str">
+        <x:v>https://prospeo.io/c/carasti-car-subscriptions</x:v>
       </x:c>
       <x:c r="U90" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V90" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/index.php/2021/04/carasti-raises-3-million-pre-series","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/index.php/2021/04/carasti-raises-3-million-pre-series, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W90" s="14" t="e">
-        <x:f>HYPERLINK("https://carasti.com/AE/en/contact-us","carasti.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://carasti.com/AE/en/contact-us, friendlyName=carasti.com</x:v>
-      </x:c>
-      <x:c r="X90" s="14" t="e">
-        <x:f>HYPERLINK("https://carasti.com/AE/en/contact-us","carasti.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://carasti.com/AE/en/contact-us, friendlyName=carasti.com</x:v>
-      </x:c>
-      <x:c r="Y90" s="14" t="e">
-        <x:f>HYPERLINK("https://carasti.com/AE/en/contact-us","carasti.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://carasti.com/AE/en/contact-us, friendlyName=carasti.com</x:v>
+      <x:c r="V90" s="14" t="str">
+        <x:v>https://www.wamda.com/index.php/2021/04/carasti-raises-3-million-pre-series</x:v>
+      </x:c>
+      <x:c r="W90" s="14" t="str">
+        <x:v>https://carasti.com/AE/en/contact-us</x:v>
+      </x:c>
+      <x:c r="X90" s="14" t="str">
+        <x:v>https://carasti.com/AE/en/contact-us</x:v>
+      </x:c>
+      <x:c r="Y90" s="14" t="str">
+        <x:v>https://carasti.com/AE/en/contact-us</x:v>
       </x:c>
       <x:c r="Z90" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8529,9 +8104,8 @@
       <x:c r="I91" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J91" s="14" t="e">
-        <x:f>HYPERLINK("https://invygo.com","invygo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://invygo.com, friendlyName=invygo.com</x:v>
+      <x:c r="J91" s="14" t="str">
+        <x:v>https://invygo.com</x:v>
       </x:c>
       <x:c r="K91" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8558,30 +8132,25 @@
       <x:c r="S91" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.invygo.com/en-ae/tc-mobile","invygo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.invygo.com/en-ae/tc-mobile, friendlyName=invygo.com</x:v>
+      <x:c r="T91" s="14" t="str">
+        <x:v>https://www.invygo.com/en-ae/tc-mobile</x:v>
       </x:c>
       <x:c r="U91" s="14" t="str">
         <x:v>https://techcrunch.com/2022/10/31/invygo-raises-10m-to-make-long-term-car-subscription-a-breeze/
 https://www.thenationalnews.com/business/technology/generation-start-up-invygo-offers-drivers-a-car-without-the-commitment-1.962867
 https://www.thenationalnews.com/business/2021/08/17/middle-east-car-subscription-start-up-invygo-raises-19m/</x:v>
       </x:c>
-      <x:c r="V91" s="14" t="e">
-        <x:f>HYPERLINK("https://techcrunch.com/2022/10/31/invygo-raises-10m-to-make-long-term-car-subscription-a-breeze/","techcrunch.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://techcrunch.com/2022/10/31/invygo-raises-10m-to-make-long-term-car-subscription-a-breeze/, friendlyName=techcrunch.com</x:v>
-      </x:c>
-      <x:c r="W91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.invygo.com/en-ae/tc-mobile","invygo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.invygo.com/en-ae/tc-mobile, friendlyName=invygo.com</x:v>
-      </x:c>
-      <x:c r="X91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Invygo-Tech-FZ-L-L-C-194620","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Invygo-Tech-FZ-L-L-C-194620, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="Y91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.invygo.com/en-ae/tc-mobile","invygo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.invygo.com/en-ae/tc-mobile, friendlyName=invygo.com</x:v>
+      <x:c r="V91" s="14" t="str">
+        <x:v>https://techcrunch.com/2022/10/31/invygo-raises-10m-to-make-long-term-car-subscription-a-breeze/</x:v>
+      </x:c>
+      <x:c r="W91" s="14" t="str">
+        <x:v>https://www.invygo.com/en-ae/tc-mobile</x:v>
+      </x:c>
+      <x:c r="X91" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Invygo-Tech-FZ-L-L-C-194620</x:v>
+      </x:c>
+      <x:c r="Y91" s="14" t="str">
+        <x:v>https://www.invygo.com/en-ae/tc-mobile</x:v>
       </x:c>
       <x:c r="Z91" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8618,9 +8187,8 @@
       <x:c r="I92" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J92" s="14" t="e">
-        <x:f>HYPERLINK("https://yallamarket.ae","yallamarket.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yallamarket.ae, friendlyName=yallamarket.ae</x:v>
+      <x:c r="J92" s="14" t="str">
+        <x:v>https://yallamarket.ae</x:v>
       </x:c>
       <x:c r="K92" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8647,30 +8215,25 @@
       <x:c r="S92" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T92" s="14" t="e">
-        <x:f>HYPERLINK("https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery","apprecs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery, friendlyName=apprecs.com</x:v>
+      <x:c r="T92" s="14" t="str">
+        <x:v>https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery</x:v>
       </x:c>
       <x:c r="U92" s="14" t="str">
         <x:v>https://www.wamda.com/index.php/2022/02/yallamarket-raises-2-million-bridge-round
 https://app.dealroom.co/companies/yallamarket
 https://www.wamda.com/index.php/en/2021/11/yallamarket-2-3-million-pre-seed-rapid-rise-quick-commerce</x:v>
       </x:c>
-      <x:c r="V92" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/index.php/2022/02/yallamarket-raises-2-million-bridge-round","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/index.php/2022/02/yallamarket-raises-2-million-bridge-round, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W92" s="14" t="e">
-        <x:f>HYPERLINK("https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery","apprecs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery, friendlyName=apprecs.com</x:v>
-      </x:c>
-      <x:c r="X92" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/368060/yallamarket?amp=1","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/368060/yallamarket?amp=1, friendlyName=yello.ae</x:v>
-      </x:c>
-      <x:c r="Y92" s="14" t="e">
-        <x:f>HYPERLINK("https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery","apprecs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery, friendlyName=apprecs.com</x:v>
+      <x:c r="V92" s="14" t="str">
+        <x:v>https://www.wamda.com/index.php/2022/02/yallamarket-raises-2-million-bridge-round</x:v>
+      </x:c>
+      <x:c r="W92" s="14" t="str">
+        <x:v>https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery</x:v>
+      </x:c>
+      <x:c r="X92" s="14" t="str">
+        <x:v>https://www.yello.ae/company/368060/yallamarket?amp=1</x:v>
+      </x:c>
+      <x:c r="Y92" s="14" t="str">
+        <x:v>https://apprecs.com/android/ae.yallamart.userapp/yallamarket-grocery-delivery</x:v>
       </x:c>
       <x:c r="Z92" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -8707,9 +8270,8 @@
       <x:c r="I93" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J93" s="14" t="e">
-        <x:f>HYPERLINK("https://cartlow.com","cartlow.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cartlow.com, friendlyName=cartlow.com</x:v>
+      <x:c r="J93" s="14" t="str">
+        <x:v>https://cartlow.com</x:v>
       </x:c>
       <x:c r="K93" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8736,9 +8298,8 @@
       <x:c r="S93" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T93" s="14" t="e">
-        <x:f>HYPERLINK("https://assets.entrepreneur.com/magazine/2022-08-entrepreneur-middle-east.pdf","assets.entrepreneur.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://assets.entrepreneur.com/magazine/2022-08-entrepreneur-middle-east.pdf, friendlyName=assets.entrepreneur.com</x:v>
+      <x:c r="T93" s="14" t="str">
+        <x:v>https://assets.entrepreneur.com/magazine/2022-08-entrepreneur-middle-east.pdf</x:v>
       </x:c>
       <x:c r="U93" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -8746,17 +8307,14 @@
       <x:c r="V93" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W93" s="14" t="e">
-        <x:f>HYPERLINK("https://cartlow.com/seller/contact-us","cartlow.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cartlow.com/seller/contact-us, friendlyName=cartlow.com</x:v>
-      </x:c>
-      <x:c r="X93" s="14" t="e">
-        <x:f>HYPERLINK("https://sustainability.cartlow.com/contact-us","sustainability.cartlow.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sustainability.cartlow.com/contact-us, friendlyName=sustainability.cartlow.com</x:v>
-      </x:c>
-      <x:c r="Y93" s="14" t="e">
-        <x:f>HYPERLINK("https://sustainability.cartlow.com/contact-us","sustainability.cartlow.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sustainability.cartlow.com/contact-us, friendlyName=sustainability.cartlow.com</x:v>
+      <x:c r="W93" s="14" t="str">
+        <x:v>https://cartlow.com/seller/contact-us</x:v>
+      </x:c>
+      <x:c r="X93" s="14" t="str">
+        <x:v>https://sustainability.cartlow.com/contact-us</x:v>
+      </x:c>
+      <x:c r="Y93" s="14" t="str">
+        <x:v>https://sustainability.cartlow.com/contact-us</x:v>
       </x:c>
       <x:c r="Z93" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8793,9 +8351,8 @@
       <x:c r="I94" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J94" s="14" t="e">
-        <x:f>HYPERLINK("https://thegivingmovement.com","thegivingmovement.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://thegivingmovement.com, friendlyName=thegivingmovement.com</x:v>
+      <x:c r="J94" s="14" t="str">
+        <x:v>https://thegivingmovement.com</x:v>
       </x:c>
       <x:c r="K94" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8822,30 +8379,25 @@
       <x:c r="S94" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T94" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ecohubmap.com/company/business/the-giving-movement/5g4nklihbcnog","ecohubmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ecohubmap.com/company/business/the-giving-movement/5g4nklihbcnog, friendlyName=ecohubmap.com</x:v>
+      <x:c r="T94" s="14" t="str">
+        <x:v>https://www.ecohubmap.com/company/business/the-giving-movement/5g4nklihbcnog</x:v>
       </x:c>
       <x:c r="U94" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/the-giving-movement
 https://www.ecohubmap.com/company/business/the-giving-movement/5g4nklihbcnog
 https://padlet-uploads.storage.googleapis.com/1097180305/f9f22c335b5ce9bdd4e29b98915dc400/BlankmanMagazineConcept.pdf</x:v>
       </x:c>
-      <x:c r="V94" s="14" t="e">
-        <x:f>HYPERLINK("https://gulfbusiness.com/en/2022/uae/uae-brand-the-giving-movement-raises-15m-in-series-a-round/","gulfbusiness.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://gulfbusiness.com/en/2022/uae/uae-brand-the-giving-movement-raises-15m-in-series-a-round/, friendlyName=gulfbusiness.com</x:v>
-      </x:c>
-      <x:c r="W94" s="14" t="e">
-        <x:f>HYPERLINK("https://thegivingmovement.com/pages/contact-us","thegivingmovement.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://thegivingmovement.com/pages/contact-us, friendlyName=thegivingmovement.com</x:v>
-      </x:c>
-      <x:c r="X94" s="14" t="e">
-        <x:f>HYPERLINK("https://thegivingmovement.com/pages/contact-us","thegivingmovement.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://thegivingmovement.com/pages/contact-us, friendlyName=thegivingmovement.com</x:v>
-      </x:c>
-      <x:c r="Y94" s="14" t="e">
-        <x:f>HYPERLINK("https://thegivingmovement.com/pages/contact-us","thegivingmovement.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://thegivingmovement.com/pages/contact-us, friendlyName=thegivingmovement.com</x:v>
+      <x:c r="V94" s="14" t="str">
+        <x:v>https://gulfbusiness.com/en/2022/uae/uae-brand-the-giving-movement-raises-15m-in-series-a-round/</x:v>
+      </x:c>
+      <x:c r="W94" s="14" t="str">
+        <x:v>https://thegivingmovement.com/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="X94" s="14" t="str">
+        <x:v>https://thegivingmovement.com/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="Y94" s="14" t="str">
+        <x:v>https://thegivingmovement.com/pages/contact-us</x:v>
       </x:c>
       <x:c r="Z94" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8882,9 +8434,8 @@
       <x:c r="I95" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J95" s="14" t="e">
-        <x:f>HYPERLINK("https://calo.app","calo.app")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://calo.app, friendlyName=calo.app</x:v>
+      <x:c r="J95" s="14" t="str">
+        <x:v>https://calo.app</x:v>
       </x:c>
       <x:c r="K95" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -8913,29 +8464,25 @@
       <x:c r="S95" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T95" s="14" t="e">
-        <x:f>HYPERLINK("https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf","assets.entrepreneur.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf, friendlyName=assets.entrepreneur.com</x:v>
+      <x:c r="T95" s="14" t="str">
+        <x:v>https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf</x:v>
       </x:c>
       <x:c r="U95" s="14" t="str">
         <x:v>https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf
 https://www.khwarizmivc.com/calo
 https://www.crunchbase.com/organization/calo</x:v>
       </x:c>
-      <x:c r="V95" s="14" t="e">
-        <x:f>HYPERLINK("https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf","assets.entrepreneur.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf, friendlyName=assets.entrepreneur.com</x:v>
-      </x:c>
-      <x:c r="W95" s="14" t="e">
-        <x:f>HYPERLINK("https://calo.app/en-om/privacy-policy","calo.app")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://calo.app/en-om/privacy-policy, friendlyName=calo.app</x:v>
+      <x:c r="V95" s="14" t="str">
+        <x:v>https://assets.entrepreneur.com/magazine/2022-01-entrepreneur-middle-east.pdf</x:v>
+      </x:c>
+      <x:c r="W95" s="14" t="str">
+        <x:v>https://calo.app/en-om/privacy-policy</x:v>
       </x:c>
       <x:c r="X95" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y95" s="14" t="e">
-        <x:f>HYPERLINK("https://calo.app/en/business/contact","calo.app")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://calo.app/en/business/contact, friendlyName=calo.app</x:v>
+      <x:c r="Y95" s="14" t="str">
+        <x:v>https://calo.app/en/business/contact</x:v>
       </x:c>
       <x:c r="Z95" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -8972,9 +8519,8 @@
       <x:c r="I96" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J96" s="14" t="e">
-        <x:f>HYPERLINK("https://eatapp.co","eatapp.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eatapp.co, friendlyName=eatapp.co</x:v>
+      <x:c r="J96" s="14" t="str">
+        <x:v>https://eatapp.co</x:v>
       </x:c>
       <x:c r="K96" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9003,9 +8549,8 @@
       <x:c r="S96" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T96" s="14" t="e">
-        <x:f>HYPERLINK("https://restaurant.eatapp.co/about","restaurant.eatapp.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://restaurant.eatapp.co/about, friendlyName=restaurant.eatapp.co</x:v>
+      <x:c r="T96" s="14" t="str">
+        <x:v>https://restaurant.eatapp.co/about</x:v>
       </x:c>
       <x:c r="U96" s="14" t="str">
         <x:v>https://restaurant.eatapp.co/privacy
@@ -9015,17 +8560,14 @@
       <x:c r="V96" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W96" s="14" t="e">
-        <x:f>HYPERLINK("https://restaurant.eatapp.co/contact-us","restaurant.eatapp.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://restaurant.eatapp.co/contact-us, friendlyName=restaurant.eatapp.co</x:v>
-      </x:c>
-      <x:c r="X96" s="14" t="e">
-        <x:f>HYPERLINK("https://restaurant.eatapp.co/knowledge/live-support","restaurant.eatapp.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://restaurant.eatapp.co/knowledge/live-support, friendlyName=restaurant.eatapp.co</x:v>
-      </x:c>
-      <x:c r="Y96" s="14" t="e">
-        <x:f>HYPERLINK("https://restaurant.eatapp.co/knowledge/live-support","restaurant.eatapp.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://restaurant.eatapp.co/knowledge/live-support, friendlyName=restaurant.eatapp.co</x:v>
+      <x:c r="W96" s="14" t="str">
+        <x:v>https://restaurant.eatapp.co/contact-us</x:v>
+      </x:c>
+      <x:c r="X96" s="14" t="str">
+        <x:v>https://restaurant.eatapp.co/knowledge/live-support</x:v>
+      </x:c>
+      <x:c r="Y96" s="14" t="str">
+        <x:v>https://restaurant.eatapp.co/knowledge/live-support</x:v>
       </x:c>
       <x:c r="Z96" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9062,9 +8604,8 @@
       <x:c r="I97" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="J97" s="14" t="e">
-        <x:f>HYPERLINK("https://wafeq.com","wafeq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wafeq.com, friendlyName=wafeq.com</x:v>
+      <x:c r="J97" s="14" t="str">
+        <x:v>https://wafeq.com</x:v>
       </x:c>
       <x:c r="K97" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9091,30 +8632,25 @@
       <x:c r="S97" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wafeq.com/en-ae","wafeq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wafeq.com/en-ae, friendlyName=wafeq.com</x:v>
+      <x:c r="T97" s="14" t="str">
+        <x:v>https://www.wafeq.com/en-ae</x:v>
       </x:c>
       <x:c r="U97" s="14" t="str">
         <x:v>https://www.wafeq.com/en-sa/about
 https://www.wamda.com/en/2023/01/wafeq-raises-3-million-seed-round-led-raed-ventures-participation-wamda-capital
 https://www.wafeq.com/en/press-releases/media-center/wafeq-series-a-funding-accounting-smes</x:v>
       </x:c>
-      <x:c r="V97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/en/2023/01/wafeq-raises-3-million-seed-round-led-raed-ventures-participation-wamda-capital","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/en/2023/01/wafeq-raises-3-million-seed-round-led-raed-ventures-participation-wamda-capital, friendlyName=wamda.com</x:v>
-      </x:c>
-      <x:c r="W97" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=com.wafeq.prod","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=com.wafeq.prod, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="X97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wafeq.com/en-ae","wafeq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wafeq.com/en-ae, friendlyName=wafeq.com</x:v>
-      </x:c>
-      <x:c r="Y97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wafeq.com/en-ae/contact-sales","wafeq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wafeq.com/en-ae/contact-sales, friendlyName=wafeq.com</x:v>
+      <x:c r="V97" s="14" t="str">
+        <x:v>https://www.wamda.com/en/2023/01/wafeq-raises-3-million-seed-round-led-raed-ventures-participation-wamda-capital</x:v>
+      </x:c>
+      <x:c r="W97" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=com.wafeq.prod</x:v>
+      </x:c>
+      <x:c r="X97" s="14" t="str">
+        <x:v>https://www.wafeq.com/en-ae</x:v>
+      </x:c>
+      <x:c r="Y97" s="14" t="str">
+        <x:v>https://www.wafeq.com/en-ae/contact-sales</x:v>
       </x:c>
       <x:c r="Z97" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -9151,9 +8687,8 @@
       <x:c r="I98" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J98" s="14" t="e">
-        <x:f>HYPERLINK("https://useholo.com","useholo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://useholo.com, friendlyName=useholo.com</x:v>
+      <x:c r="J98" s="14" t="str">
+        <x:v>https://useholo.com</x:v>
       </x:c>
       <x:c r="K98" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9180,28 +8715,23 @@
       <x:c r="S98" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.wamda.com/wamda-investments/holo","wamda.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wamda.com/wamda-investments/holo, friendlyName=wamda.com</x:v>
+      <x:c r="T98" s="14" t="str">
+        <x:v>https://www.wamda.com/wamda-investments/holo</x:v>
       </x:c>
       <x:c r="U98" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.useholo.com/en/about-us","useholo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.useholo.com/en/about-us, friendlyName=useholo.com</x:v>
-      </x:c>
-      <x:c r="W98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="X98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="Y98" s="14" t="e">
-        <x:f>HYPERLINK("https://sa.useholo.com/en/contact-us","sa.useholo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sa.useholo.com/en/contact-us, friendlyName=sa.useholo.com</x:v>
+      <x:c r="V98" s="14" t="str">
+        <x:v>https://www.useholo.com/en/about-us</x:v>
+      </x:c>
+      <x:c r="W98" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761</x:v>
+      </x:c>
+      <x:c r="X98" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Holo-Mortgage-Consultants-230761</x:v>
+      </x:c>
+      <x:c r="Y98" s="14" t="str">
+        <x:v>https://sa.useholo.com/en/contact-us</x:v>
       </x:c>
       <x:c r="Z98" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -9238,9 +8768,8 @@
       <x:c r="I99" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J99" s="14" t="e">
-        <x:f>HYPERLINK("https://smartcrowd.ae","smartcrowd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://smartcrowd.ae, friendlyName=smartcrowd.ae</x:v>
+      <x:c r="J99" s="14" t="str">
+        <x:v>https://smartcrowd.ae</x:v>
       </x:c>
       <x:c r="K99" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9267,9 +8796,8 @@
       <x:c r="S99" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.thenationalnews.com/business/property/2024/04/01/how-smartcrowd-is-enabling-people-to-make-their-first-property-investment/","thenationalnews.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thenationalnews.com/business/property/2024/04/01/how-smartcrowd-is-enabling-people-to-make-their-first-property-investment/, friendlyName=thenationalnews.com</x:v>
+      <x:c r="T99" s="14" t="str">
+        <x:v>https://www.thenationalnews.com/business/property/2024/04/01/how-smartcrowd-is-enabling-people-to-make-their-first-property-investment/</x:v>
       </x:c>
       <x:c r="U99" s="14" t="str">
         <x:v>https://www.thenationalnews.com/business/property/2024/04/01/how-smartcrowd-is-enabling-people-to-make-their-first-property-investment/
@@ -9279,16 +8807,14 @@
       <x:c r="V99" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.smartcrowd.ae/","smartcrowd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.smartcrowd.ae/, friendlyName=smartcrowd.ae</x:v>
+      <x:c r="W99" s="14" t="str">
+        <x:v>https://www.smartcrowd.ae/</x:v>
       </x:c>
       <x:c r="X99" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.smartcrowd.ae/","smartcrowd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.smartcrowd.ae/, friendlyName=smartcrowd.ae</x:v>
+      <x:c r="Y99" s="14" t="str">
+        <x:v>https://www.smartcrowd.ae/</x:v>
       </x:c>
       <x:c r="Z99" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9325,9 +8851,8 @@
       <x:c r="I100" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J100" s="14" t="e">
-        <x:f>HYPERLINK("https://prypco.com","prypco.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prypco.com, friendlyName=prypco.com</x:v>
+      <x:c r="J100" s="14" t="str">
+        <x:v>https://prypco.com</x:v>
       </x:c>
       <x:c r="K100" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9354,9 +8879,8 @@
       <x:c r="S100" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T100" s="14" t="e">
-        <x:f>HYPERLINK("https://www.yello.ae/company/375075/prypco","yello.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.yello.ae/company/375075/prypco, friendlyName=yello.ae</x:v>
+      <x:c r="T100" s="14" t="str">
+        <x:v>https://www.yello.ae/company/375075/prypco</x:v>
       </x:c>
       <x:c r="U100" s="14" t="str">
         <x:v>https://www.crunchbase.com/organization/prypco
@@ -9366,17 +8890,14 @@
       <x:c r="V100" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W100" s="14" t="e">
-        <x:f>HYPERLINK("https://prypco.com/terms-and-conditions","prypco.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prypco.com/terms-and-conditions, friendlyName=prypco.com</x:v>
-      </x:c>
-      <x:c r="X100" s="14" t="e">
-        <x:f>HYPERLINK("https://prypco.com/terms-and-conditions","prypco.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://prypco.com/terms-and-conditions, friendlyName=prypco.com</x:v>
-      </x:c>
-      <x:c r="Y100" s="14" t="e">
-        <x:f>HYPERLINK("https://help.prypco.com/one/en/articles/13682346-how-to-contact-prypco-support","help.prypco.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.prypco.com/one/en/articles/13682346-how-to-contact-prypco-support, friendlyName=help.prypco.com</x:v>
+      <x:c r="W100" s="14" t="str">
+        <x:v>https://prypco.com/terms-and-conditions</x:v>
+      </x:c>
+      <x:c r="X100" s="14" t="str">
+        <x:v>https://prypco.com/terms-and-conditions</x:v>
+      </x:c>
+      <x:c r="Y100" s="14" t="str">
+        <x:v>https://help.prypco.com/one/en/articles/13682346-how-to-contact-prypco-support</x:v>
       </x:c>
       <x:c r="Z100" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9413,9 +8934,8 @@
       <x:c r="I101" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="J101" s="14" t="e">
-        <x:f>HYPERLINK("https://holofair.io","holofair.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://holofair.io, friendlyName=holofair.io</x:v>
+      <x:c r="J101" s="14" t="str">
+        <x:v>https://holofair.io</x:v>
       </x:c>
       <x:c r="K101" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9442,9 +8962,8 @@
       <x:c r="S101" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.gulfleads.ae/company/holofair-c55bf5","gulfleads.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.gulfleads.ae/company/holofair-c55bf5, friendlyName=gulfleads.ae</x:v>
+      <x:c r="T101" s="14" t="str">
+        <x:v>https://www.gulfleads.ae/company/holofair-c55bf5</x:v>
       </x:c>
       <x:c r="U101" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -9455,13 +8974,11 @@
       <x:c r="W101" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="X101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.holofair.io/contact","holofair.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.holofair.io/contact, friendlyName=holofair.io</x:v>
-      </x:c>
-      <x:c r="Y101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.holofair.io/contact","holofair.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.holofair.io/contact, friendlyName=holofair.io</x:v>
+      <x:c r="X101" s="14" t="str">
+        <x:v>https://www.holofair.io/contact</x:v>
+      </x:c>
+      <x:c r="Y101" s="14" t="str">
+        <x:v>https://www.holofair.io/contact</x:v>
       </x:c>
       <x:c r="Z101" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -9498,9 +9015,8 @@
       <x:c r="I102" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="J102" s="14" t="e">
-        <x:f>HYPERLINK("https://podeo.co","podeo.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://podeo.co, friendlyName=podeo.co</x:v>
+      <x:c r="J102" s="14" t="str">
+        <x:v>https://podeo.co</x:v>
       </x:c>
       <x:c r="K102" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9527,9 +9043,8 @@
       <x:c r="S102" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T102" s="14" t="e">
-        <x:f>HYPERLINK("https://podeo.co/about-us","podeo.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://podeo.co/about-us, friendlyName=podeo.co</x:v>
+      <x:c r="T102" s="14" t="str">
+        <x:v>https://podeo.co/about-us</x:v>
       </x:c>
       <x:c r="U102" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -9537,16 +9052,14 @@
       <x:c r="V102" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W102" s="14" t="e">
-        <x:f>HYPERLINK("https://podeo.co/contact-us","podeo.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://podeo.co/contact-us, friendlyName=podeo.co</x:v>
+      <x:c r="W102" s="14" t="str">
+        <x:v>https://podeo.co/contact-us</x:v>
       </x:c>
       <x:c r="X102" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y102" s="14" t="e">
-        <x:f>HYPERLINK("https://podeo.co/contact-us","podeo.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://podeo.co/contact-us, friendlyName=podeo.co</x:v>
+      <x:c r="Y102" s="14" t="str">
+        <x:v>https://podeo.co/contact-us</x:v>
       </x:c>
       <x:c r="Z102" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9583,9 +9096,8 @@
       <x:c r="I103" s="6" t="str">
         <x:v>تمويل / مؤسسون</x:v>
       </x:c>
-      <x:c r="J103" s="14" t="e">
-        <x:f>HYPERLINK("https://getbaraka.com","getbaraka.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://getbaraka.com, friendlyName=getbaraka.com</x:v>
+      <x:c r="J103" s="14" t="str">
+        <x:v>https://getbaraka.com</x:v>
       </x:c>
       <x:c r="K103" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9612,9 +9124,8 @@
       <x:c r="S103" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T103" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ycombinator.com/companies/baraka","ycombinator.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ycombinator.com/companies/baraka, friendlyName=ycombinator.com</x:v>
+      <x:c r="T103" s="14" t="str">
+        <x:v>https://www.ycombinator.com/companies/baraka</x:v>
       </x:c>
       <x:c r="U103" s="14" t="str">
         <x:v>https://www.ycombinator.com/companies/baraka
@@ -9624,16 +9135,14 @@
       <x:c r="V103" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="W103" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ycombinator.com/companies/baraka","ycombinator.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ycombinator.com/companies/baraka, friendlyName=ycombinator.com</x:v>
+      <x:c r="W103" s="14" t="str">
+        <x:v>https://www.ycombinator.com/companies/baraka</x:v>
       </x:c>
       <x:c r="X103" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y103" s="14" t="e">
-        <x:f>HYPERLINK("https://www.getbaraka.com/contact","getbaraka.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.getbaraka.com/contact, friendlyName=getbaraka.com</x:v>
+      <x:c r="Y103" s="14" t="str">
+        <x:v>https://www.getbaraka.com/contact</x:v>
       </x:c>
       <x:c r="Z103" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -9670,9 +9179,8 @@
       <x:c r="I104" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J104" s="14" t="e">
-        <x:f>HYPERLINK("https://camb.ai","camb.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://camb.ai, friendlyName=camb.ai</x:v>
+      <x:c r="J104" s="14" t="str">
+        <x:v>https://camb.ai</x:v>
       </x:c>
       <x:c r="K104" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9699,29 +9207,25 @@
       <x:c r="S104" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.gulfstartupmap.com/startups/camb-ai","gulfstartupmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.gulfstartupmap.com/startups/camb-ai, friendlyName=gulfstartupmap.com</x:v>
+      <x:c r="T104" s="14" t="str">
+        <x:v>https://www.gulfstartupmap.com/startups/camb-ai</x:v>
       </x:c>
       <x:c r="U104" s="14" t="str">
         <x:v>https://www.gulfstartupmap.com/startups/camb-ai
 https://www.camb.ai/blog-post/announcing-camb-ais-4m-seed-round-led-by-courtside-ventures
 https://www.crunchbase.com/organization/camb-ai</x:v>
       </x:c>
-      <x:c r="V104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.gulfstartupmap.com/startups/camb-ai","gulfstartupmap.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.gulfstartupmap.com/startups/camb-ai, friendlyName=gulfstartupmap.com</x:v>
-      </x:c>
-      <x:c r="W104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.camb.ai/fr/terms-conditions","camb.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.camb.ai/fr/terms-conditions, friendlyName=camb.ai</x:v>
+      <x:c r="V104" s="14" t="str">
+        <x:v>https://www.gulfstartupmap.com/startups/camb-ai</x:v>
+      </x:c>
+      <x:c r="W104" s="14" t="str">
+        <x:v>https://www.camb.ai/fr/terms-conditions</x:v>
       </x:c>
       <x:c r="X104" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="Y104" s="14" t="e">
-        <x:f>HYPERLINK("https://help.camb.ai/en/articles/8751313-contact-us","help.camb.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://help.camb.ai/en/articles/8751313-contact-us, friendlyName=help.camb.ai</x:v>
+      <x:c r="Y104" s="14" t="str">
+        <x:v>https://help.camb.ai/en/articles/8751313-contact-us</x:v>
       </x:c>
       <x:c r="Z104" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9758,9 +9262,8 @@
       <x:c r="I105" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="J105" s="14" t="e">
-        <x:f>HYPERLINK("https://derq.com","derq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://derq.com, friendlyName=derq.com</x:v>
+      <x:c r="J105" s="14" t="str">
+        <x:v>https://derq.com</x:v>
       </x:c>
       <x:c r="K105" s="6" t="str">
         <x:v>غير مؤكد من المصادر المراجعة</x:v>
@@ -9787,28 +9290,23 @@
       <x:c r="S105" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T105" s="14" t="e">
-        <x:f>HYPERLINK("https://en.derq.com/faq","en.derq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.derq.com/faq, friendlyName=en.derq.com</x:v>
+      <x:c r="T105" s="14" t="str">
+        <x:v>https://en.derq.com/faq</x:v>
       </x:c>
       <x:c r="U105" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V105" s="14" t="e">
-        <x:f>HYPERLINK("https://en.derq.com/press-coverage/2017/11/19/dubai-startup-derq-secures-15-million-seed-round","en.derq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.derq.com/press-coverage/2017/11/19/dubai-startup-derq-secures-15-million-seed-round, friendlyName=en.derq.com</x:v>
-      </x:c>
-      <x:c r="W105" s="14" t="e">
-        <x:f>HYPERLINK("https://en.derq.com/privacy-policy","en.derq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.derq.com/privacy-policy, friendlyName=en.derq.com</x:v>
-      </x:c>
-      <x:c r="X105" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/company-list/Derq-Systems-FZ-LLC-130168","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/company-list/Derq-Systems-FZ-LLC-130168, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="Y105" s="14" t="e">
-        <x:f>HYPERLINK("https://en.derq.com/faq","en.derq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://en.derq.com/faq, friendlyName=en.derq.com</x:v>
+      <x:c r="V105" s="14" t="str">
+        <x:v>https://en.derq.com/press-coverage/2017/11/19/dubai-startup-derq-secures-15-million-seed-round</x:v>
+      </x:c>
+      <x:c r="W105" s="14" t="str">
+        <x:v>https://en.derq.com/privacy-policy</x:v>
+      </x:c>
+      <x:c r="X105" s="14" t="str">
+        <x:v>https://www.decypha.com/en/company-list/Derq-Systems-FZ-LLC-130168</x:v>
+      </x:c>
+      <x:c r="Y105" s="14" t="str">
+        <x:v>https://en.derq.com/faq</x:v>
       </x:c>
       <x:c r="Z105" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -9837,7 +9335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R339a6fb152384bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5d2be516cc14b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10020,13 +9518,11 @@
       <x:c r="K6" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L6" s="14" t="e">
-        <x:f>HYPERLINK("https://becocapital.com","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://becocapital.com, friendlyName=becocapital.com</x:v>
-      </x:c>
-      <x:c r="M6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/contact/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/contact/, friendlyName=becocapital.com</x:v>
+      <x:c r="L6" s="14" t="str">
+        <x:v>https://becocapital.com</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>https://www.becocapital.com/contact/</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10046,16 +9542,14 @@
       <x:c r="S6" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/contact/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/contact/, friendlyName=becocapital.com</x:v>
+      <x:c r="T6" s="14" t="str">
+        <x:v>https://www.becocapital.com/contact/</x:v>
       </x:c>
       <x:c r="U6" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V6" s="14" t="e">
-        <x:f>HYPERLINK("https://www.becocapital.com/contact/","becocapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.becocapital.com/contact/, friendlyName=becocapital.com</x:v>
+      <x:c r="V6" s="14" t="str">
+        <x:v>https://www.becocapital.com/contact/</x:v>
       </x:c>
       <x:c r="W6" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10098,13 +9592,11 @@
       <x:c r="K7" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="e">
-        <x:f>HYPERLINK("https://shorooq.com","shorooq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://shorooq.com, friendlyName=shorooq.com</x:v>
-      </x:c>
-      <x:c r="M7" s="14" t="e">
-        <x:f>HYPERLINK("https://www.shorooq.com/","shorooq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.shorooq.com/, friendlyName=shorooq.com</x:v>
+      <x:c r="L7" s="14" t="str">
+        <x:v>https://shorooq.com</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="str">
+        <x:v>https://www.shorooq.com/</x:v>
       </x:c>
       <x:c r="N7" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10122,17 +9614,14 @@
       <x:c r="S7" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T7" s="14" t="e">
-        <x:f>HYPERLINK("https://www.shorooq.com/","shorooq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.shorooq.com/, friendlyName=shorooq.com</x:v>
-      </x:c>
-      <x:c r="U7" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820, friendlyName=adgm.com</x:v>
-      </x:c>
-      <x:c r="V7" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820, friendlyName=adgm.com</x:v>
+      <x:c r="T7" s="14" t="str">
+        <x:v>https://www.shorooq.com/</x:v>
+      </x:c>
+      <x:c r="U7" s="14" t="str">
+        <x:v>https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820</x:v>
+      </x:c>
+      <x:c r="V7" s="14" t="str">
+        <x:v>https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165820</x:v>
       </x:c>
       <x:c r="W7" s="6" t="str">
         <x:v>سجل تنظيمي رسمي</x:v>
@@ -10175,13 +9664,11 @@
       <x:c r="K8" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L8" s="14" t="e">
-        <x:f>HYPERLINK("https://wamdacapital.com","wamdacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wamdacapital.com, friendlyName=wamdacapital.com</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="e">
-        <x:f>HYPERLINK("https://wamdacapital.com/contact-us/","wamdacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wamdacapital.com/contact-us/, friendlyName=wamdacapital.com</x:v>
+      <x:c r="L8" s="14" t="str">
+        <x:v>https://wamdacapital.com</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="str">
+        <x:v>https://wamdacapital.com/contact-us/</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10199,13 +9686,11 @@
       <x:c r="S8" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T8" s="14" t="e">
-        <x:f>HYPERLINK("https://wamdacapital.com/contact-us/","wamdacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wamdacapital.com/contact-us/, friendlyName=wamdacapital.com</x:v>
-      </x:c>
-      <x:c r="U8" s="14" t="e">
-        <x:f>HYPERLINK("https://wamdacapital.com/contact-us/","wamdacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wamdacapital.com/contact-us/, friendlyName=wamdacapital.com</x:v>
+      <x:c r="T8" s="14" t="str">
+        <x:v>https://wamdacapital.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="U8" s="14" t="str">
+        <x:v>https://wamdacapital.com/contact-us/</x:v>
       </x:c>
       <x:c r="V8" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10251,13 +9736,11 @@
       <x:c r="K9" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L9" s="14" t="e">
-        <x:f>HYPERLINK("https://global.vc","global.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://global.vc, friendlyName=global.vc</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="e">
-        <x:f>HYPERLINK("https://www.global.vc/contact","global.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.global.vc/contact, friendlyName=global.vc</x:v>
+      <x:c r="L9" s="14" t="str">
+        <x:v>https://global.vc</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="str">
+        <x:v>https://www.global.vc/contact</x:v>
       </x:c>
       <x:c r="N9" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10277,13 +9760,11 @@
       <x:c r="S9" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T9" s="14" t="e">
-        <x:f>HYPERLINK("https://www.global.vc/contact","global.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.global.vc/contact, friendlyName=global.vc</x:v>
-      </x:c>
-      <x:c r="U9" s="14" t="e">
-        <x:f>HYPERLINK("https://jobs.global.vc/cookie-policy","jobs.global.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jobs.global.vc/cookie-policy, friendlyName=jobs.global.vc</x:v>
+      <x:c r="T9" s="14" t="str">
+        <x:v>https://www.global.vc/contact</x:v>
+      </x:c>
+      <x:c r="U9" s="14" t="str">
+        <x:v>https://jobs.global.vc/cookie-policy</x:v>
       </x:c>
       <x:c r="V9" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10329,13 +9810,11 @@
       <x:c r="K10" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L10" s="14" t="e">
-        <x:f>HYPERLINK("https://mevp.com","mevp.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mevp.com, friendlyName=mevp.com</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="e">
-        <x:f>HYPERLINK("https://jobs.mevp.com/cookie-policy","jobs.mevp.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jobs.mevp.com/cookie-policy, friendlyName=jobs.mevp.com</x:v>
+      <x:c r="L10" s="14" t="str">
+        <x:v>https://mevp.com</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="str">
+        <x:v>https://jobs.mevp.com/cookie-policy</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10353,13 +9832,11 @@
       <x:c r="S10" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T10" s="14" t="e">
-        <x:f>HYPERLINK("https://jobs.mevp.com/cookie-policy","jobs.mevp.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jobs.mevp.com/cookie-policy, friendlyName=jobs.mevp.com</x:v>
-      </x:c>
-      <x:c r="U10" s="14" t="e">
-        <x:f>HYPERLINK("https://jobs.mevp.com/cookie-policy","jobs.mevp.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jobs.mevp.com/cookie-policy, friendlyName=jobs.mevp.com</x:v>
+      <x:c r="T10" s="14" t="str">
+        <x:v>https://jobs.mevp.com/cookie-policy</x:v>
+      </x:c>
+      <x:c r="U10" s="14" t="str">
+        <x:v>https://jobs.mevp.com/cookie-policy</x:v>
       </x:c>
       <x:c r="V10" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10405,13 +9882,11 @@
       <x:c r="K11" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L11" s="14" t="e">
-        <x:f>HYPERLINK("https://nuwacapital.io","nuwacapital.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nuwacapital.io, friendlyName=nuwacapital.io</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="e">
-        <x:f>HYPERLINK("https://nuwacapital.webflow.io/contact","nuwacapital.webflow.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nuwacapital.webflow.io/contact, friendlyName=nuwacapital.webflow.io</x:v>
+      <x:c r="L11" s="14" t="str">
+        <x:v>https://nuwacapital.io</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>https://nuwacapital.webflow.io/contact</x:v>
       </x:c>
       <x:c r="N11" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10429,13 +9904,11 @@
       <x:c r="S11" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T11" s="14" t="e">
-        <x:f>HYPERLINK("https://nuwacapital.webflow.io/contact","nuwacapital.webflow.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nuwacapital.webflow.io/contact, friendlyName=nuwacapital.webflow.io</x:v>
-      </x:c>
-      <x:c r="U11" s="14" t="e">
-        <x:f>HYPERLINK("https://nuwacapital.webflow.io/contact","nuwacapital.webflow.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://nuwacapital.webflow.io/contact, friendlyName=nuwacapital.webflow.io</x:v>
+      <x:c r="T11" s="14" t="str">
+        <x:v>https://nuwacapital.webflow.io/contact</x:v>
+      </x:c>
+      <x:c r="U11" s="14" t="str">
+        <x:v>https://nuwacapital.webflow.io/contact</x:v>
       </x:c>
       <x:c r="V11" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10481,13 +9954,11 @@
       <x:c r="K12" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L12" s="14" t="e">
-        <x:f>HYPERLINK("https://venturesouq.com","venturesouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://venturesouq.com, friendlyName=venturesouq.com</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="e">
-        <x:f>HYPERLINK("https://www.venturesouq.com/contact","venturesouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.venturesouq.com/contact, friendlyName=venturesouq.com</x:v>
+      <x:c r="L12" s="14" t="str">
+        <x:v>https://venturesouq.com</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>https://www.venturesouq.com/contact</x:v>
       </x:c>
       <x:c r="N12" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10505,13 +9976,11 @@
       <x:c r="S12" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T12" s="14" t="e">
-        <x:f>HYPERLINK("https://www.venturesouq.com/contact","venturesouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.venturesouq.com/contact, friendlyName=venturesouq.com</x:v>
-      </x:c>
-      <x:c r="U12" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165875","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165875, friendlyName=adgm.com</x:v>
+      <x:c r="T12" s="14" t="str">
+        <x:v>https://www.venturesouq.com/contact</x:v>
+      </x:c>
+      <x:c r="U12" s="14" t="str">
+        <x:v>https://www.adgm.com/api/FSRAC_FirmPdf/GenerateFirmProfilePdf?FirmId=165875</x:v>
       </x:c>
       <x:c r="V12" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10557,13 +10026,11 @@
       <x:c r="K13" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L13" s="14" t="e">
-        <x:f>HYPERLINK("https://cotu.vc","cotu.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cotu.vc, friendlyName=cotu.vc</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cotu.vc/","cotu.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cotu.vc/, friendlyName=cotu.vc</x:v>
+      <x:c r="L13" s="14" t="str">
+        <x:v>https://cotu.vc</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>https://www.cotu.vc/</x:v>
       </x:c>
       <x:c r="N13" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10581,9 +10048,8 @@
       <x:c r="S13" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T13" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cotu.vc/","cotu.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cotu.vc/, friendlyName=cotu.vc</x:v>
+      <x:c r="T13" s="14" t="str">
+        <x:v>https://www.cotu.vc/</x:v>
       </x:c>
       <x:c r="U13" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10632,13 +10098,11 @@
       <x:c r="K14" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="L14" s="14" t="e">
-        <x:f>HYPERLINK("https://iliad-partners.com","iliad-partners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://iliad-partners.com, friendlyName=iliad-partners.com</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="e">
-        <x:f>HYPERLINK("https://www.iliad-partners.com/contact","iliad-partners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.iliad-partners.com/contact, friendlyName=iliad-partners.com</x:v>
+      <x:c r="L14" s="14" t="str">
+        <x:v>https://iliad-partners.com</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>https://www.iliad-partners.com/contact</x:v>
       </x:c>
       <x:c r="N14" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10656,13 +10120,11 @@
       <x:c r="S14" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T14" s="14" t="e">
-        <x:f>HYPERLINK("https://www.iliad-partners.com/contact","iliad-partners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.iliad-partners.com/contact, friendlyName=iliad-partners.com</x:v>
-      </x:c>
-      <x:c r="U14" s="14" t="e">
-        <x:f>HYPERLINK("https://www.privateequityinternational.com/institution-profiles/iliad-partners.html","privateequityinternational.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.privateequityinternational.com/institution-profiles/iliad-partners.html, friendlyName=privateequityinternational.com</x:v>
+      <x:c r="T14" s="14" t="str">
+        <x:v>https://www.iliad-partners.com/contact</x:v>
+      </x:c>
+      <x:c r="U14" s="14" t="str">
+        <x:v>https://www.privateequityinternational.com/institution-profiles/iliad-partners.html</x:v>
       </x:c>
       <x:c r="V14" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10708,13 +10170,11 @@
       <x:c r="K15" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L15" s="14" t="e">
-        <x:f>HYPERLINK("https://access-bridge.com","access-bridge.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://access-bridge.com, friendlyName=access-bridge.com</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="e">
-        <x:f>HYPERLINK("https://access-bridge.com/","access-bridge.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://access-bridge.com/, friendlyName=access-bridge.com</x:v>
+      <x:c r="L15" s="14" t="str">
+        <x:v>https://access-bridge.com</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>https://access-bridge.com/</x:v>
       </x:c>
       <x:c r="N15" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10732,17 +10192,14 @@
       <x:c r="S15" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T15" s="14" t="e">
-        <x:f>HYPERLINK("https://access-bridge.com/","access-bridge.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://access-bridge.com/, friendlyName=access-bridge.com</x:v>
-      </x:c>
-      <x:c r="U15" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006, friendlyName=adgm.com</x:v>
-      </x:c>
-      <x:c r="V15" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006, friendlyName=adgm.com</x:v>
+      <x:c r="T15" s="14" t="str">
+        <x:v>https://access-bridge.com/</x:v>
+      </x:c>
+      <x:c r="U15" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006</x:v>
+      </x:c>
+      <x:c r="V15" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/access-bridge-ventures-limited-200006</x:v>
       </x:c>
       <x:c r="W15" s="6" t="str">
         <x:v>سجل تنظيمي رسمي</x:v>
@@ -10785,13 +10242,11 @@
       <x:c r="K16" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L16" s="14" t="e">
-        <x:f>HYPERLINK("https://plus.vc","plus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://plus.vc, friendlyName=plus.vc</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="e">
-        <x:f>HYPERLINK("https://plus.vc/contact","plus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://plus.vc/contact, friendlyName=plus.vc</x:v>
+      <x:c r="L16" s="14" t="str">
+        <x:v>https://plus.vc</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
+        <x:v>https://plus.vc/contact</x:v>
       </x:c>
       <x:c r="N16" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10809,13 +10264,11 @@
       <x:c r="S16" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T16" s="14" t="e">
-        <x:f>HYPERLINK("https://plus.vc/contact","plus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://plus.vc/contact, friendlyName=plus.vc</x:v>
-      </x:c>
-      <x:c r="U16" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/plus-vc-management-limited-200029","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/plus-vc-management-limited-200029, friendlyName=adgm.com</x:v>
+      <x:c r="T16" s="14" t="str">
+        <x:v>https://plus.vc/contact</x:v>
+      </x:c>
+      <x:c r="U16" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/plus-vc-management-limited-200029</x:v>
       </x:c>
       <x:c r="V16" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10861,13 +10314,11 @@
       <x:c r="K17" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="L17" s="14" t="e">
-        <x:f>HYPERLINK("https://ventures.further.ae","ventures.further.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ventures.further.ae, friendlyName=ventures.further.ae</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="e">
-        <x:f>HYPERLINK("https://ventures.further.ae/contact","ventures.further.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ventures.further.ae/contact, friendlyName=ventures.further.ae</x:v>
+      <x:c r="L17" s="14" t="str">
+        <x:v>https://ventures.further.ae</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="str">
+        <x:v>https://ventures.further.ae/contact</x:v>
       </x:c>
       <x:c r="N17" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10885,13 +10336,11 @@
       <x:c r="S17" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T17" s="14" t="e">
-        <x:f>HYPERLINK("https://ventures.further.ae/contact","ventures.further.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ventures.further.ae/contact, friendlyName=ventures.further.ae</x:v>
-      </x:c>
-      <x:c r="U17" s="14" t="e">
-        <x:f>HYPERLINK("https://ventures.further.ae/contact","ventures.further.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ventures.further.ae/contact, friendlyName=ventures.further.ae</x:v>
+      <x:c r="T17" s="14" t="str">
+        <x:v>https://ventures.further.ae/contact</x:v>
+      </x:c>
+      <x:c r="U17" s="14" t="str">
+        <x:v>https://ventures.further.ae/contact</x:v>
       </x:c>
       <x:c r="V17" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -10937,13 +10386,11 @@
       <x:c r="K18" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L18" s="14" t="e">
-        <x:f>HYPERLINK("https://oraseyacapital.com","oraseyacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://oraseyacapital.com, friendlyName=oraseyacapital.com</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.oraseyacapital.com/","oraseyacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.oraseyacapital.com/, friendlyName=oraseyacapital.com</x:v>
+      <x:c r="L18" s="14" t="str">
+        <x:v>https://oraseyacapital.com</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="str">
+        <x:v>https://www.oraseyacapital.com/</x:v>
       </x:c>
       <x:c r="N18" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -10961,13 +10408,11 @@
       <x:c r="S18" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.oraseyacapital.com/","oraseyacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.oraseyacapital.com/, friendlyName=oraseyacapital.com</x:v>
-      </x:c>
-      <x:c r="U18" s="14" t="e">
-        <x:f>HYPERLINK("https://www.oraseyacapital.com/privacypolicy","oraseyacapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.oraseyacapital.com/privacypolicy, friendlyName=oraseyacapital.com</x:v>
+      <x:c r="T18" s="14" t="str">
+        <x:v>https://www.oraseyacapital.com/</x:v>
+      </x:c>
+      <x:c r="U18" s="14" t="str">
+        <x:v>https://www.oraseyacapital.com/privacypolicy</x:v>
       </x:c>
       <x:c r="V18" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11013,13 +10458,11 @@
       <x:c r="K19" s="6" t="str">
         <x:v>تمويل / مؤسسون</x:v>
       </x:c>
-      <x:c r="L19" s="14" t="e">
-        <x:f>HYPERLINK("https://pvp-me.com","pvp-me.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pvp-me.com, friendlyName=pvp-me.com</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="e">
-        <x:f>HYPERLINK("https://pvp-me.com/","pvp-me.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pvp-me.com/, friendlyName=pvp-me.com</x:v>
+      <x:c r="L19" s="14" t="str">
+        <x:v>https://pvp-me.com</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="str">
+        <x:v>https://pvp-me.com/</x:v>
       </x:c>
       <x:c r="N19" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11037,17 +10480,14 @@
       <x:c r="S19" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T19" s="14" t="e">
-        <x:f>HYPERLINK("https://pvp-me.com/","pvp-me.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pvp-me.com/, friendlyName=pvp-me.com</x:v>
-      </x:c>
-      <x:c r="U19" s="14" t="e">
-        <x:f>HYPERLINK("https://pvp-me.com/","pvp-me.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pvp-me.com/, friendlyName=pvp-me.com</x:v>
-      </x:c>
-      <x:c r="V19" s="14" t="e">
-        <x:f>HYPERLINK("https://pvp-me.com/","pvp-me.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pvp-me.com/, friendlyName=pvp-me.com</x:v>
+      <x:c r="T19" s="14" t="str">
+        <x:v>https://pvp-me.com/</x:v>
+      </x:c>
+      <x:c r="U19" s="14" t="str">
+        <x:v>https://pvp-me.com/</x:v>
+      </x:c>
+      <x:c r="V19" s="14" t="str">
+        <x:v>https://pvp-me.com/</x:v>
       </x:c>
       <x:c r="W19" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -11090,13 +10530,11 @@
       <x:c r="K20" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L20" s="14" t="e">
-        <x:f>HYPERLINK("https://bunat.vc","bunat.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bunat.vc, friendlyName=bunat.vc</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="e">
-        <x:f>HYPERLINK("https://bunat.vc/contact/","bunat.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bunat.vc/contact/, friendlyName=bunat.vc</x:v>
+      <x:c r="L20" s="14" t="str">
+        <x:v>https://bunat.vc</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="str">
+        <x:v>https://bunat.vc/contact/</x:v>
       </x:c>
       <x:c r="N20" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11114,9 +10552,8 @@
       <x:c r="S20" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T20" s="14" t="e">
-        <x:f>HYPERLINK("https://bunat.vc/contact/","bunat.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bunat.vc/contact/, friendlyName=bunat.vc</x:v>
+      <x:c r="T20" s="14" t="str">
+        <x:v>https://bunat.vc/contact/</x:v>
       </x:c>
       <x:c r="U20" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11165,13 +10602,11 @@
       <x:c r="K21" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L21" s="14" t="e">
-        <x:f>HYPERLINK("https://jasoor.vc","jasoor.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jasoor.vc, friendlyName=jasoor.vc</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="e">
-        <x:f>HYPERLINK("https://jasoor.vc/","jasoor.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jasoor.vc/, friendlyName=jasoor.vc</x:v>
+      <x:c r="L21" s="14" t="str">
+        <x:v>https://jasoor.vc</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="str">
+        <x:v>https://jasoor.vc/</x:v>
       </x:c>
       <x:c r="N21" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11189,13 +10624,11 @@
       <x:c r="S21" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T21" s="14" t="e">
-        <x:f>HYPERLINK("https://jasoor.vc/","jasoor.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jasoor.vc/, friendlyName=jasoor.vc</x:v>
-      </x:c>
-      <x:c r="U21" s="14" t="e">
-        <x:f>HYPERLINK("https://jasoor.vc/","jasoor.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jasoor.vc/, friendlyName=jasoor.vc</x:v>
+      <x:c r="T21" s="14" t="str">
+        <x:v>https://jasoor.vc/</x:v>
+      </x:c>
+      <x:c r="U21" s="14" t="str">
+        <x:v>https://jasoor.vc/</x:v>
       </x:c>
       <x:c r="V21" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11241,13 +10674,11 @@
       <x:c r="K22" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L22" s="14" t="e">
-        <x:f>HYPERLINK("https://natural.ventures","natural.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natural.ventures, friendlyName=natural.ventures</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="e">
-        <x:f>HYPERLINK("https://natural.ventures/contact-us/","natural.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natural.ventures/contact-us/, friendlyName=natural.ventures</x:v>
+      <x:c r="L22" s="14" t="str">
+        <x:v>https://natural.ventures</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="str">
+        <x:v>https://natural.ventures/contact-us/</x:v>
       </x:c>
       <x:c r="N22" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11265,13 +10696,11 @@
       <x:c r="S22" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T22" s="14" t="e">
-        <x:f>HYPERLINK("https://natural.ventures/contact-us/","natural.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natural.ventures/contact-us/, friendlyName=natural.ventures</x:v>
-      </x:c>
-      <x:c r="U22" s="14" t="e">
-        <x:f>HYPERLINK("https://natural.ventures/contact-us/","natural.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://natural.ventures/contact-us/, friendlyName=natural.ventures</x:v>
+      <x:c r="T22" s="14" t="str">
+        <x:v>https://natural.ventures/contact-us/</x:v>
+      </x:c>
+      <x:c r="U22" s="14" t="str">
+        <x:v>https://natural.ventures/contact-us/</x:v>
       </x:c>
       <x:c r="V22" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11317,13 +10746,11 @@
       <x:c r="K23" s="6" t="str">
         <x:v>بريد عمل منشور لمسؤول بالجهة</x:v>
       </x:c>
-      <x:c r="L23" s="14" t="e">
-        <x:f>HYPERLINK("https://mindshiftcapital.com","mindshiftcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mindshiftcapital.com, friendlyName=mindshiftcapital.com</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mindshiftcapital.com/","mindshiftcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mindshiftcapital.com/, friendlyName=mindshiftcapital.com</x:v>
+      <x:c r="L23" s="14" t="str">
+        <x:v>https://mindshiftcapital.com</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="str">
+        <x:v>https://www.mindshiftcapital.com/</x:v>
       </x:c>
       <x:c r="N23" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11341,13 +10768,11 @@
       <x:c r="S23" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T23" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mindshiftcapital.com/","mindshiftcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mindshiftcapital.com/, friendlyName=mindshiftcapital.com</x:v>
-      </x:c>
-      <x:c r="U23" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mindshiftcapital.com/","mindshiftcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mindshiftcapital.com/, friendlyName=mindshiftcapital.com</x:v>
+      <x:c r="T23" s="14" t="str">
+        <x:v>https://www.mindshiftcapital.com/</x:v>
+      </x:c>
+      <x:c r="U23" s="14" t="str">
+        <x:v>https://www.mindshiftcapital.com/</x:v>
       </x:c>
       <x:c r="V23" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11393,13 +10818,11 @@
       <x:c r="K24" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L24" s="14" t="e">
-        <x:f>HYPERLINK("https://jabbar.com","jabbar.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jabbar.com, friendlyName=jabbar.com</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="e">
-        <x:f>HYPERLINK("https://jabbar.com/","jabbar.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jabbar.com/, friendlyName=jabbar.com</x:v>
+      <x:c r="L24" s="14" t="str">
+        <x:v>https://jabbar.com</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="str">
+        <x:v>https://jabbar.com/</x:v>
       </x:c>
       <x:c r="N24" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11417,13 +10840,11 @@
       <x:c r="S24" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T24" s="14" t="e">
-        <x:f>HYPERLINK("https://jabbar.com/","jabbar.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://jabbar.com/, friendlyName=jabbar.com</x:v>
-      </x:c>
-      <x:c r="U24" s="14" t="e">
-        <x:f>HYPERLINK("https://find-lead.com/jabbar-internet-group-details","find-lead.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://find-lead.com/jabbar-internet-group-details, friendlyName=find-lead.com</x:v>
+      <x:c r="T24" s="14" t="str">
+        <x:v>https://jabbar.com/</x:v>
+      </x:c>
+      <x:c r="U24" s="14" t="str">
+        <x:v>https://find-lead.com/jabbar-internet-group-details</x:v>
       </x:c>
       <x:c r="V24" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11469,13 +10890,11 @@
       <x:c r="K25" s="6" t="str">
         <x:v>إعلام؛ اطلب تحويلك للفريق المختص</x:v>
       </x:c>
-      <x:c r="L25" s="14" t="e">
-        <x:f>HYPERLINK("https://modus.vc","modus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://modus.vc, friendlyName=modus.vc</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="e">
-        <x:f>HYPERLINK("https://modus.vc/contact/","modus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://modus.vc/contact/, friendlyName=modus.vc</x:v>
+      <x:c r="L25" s="14" t="str">
+        <x:v>https://modus.vc</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="str">
+        <x:v>https://modus.vc/contact/</x:v>
       </x:c>
       <x:c r="N25" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11493,13 +10912,11 @@
       <x:c r="S25" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T25" s="14" t="e">
-        <x:f>HYPERLINK("https://modus.vc/contact/","modus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://modus.vc/contact/, friendlyName=modus.vc</x:v>
-      </x:c>
-      <x:c r="U25" s="14" t="e">
-        <x:f>HYPERLINK("https://modus.vc/press-kit/","modus.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://modus.vc/press-kit/, friendlyName=modus.vc</x:v>
+      <x:c r="T25" s="14" t="str">
+        <x:v>https://modus.vc/contact/</x:v>
+      </x:c>
+      <x:c r="U25" s="14" t="str">
+        <x:v>https://modus.vc/press-kit/</x:v>
       </x:c>
       <x:c r="V25" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11545,13 +10962,11 @@
       <x:c r="K26" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L26" s="14" t="e">
-        <x:f>HYPERLINK("https://mubadalacapital.ae","mubadalacapital.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mubadalacapital.ae, friendlyName=mubadalacapital.ae</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadalacapital.ae/","mubadalacapital.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadalacapital.ae/, friendlyName=mubadalacapital.ae</x:v>
+      <x:c r="L26" s="14" t="str">
+        <x:v>https://mubadalacapital.ae</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="str">
+        <x:v>https://www.mubadalacapital.ae/</x:v>
       </x:c>
       <x:c r="N26" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11571,17 +10986,14 @@
       <x:c r="S26" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T26" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadalacapital.ae/","mubadalacapital.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadalacapital.ae/, friendlyName=mubadalacapital.ae</x:v>
-      </x:c>
-      <x:c r="U26" s="14" t="e">
-        <x:f>HYPERLINK("https://www.decypha.com/en/investment/public/Mubadala-Capital-149029","decypha.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.decypha.com/en/investment/public/Mubadala-Capital-149029, friendlyName=decypha.com</x:v>
-      </x:c>
-      <x:c r="V26" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadalacapital.ae/","mubadalacapital.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadalacapital.ae/, friendlyName=mubadalacapital.ae</x:v>
+      <x:c r="T26" s="14" t="str">
+        <x:v>https://www.mubadalacapital.ae/</x:v>
+      </x:c>
+      <x:c r="U26" s="14" t="str">
+        <x:v>https://www.decypha.com/en/investment/public/Mubadala-Capital-149029</x:v>
+      </x:c>
+      <x:c r="V26" s="14" t="str">
+        <x:v>https://www.mubadalacapital.ae/</x:v>
       </x:c>
       <x:c r="W26" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -11624,13 +11036,11 @@
       <x:c r="K27" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L27" s="14" t="e">
-        <x:f>HYPERLINK("https://salicainvestments.com","salicainvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://salicainvestments.com, friendlyName=salicainvestments.com</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="e">
-        <x:f>HYPERLINK("https://salicainvestments.com/contact/","salicainvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://salicainvestments.com/contact/, friendlyName=salicainvestments.com</x:v>
+      <x:c r="L27" s="14" t="str">
+        <x:v>https://salicainvestments.com</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="str">
+        <x:v>https://salicainvestments.com/contact/</x:v>
       </x:c>
       <x:c r="N27" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11648,9 +11058,8 @@
       <x:c r="S27" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T27" s="14" t="e">
-        <x:f>HYPERLINK("https://salicainvestments.com/contact/","salicainvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://salicainvestments.com/contact/, friendlyName=salicainvestments.com</x:v>
+      <x:c r="T27" s="14" t="str">
+        <x:v>https://salicainvestments.com/contact/</x:v>
       </x:c>
       <x:c r="U27" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11699,13 +11108,11 @@
       <x:c r="K28" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L28" s="14" t="e">
-        <x:f>HYPERLINK("https://tvmcapitalhealthcare.com","tvmcapitalhealthcare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tvmcapitalhealthcare.com, friendlyName=tvmcapitalhealthcare.com</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="e">
-        <x:f>HYPERLINK("https://tvmcapitalhealthcare.com/contact/","tvmcapitalhealthcare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tvmcapitalhealthcare.com/contact/, friendlyName=tvmcapitalhealthcare.com</x:v>
+      <x:c r="L28" s="14" t="str">
+        <x:v>https://tvmcapitalhealthcare.com</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="str">
+        <x:v>https://tvmcapitalhealthcare.com/contact/</x:v>
       </x:c>
       <x:c r="N28" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11723,16 +11130,14 @@
       <x:c r="S28" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T28" s="14" t="e">
-        <x:f>HYPERLINK("https://tvmcapitalhealthcare.com/contact/","tvmcapitalhealthcare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tvmcapitalhealthcare.com/contact/, friendlyName=tvmcapitalhealthcare.com</x:v>
+      <x:c r="T28" s="14" t="str">
+        <x:v>https://tvmcapitalhealthcare.com/contact/</x:v>
       </x:c>
       <x:c r="U28" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V28" s="14" t="e">
-        <x:f>HYPERLINK("https://tvmcapitalhealthcare.com/contact/","tvmcapitalhealthcare.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://tvmcapitalhealthcare.com/contact/, friendlyName=tvmcapitalhealthcare.com</x:v>
+      <x:c r="V28" s="14" t="str">
+        <x:v>https://tvmcapitalhealthcare.com/contact/</x:v>
       </x:c>
       <x:c r="W28" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11775,13 +11180,11 @@
       <x:c r="K29" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L29" s="14" t="e">
-        <x:f>HYPERLINK("https://annexinvestments.com","annexinvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://annexinvestments.com, friendlyName=annexinvestments.com</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="e">
-        <x:f>HYPERLINK("https://annexinvestments.com/","annexinvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://annexinvestments.com/, friendlyName=annexinvestments.com</x:v>
+      <x:c r="L29" s="14" t="str">
+        <x:v>https://annexinvestments.com</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="str">
+        <x:v>https://annexinvestments.com/</x:v>
       </x:c>
       <x:c r="N29" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11799,13 +11202,11 @@
       <x:c r="S29" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T29" s="14" t="e">
-        <x:f>HYPERLINK("https://annexinvestments.com/","annexinvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://annexinvestments.com/, friendlyName=annexinvestments.com</x:v>
-      </x:c>
-      <x:c r="U29" s="14" t="e">
-        <x:f>HYPERLINK("https://annexinvestments.com/","annexinvestments.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://annexinvestments.com/, friendlyName=annexinvestments.com</x:v>
+      <x:c r="T29" s="14" t="str">
+        <x:v>https://annexinvestments.com/</x:v>
+      </x:c>
+      <x:c r="U29" s="14" t="str">
+        <x:v>https://annexinvestments.com/</x:v>
       </x:c>
       <x:c r="V29" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11851,13 +11252,11 @@
       <x:c r="K30" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L30" s="14" t="e">
-        <x:f>HYPERLINK("https://byld.vc","byld.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://byld.vc, friendlyName=byld.vc</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.byld.vc/","byld.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.byld.vc/, friendlyName=byld.vc</x:v>
+      <x:c r="L30" s="14" t="str">
+        <x:v>https://byld.vc</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="str">
+        <x:v>https://www.byld.vc/</x:v>
       </x:c>
       <x:c r="N30" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11875,13 +11274,11 @@
       <x:c r="S30" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.byld.vc/","byld.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.byld.vc/, friendlyName=byld.vc</x:v>
-      </x:c>
-      <x:c r="U30" s="14" t="e">
-        <x:f>HYPERLINK("https://www.byld.vc/privacy","byld.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.byld.vc/privacy, friendlyName=byld.vc</x:v>
+      <x:c r="T30" s="14" t="str">
+        <x:v>https://www.byld.vc/</x:v>
+      </x:c>
+      <x:c r="U30" s="14" t="str">
+        <x:v>https://www.byld.vc/privacy</x:v>
       </x:c>
       <x:c r="V30" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -11927,13 +11324,11 @@
       <x:c r="K31" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L31" s="14" t="e">
-        <x:f>HYPERLINK("https://leo.capital","leo.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://leo.capital, friendlyName=leo.capital</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="e">
-        <x:f>HYPERLINK("https://leo.capital/","leo.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://leo.capital/, friendlyName=leo.capital</x:v>
+      <x:c r="L31" s="14" t="str">
+        <x:v>https://leo.capital</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="str">
+        <x:v>https://leo.capital/</x:v>
       </x:c>
       <x:c r="N31" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -11953,9 +11348,8 @@
       <x:c r="S31" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T31" s="14" t="e">
-        <x:f>HYPERLINK("https://leo.capital/","leo.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://leo.capital/, friendlyName=leo.capital</x:v>
+      <x:c r="T31" s="14" t="str">
+        <x:v>https://leo.capital/</x:v>
       </x:c>
       <x:c r="U31" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12004,13 +11398,11 @@
       <x:c r="K32" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L32" s="14" t="e">
-        <x:f>HYPERLINK("https://partechpartners.com","partechpartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://partechpartners.com, friendlyName=partechpartners.com</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="e">
-        <x:f>HYPERLINK("https://partechpartners.com/contact","partechpartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://partechpartners.com/contact, friendlyName=partechpartners.com</x:v>
+      <x:c r="L32" s="14" t="str">
+        <x:v>https://partechpartners.com</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="str">
+        <x:v>https://partechpartners.com/contact</x:v>
       </x:c>
       <x:c r="N32" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12030,9 +11422,8 @@
       <x:c r="S32" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T32" s="14" t="e">
-        <x:f>HYPERLINK("https://partechpartners.com/","partechpartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://partechpartners.com/, friendlyName=partechpartners.com</x:v>
+      <x:c r="T32" s="14" t="str">
+        <x:v>https://partechpartners.com/</x:v>
       </x:c>
       <x:c r="U32" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12081,13 +11472,11 @@
       <x:c r="K33" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L33" s="14" t="e">
-        <x:f>HYPERLINK("https://whitestarcapital.com","whitestarcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://whitestarcapital.com, friendlyName=whitestarcapital.com</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="e">
-        <x:f>HYPERLINK("https://whitestarcapital.com/team/","whitestarcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://whitestarcapital.com/team/, friendlyName=whitestarcapital.com</x:v>
+      <x:c r="L33" s="14" t="str">
+        <x:v>https://whitestarcapital.com</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="str">
+        <x:v>https://whitestarcapital.com/team/</x:v>
       </x:c>
       <x:c r="N33" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12105,13 +11494,11 @@
       <x:c r="S33" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T33" s="14" t="e">
-        <x:f>HYPERLINK("https://whitestarcapital.com/team/","whitestarcapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://whitestarcapital.com/team/, friendlyName=whitestarcapital.com</x:v>
-      </x:c>
-      <x:c r="U33" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/white-star-capital","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/white-star-capital, friendlyName=crunchbase.com</x:v>
+      <x:c r="T33" s="14" t="str">
+        <x:v>https://whitestarcapital.com/team/</x:v>
+      </x:c>
+      <x:c r="U33" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/white-star-capital</x:v>
       </x:c>
       <x:c r="V33" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12157,13 +11544,11 @@
       <x:c r="K34" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L34" s="14" t="e">
-        <x:f>HYPERLINK("https://raivencapital.com","raivencapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://raivencapital.com, friendlyName=raivencapital.com</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="e">
-        <x:f>HYPERLINK("https://raivencapital.com/","raivencapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://raivencapital.com/, friendlyName=raivencapital.com</x:v>
+      <x:c r="L34" s="14" t="str">
+        <x:v>https://raivencapital.com</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="str">
+        <x:v>https://raivencapital.com/</x:v>
       </x:c>
       <x:c r="N34" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12181,9 +11566,8 @@
       <x:c r="S34" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T34" s="14" t="e">
-        <x:f>HYPERLINK("https://raivencapital.com/","raivencapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://raivencapital.com/, friendlyName=raivencapital.com</x:v>
+      <x:c r="T34" s="14" t="str">
+        <x:v>https://raivencapital.com/</x:v>
       </x:c>
       <x:c r="U34" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12232,13 +11616,11 @@
       <x:c r="K35" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L35" s="14" t="e">
-        <x:f>HYPERLINK("https://klumiventures.com","klumiventures.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://klumiventures.com, friendlyName=klumiventures.com</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="e">
-        <x:f>HYPERLINK("https://www.klumiventures.com/contact","klumiventures.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.klumiventures.com/contact, friendlyName=klumiventures.com</x:v>
+      <x:c r="L35" s="14" t="str">
+        <x:v>https://klumiventures.com</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="str">
+        <x:v>https://www.klumiventures.com/contact</x:v>
       </x:c>
       <x:c r="N35" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12256,13 +11638,11 @@
       <x:c r="S35" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T35" s="14" t="e">
-        <x:f>HYPERLINK("https://www.klumiventures.com/contact","klumiventures.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.klumiventures.com/contact, friendlyName=klumiventures.com</x:v>
-      </x:c>
-      <x:c r="U35" s="14" t="e">
-        <x:f>HYPERLINK("https://www.klumiventures.com/contact","klumiventures.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.klumiventures.com/contact, friendlyName=klumiventures.com</x:v>
+      <x:c r="T35" s="14" t="str">
+        <x:v>https://www.klumiventures.com/contact</x:v>
+      </x:c>
+      <x:c r="U35" s="14" t="str">
+        <x:v>https://www.klumiventures.com/contact</x:v>
       </x:c>
       <x:c r="V35" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12308,13 +11688,11 @@
       <x:c r="K36" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L36" s="14" t="e">
-        <x:f>HYPERLINK("https://hashgraphvc.com","hashgraphvc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hashgraphvc.com, friendlyName=hashgraphvc.com</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="e">
-        <x:f>HYPERLINK("https://hashgraphvc.com/","hashgraphvc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hashgraphvc.com/, friendlyName=hashgraphvc.com</x:v>
+      <x:c r="L36" s="14" t="str">
+        <x:v>https://hashgraphvc.com</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="str">
+        <x:v>https://hashgraphvc.com/</x:v>
       </x:c>
       <x:c r="N36" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12332,13 +11710,11 @@
       <x:c r="S36" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T36" s="14" t="e">
-        <x:f>HYPERLINK("https://hashgraphvc.com/","hashgraphvc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hashgraphvc.com/, friendlyName=hashgraphvc.com</x:v>
-      </x:c>
-      <x:c r="U36" s="14" t="e">
-        <x:f>HYPERLINK("https://hashgraphvc.com/privacy-policy/","hashgraphvc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hashgraphvc.com/privacy-policy/, friendlyName=hashgraphvc.com</x:v>
+      <x:c r="T36" s="14" t="str">
+        <x:v>https://hashgraphvc.com/</x:v>
+      </x:c>
+      <x:c r="U36" s="14" t="str">
+        <x:v>https://hashgraphvc.com/privacy-policy/</x:v>
       </x:c>
       <x:c r="V36" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12384,13 +11760,11 @@
       <x:c r="K37" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L37" s="14" t="e">
-        <x:f>HYPERLINK("https://homegrowncpg.com","homegrowncpg.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://homegrowncpg.com, friendlyName=homegrowncpg.com</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="e">
-        <x:f>HYPERLINK("https://www.homegrowncpg.com/","homegrowncpg.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.homegrowncpg.com/, friendlyName=homegrowncpg.com</x:v>
+      <x:c r="L37" s="14" t="str">
+        <x:v>https://homegrowncpg.com</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="str">
+        <x:v>https://www.homegrowncpg.com/</x:v>
       </x:c>
       <x:c r="N37" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12408,13 +11782,11 @@
       <x:c r="S37" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T37" s="14" t="e">
-        <x:f>HYPERLINK("https://www.homegrowncpg.com/","homegrowncpg.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.homegrowncpg.com/, friendlyName=homegrowncpg.com</x:v>
-      </x:c>
-      <x:c r="U37" s="14" t="e">
-        <x:f>HYPERLINK("https://www.homegrowncpg.com/","homegrowncpg.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.homegrowncpg.com/, friendlyName=homegrowncpg.com</x:v>
+      <x:c r="T37" s="14" t="str">
+        <x:v>https://www.homegrowncpg.com/</x:v>
+      </x:c>
+      <x:c r="U37" s="14" t="str">
+        <x:v>https://www.homegrowncpg.com/</x:v>
       </x:c>
       <x:c r="V37" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12460,13 +11832,11 @@
       <x:c r="K38" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L38" s="14" t="e">
-        <x:f>HYPERLINK("https://fikr.vc","fikr.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fikr.vc, friendlyName=fikr.vc</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.fikr.vc/","fikr.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.fikr.vc/, friendlyName=fikr.vc</x:v>
+      <x:c r="L38" s="14" t="str">
+        <x:v>https://fikr.vc</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="str">
+        <x:v>https://www.fikr.vc/</x:v>
       </x:c>
       <x:c r="N38" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12484,9 +11854,8 @@
       <x:c r="S38" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T38" s="14" t="e">
-        <x:f>HYPERLINK("https://www.fikr.vc/","fikr.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.fikr.vc/, friendlyName=fikr.vc</x:v>
+      <x:c r="T38" s="14" t="str">
+        <x:v>https://www.fikr.vc/</x:v>
       </x:c>
       <x:c r="U38" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12535,13 +11904,11 @@
       <x:c r="K39" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L39" s="14" t="e">
-        <x:f>HYPERLINK("https://21vc.com","21vc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://21vc.com, friendlyName=21vc.com</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="e">
-        <x:f>HYPERLINK("https://www.21vc.com/","21vc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.21vc.com/, friendlyName=21vc.com</x:v>
+      <x:c r="L39" s="14" t="str">
+        <x:v>https://21vc.com</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="str">
+        <x:v>https://www.21vc.com/</x:v>
       </x:c>
       <x:c r="N39" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12559,13 +11926,11 @@
       <x:c r="S39" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T39" s="14" t="e">
-        <x:f>HYPERLINK("https://www.21vc.com/","21vc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.21vc.com/, friendlyName=21vc.com</x:v>
-      </x:c>
-      <x:c r="U39" s="14" t="e">
-        <x:f>HYPERLINK("https://www.21vc.com/","21vc.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.21vc.com/, friendlyName=21vc.com</x:v>
+      <x:c r="T39" s="14" t="str">
+        <x:v>https://www.21vc.com/</x:v>
+      </x:c>
+      <x:c r="U39" s="14" t="str">
+        <x:v>https://www.21vc.com/</x:v>
       </x:c>
       <x:c r="V39" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12611,13 +11976,11 @@
       <x:c r="K40" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L40" s="14" t="e">
-        <x:f>HYPERLINK("https://yellowfin.vc","yellowfin.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yellowfin.vc, friendlyName=yellowfin.vc</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="e">
-        <x:f>HYPERLINK("https://yellowfin.vc/","yellowfin.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yellowfin.vc/, friendlyName=yellowfin.vc</x:v>
+      <x:c r="L40" s="14" t="str">
+        <x:v>https://yellowfin.vc</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="str">
+        <x:v>https://yellowfin.vc/</x:v>
       </x:c>
       <x:c r="N40" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12635,13 +11998,11 @@
       <x:c r="S40" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T40" s="14" t="e">
-        <x:f>HYPERLINK("https://yellowfin.vc/","yellowfin.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yellowfin.vc/, friendlyName=yellowfin.vc</x:v>
-      </x:c>
-      <x:c r="U40" s="14" t="e">
-        <x:f>HYPERLINK("https://yellowfin.vc/","yellowfin.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://yellowfin.vc/, friendlyName=yellowfin.vc</x:v>
+      <x:c r="T40" s="14" t="str">
+        <x:v>https://yellowfin.vc/</x:v>
+      </x:c>
+      <x:c r="U40" s="14" t="str">
+        <x:v>https://yellowfin.vc/</x:v>
       </x:c>
       <x:c r="V40" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12687,13 +12048,11 @@
       <x:c r="K41" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L41" s="14" t="e">
-        <x:f>HYPERLINK("https://taucapital.ae","taucapital.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://taucapital.ae, friendlyName=taucapital.ae</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095, friendlyName=adgm.com</x:v>
+      <x:c r="L41" s="14" t="str">
+        <x:v>https://taucapital.ae</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095</x:v>
       </x:c>
       <x:c r="N41" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12713,9 +12072,8 @@
       <x:c r="S41" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T41" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095, friendlyName=adgm.com</x:v>
+      <x:c r="T41" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/tau-capital-limited-240095</x:v>
       </x:c>
       <x:c r="U41" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12764,13 +12122,11 @@
       <x:c r="K42" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L42" s="14" t="e">
-        <x:f>HYPERLINK("https://generalatlantic.com","generalatlantic.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://generalatlantic.com, friendlyName=generalatlantic.com</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="e">
-        <x:f>HYPERLINK("https://www.generalatlantic.com/contact/","generalatlantic.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.generalatlantic.com/contact/, friendlyName=generalatlantic.com</x:v>
+      <x:c r="L42" s="14" t="str">
+        <x:v>https://generalatlantic.com</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="str">
+        <x:v>https://www.generalatlantic.com/contact/</x:v>
       </x:c>
       <x:c r="N42" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12790,9 +12146,8 @@
       <x:c r="S42" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T42" s="14" t="e">
-        <x:f>HYPERLINK("https://www.generalatlantic.com/contact/","generalatlantic.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.generalatlantic.com/contact/, friendlyName=generalatlantic.com</x:v>
+      <x:c r="T42" s="14" t="str">
+        <x:v>https://www.generalatlantic.com/contact/</x:v>
       </x:c>
       <x:c r="U42" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12841,13 +12196,11 @@
       <x:c r="K43" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L43" s="14" t="e">
-        <x:f>HYPERLINK("https://visionfund.com","visionfund.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://visionfund.com, friendlyName=visionfund.com</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="e">
-        <x:f>HYPERLINK("https://visionfund.com/contact","visionfund.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://visionfund.com/contact, friendlyName=visionfund.com</x:v>
+      <x:c r="L43" s="14" t="str">
+        <x:v>https://visionfund.com</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="str">
+        <x:v>https://visionfund.com/contact</x:v>
       </x:c>
       <x:c r="N43" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12867,9 +12220,8 @@
       <x:c r="S43" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T43" s="14" t="e">
-        <x:f>HYPERLINK("https://visionfund.com/contact","visionfund.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://visionfund.com/contact, friendlyName=visionfund.com</x:v>
+      <x:c r="T43" s="14" t="str">
+        <x:v>https://visionfund.com/contact</x:v>
       </x:c>
       <x:c r="U43" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12918,13 +12270,11 @@
       <x:c r="K44" s="6" t="str">
         <x:v>تمويل / مؤسسون</x:v>
       </x:c>
-      <x:c r="L44" s="14" t="e">
-        <x:f>HYPERLINK("https://msanovo.com","msanovo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://msanovo.com, friendlyName=msanovo.com</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="e">
-        <x:f>HYPERLINK("https://msanovo.com/contact/","msanovo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://msanovo.com/contact/, friendlyName=msanovo.com</x:v>
+      <x:c r="L44" s="14" t="str">
+        <x:v>https://msanovo.com</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="str">
+        <x:v>https://msanovo.com/contact/</x:v>
       </x:c>
       <x:c r="N44" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -12942,13 +12292,11 @@
       <x:c r="S44" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T44" s="14" t="e">
-        <x:f>HYPERLINK("https://msanovo.com/contact/","msanovo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://msanovo.com/contact/, friendlyName=msanovo.com</x:v>
-      </x:c>
-      <x:c r="U44" s="14" t="e">
-        <x:f>HYPERLINK("https://msanovo.com/contact/","msanovo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://msanovo.com/contact/, friendlyName=msanovo.com</x:v>
+      <x:c r="T44" s="14" t="str">
+        <x:v>https://msanovo.com/contact/</x:v>
+      </x:c>
+      <x:c r="U44" s="14" t="str">
+        <x:v>https://msanovo.com/contact/</x:v>
       </x:c>
       <x:c r="V44" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -12994,13 +12342,11 @@
       <x:c r="K45" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L45" s="14" t="e">
-        <x:f>HYPERLINK("https://hashed.com","hashed.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hashed.com, friendlyName=hashed.com</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hashed.com/about/","hashed.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hashed.com/about/, friendlyName=hashed.com</x:v>
+      <x:c r="L45" s="14" t="str">
+        <x:v>https://hashed.com</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="str">
+        <x:v>https://www.hashed.com/about/</x:v>
       </x:c>
       <x:c r="N45" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13018,13 +12364,11 @@
       <x:c r="S45" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hashed.com/about/","hashed.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hashed.com/about/, friendlyName=hashed.com</x:v>
-      </x:c>
-      <x:c r="U45" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adgm.com/public-registers/fsra/firms/financial-firms/hashed-global-management-limited-250077","adgm.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adgm.com/public-registers/fsra/firms/financial-firms/hashed-global-management-limited-250077, friendlyName=adgm.com</x:v>
+      <x:c r="T45" s="14" t="str">
+        <x:v>https://www.hashed.com/about/</x:v>
+      </x:c>
+      <x:c r="U45" s="14" t="str">
+        <x:v>https://www.adgm.com/public-registers/fsra/firms/financial-firms/hashed-global-management-limited-250077</x:v>
       </x:c>
       <x:c r="V45" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13070,13 +12414,11 @@
       <x:c r="K46" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L46" s="14" t="e">
-        <x:f>HYPERLINK("https://constructor.capital","constructor.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://constructor.capital, friendlyName=constructor.capital</x:v>
-      </x:c>
-      <x:c r="M46" s="14" t="e">
-        <x:f>HYPERLINK("https://constructor.capital/news/constructor-capital-2025-recap-team-growth-27-portfolio-companies-supported-and-a-new-series-a-investment-in-vitrealab","constructor.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://constructor.capital/news/constructor-capital-2025-recap-team-growth-27-portfolio-companies-supported-and-a-new-series-a-investment-in-vitrealab, friendlyName=constructor.capital</x:v>
+      <x:c r="L46" s="14" t="str">
+        <x:v>https://constructor.capital</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="str">
+        <x:v>https://constructor.capital/news/constructor-capital-2025-recap-team-growth-27-portfolio-companies-supported-and-a-new-series-a-investment-in-vitrealab</x:v>
       </x:c>
       <x:c r="N46" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13094,9 +12436,8 @@
       <x:c r="S46" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T46" s="14" t="e">
-        <x:f>HYPERLINK("https://constructor.capital/","constructor.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://constructor.capital/, friendlyName=constructor.capital</x:v>
+      <x:c r="T46" s="14" t="str">
+        <x:v>https://constructor.capital/</x:v>
       </x:c>
       <x:c r="U46" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13145,13 +12486,11 @@
       <x:c r="K47" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L47" s="14" t="e">
-        <x:f>HYPERLINK("https://212.vc","212.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://212.vc, friendlyName=212.vc</x:v>
-      </x:c>
-      <x:c r="M47" s="14" t="e">
-        <x:f>HYPERLINK("https://212.vc/contact/","212.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://212.vc/contact/, friendlyName=212.vc</x:v>
+      <x:c r="L47" s="14" t="str">
+        <x:v>https://212.vc</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="str">
+        <x:v>https://212.vc/contact/</x:v>
       </x:c>
       <x:c r="N47" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13169,13 +12508,11 @@
       <x:c r="S47" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T47" s="14" t="e">
-        <x:f>HYPERLINK("https://212.vc/contact/","212.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://212.vc/contact/, friendlyName=212.vc</x:v>
-      </x:c>
-      <x:c r="U47" s="14" t="e">
-        <x:f>HYPERLINK("https://212.vc/contact/","212.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://212.vc/contact/, friendlyName=212.vc</x:v>
+      <x:c r="T47" s="14" t="str">
+        <x:v>https://212.vc/contact/</x:v>
+      </x:c>
+      <x:c r="U47" s="14" t="str">
+        <x:v>https://212.vc/contact/</x:v>
       </x:c>
       <x:c r="V47" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13221,13 +12558,11 @@
       <x:c r="K48" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L48" s="14" t="e">
-        <x:f>HYPERLINK("https://ajeej.com","ajeej.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ajeej.com, friendlyName=ajeej.com</x:v>
-      </x:c>
-      <x:c r="M48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ajeej.com/contact","ajeej.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ajeej.com/contact, friendlyName=ajeej.com</x:v>
+      <x:c r="L48" s="14" t="str">
+        <x:v>https://ajeej.com</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="str">
+        <x:v>https://www.ajeej.com/contact</x:v>
       </x:c>
       <x:c r="N48" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13245,17 +12580,14 @@
       <x:c r="S48" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ajeej.com/contact","ajeej.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ajeej.com/contact, friendlyName=ajeej.com</x:v>
-      </x:c>
-      <x:c r="U48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ajeej.com/contact","ajeej.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ajeej.com/contact, friendlyName=ajeej.com</x:v>
-      </x:c>
-      <x:c r="V48" s="14" t="e">
-        <x:f>HYPERLINK("https://www.ajeej.com/contact","ajeej.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.ajeej.com/contact, friendlyName=ajeej.com</x:v>
+      <x:c r="T48" s="14" t="str">
+        <x:v>https://www.ajeej.com/contact</x:v>
+      </x:c>
+      <x:c r="U48" s="14" t="str">
+        <x:v>https://www.ajeej.com/contact</x:v>
+      </x:c>
+      <x:c r="V48" s="14" t="str">
+        <x:v>https://www.ajeej.com/contact</x:v>
       </x:c>
       <x:c r="W48" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -13298,13 +12630,11 @@
       <x:c r="K49" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L49" s="14" t="e">
-        <x:f>HYPERLINK("https://phoenician.vc","phoenician.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://phoenician.vc, friendlyName=phoenician.vc</x:v>
-      </x:c>
-      <x:c r="M49" s="14" t="e">
-        <x:f>HYPERLINK("https://www.phoenician.vc/contact","phoenician.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.phoenician.vc/contact, friendlyName=phoenician.vc</x:v>
+      <x:c r="L49" s="14" t="str">
+        <x:v>https://phoenician.vc</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="str">
+        <x:v>https://www.phoenician.vc/contact</x:v>
       </x:c>
       <x:c r="N49" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13322,17 +12652,14 @@
       <x:c r="S49" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T49" s="14" t="e">
-        <x:f>HYPERLINK("https://www.phoenician.vc/contact","phoenician.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.phoenician.vc/contact, friendlyName=phoenician.vc</x:v>
-      </x:c>
-      <x:c r="U49" s="14" t="e">
-        <x:f>HYPERLINK("https://www.phoenician.vc/contact","phoenician.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.phoenician.vc/contact, friendlyName=phoenician.vc</x:v>
-      </x:c>
-      <x:c r="V49" s="14" t="e">
-        <x:f>HYPERLINK("https://www.phoenician.vc/contact","phoenician.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.phoenician.vc/contact, friendlyName=phoenician.vc</x:v>
+      <x:c r="T49" s="14" t="str">
+        <x:v>https://www.phoenician.vc/contact</x:v>
+      </x:c>
+      <x:c r="U49" s="14" t="str">
+        <x:v>https://www.phoenician.vc/contact</x:v>
+      </x:c>
+      <x:c r="V49" s="14" t="str">
+        <x:v>https://www.phoenician.vc/contact</x:v>
       </x:c>
       <x:c r="W49" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -13375,13 +12702,11 @@
       <x:c r="K50" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L50" s="14" t="e">
-        <x:f>HYPERLINK("https://primalcapital.io","primalcapital.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://primalcapital.io, friendlyName=primalcapital.io</x:v>
-      </x:c>
-      <x:c r="M50" s="14" t="e">
-        <x:f>HYPERLINK("https://www.primalcapital.io/","primalcapital.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.primalcapital.io/, friendlyName=primalcapital.io</x:v>
+      <x:c r="L50" s="14" t="str">
+        <x:v>https://primalcapital.io</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="str">
+        <x:v>https://www.primalcapital.io/</x:v>
       </x:c>
       <x:c r="N50" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13399,13 +12724,11 @@
       <x:c r="S50" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T50" s="14" t="e">
-        <x:f>HYPERLINK("https://www.primalcapital.io/","primalcapital.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.primalcapital.io/, friendlyName=primalcapital.io</x:v>
-      </x:c>
-      <x:c r="U50" s="14" t="e">
-        <x:f>HYPERLINK("https://www.primalcapital.io/","primalcapital.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.primalcapital.io/, friendlyName=primalcapital.io</x:v>
+      <x:c r="T50" s="14" t="str">
+        <x:v>https://www.primalcapital.io/</x:v>
+      </x:c>
+      <x:c r="U50" s="14" t="str">
+        <x:v>https://www.primalcapital.io/</x:v>
       </x:c>
       <x:c r="V50" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13451,13 +12774,11 @@
       <x:c r="K51" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="L51" s="14" t="e">
-        <x:f>HYPERLINK("https://lunarapartners.com","lunarapartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://lunarapartners.com, friendlyName=lunarapartners.com</x:v>
-      </x:c>
-      <x:c r="M51" s="14" t="e">
-        <x:f>HYPERLINK("https://www.lunarapartners.com/contact.html","lunarapartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.lunarapartners.com/contact.html, friendlyName=lunarapartners.com</x:v>
+      <x:c r="L51" s="14" t="str">
+        <x:v>https://lunarapartners.com</x:v>
+      </x:c>
+      <x:c r="M51" s="14" t="str">
+        <x:v>https://www.lunarapartners.com/contact.html</x:v>
       </x:c>
       <x:c r="N51" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13475,13 +12796,11 @@
       <x:c r="S51" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T51" s="14" t="e">
-        <x:f>HYPERLINK("https://www.lunarapartners.com/contact.html","lunarapartners.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.lunarapartners.com/contact.html, friendlyName=lunarapartners.com</x:v>
-      </x:c>
-      <x:c r="U51" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/lunara-partners","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/lunara-partners, friendlyName=crunchbase.com</x:v>
+      <x:c r="T51" s="14" t="str">
+        <x:v>https://www.lunarapartners.com/contact.html</x:v>
+      </x:c>
+      <x:c r="U51" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/lunara-partners</x:v>
       </x:c>
       <x:c r="V51" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13527,13 +12846,11 @@
       <x:c r="K52" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L52" s="14" t="e">
-        <x:f>HYPERLINK("https://pininvest.co","pininvest.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://pininvest.co, friendlyName=pininvest.co</x:v>
-      </x:c>
-      <x:c r="M52" s="14" t="e">
-        <x:f>HYPERLINK("https://www.linkedin.com/company/pin-invest","linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.linkedin.com/company/pin-invest, friendlyName=linkedin.com</x:v>
+      <x:c r="L52" s="14" t="str">
+        <x:v>https://pininvest.co</x:v>
+      </x:c>
+      <x:c r="M52" s="14" t="str">
+        <x:v>https://www.linkedin.com/company/pin-invest</x:v>
       </x:c>
       <x:c r="N52" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13553,9 +12870,8 @@
       <x:c r="S52" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T52" s="14" t="e">
-        <x:f>HYPERLINK("https://www.linkedin.com/company/pin-invest","linkedin.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.linkedin.com/company/pin-invest, friendlyName=linkedin.com</x:v>
+      <x:c r="T52" s="14" t="str">
+        <x:v>https://www.linkedin.com/company/pin-invest</x:v>
       </x:c>
       <x:c r="U52" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13604,13 +12920,11 @@
       <x:c r="K53" s="6" t="str">
         <x:v>شراكات / استفسارات أعمال</x:v>
       </x:c>
-      <x:c r="L53" s="14" t="e">
-        <x:f>HYPERLINK("https://venturewave.capital","venturewave.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://venturewave.capital, friendlyName=venturewave.capital</x:v>
-      </x:c>
-      <x:c r="M53" s="14" t="e">
-        <x:f>HYPERLINK("https://venturewave.capital/get-in-touch/","venturewave.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://venturewave.capital/get-in-touch/, friendlyName=venturewave.capital</x:v>
+      <x:c r="L53" s="14" t="str">
+        <x:v>https://venturewave.capital</x:v>
+      </x:c>
+      <x:c r="M53" s="14" t="str">
+        <x:v>https://venturewave.capital/get-in-touch/</x:v>
       </x:c>
       <x:c r="N53" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13628,13 +12942,11 @@
       <x:c r="S53" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T53" s="14" t="e">
-        <x:f>HYPERLINK("https://venturewave.capital/get-in-touch/","venturewave.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://venturewave.capital/get-in-touch/, friendlyName=venturewave.capital</x:v>
-      </x:c>
-      <x:c r="U53" s="14" t="e">
-        <x:f>HYPERLINK("https://venturewave.capital/get-in-touch/","venturewave.capital")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://venturewave.capital/get-in-touch/, friendlyName=venturewave.capital</x:v>
+      <x:c r="T53" s="14" t="str">
+        <x:v>https://venturewave.capital/get-in-touch/</x:v>
+      </x:c>
+      <x:c r="U53" s="14" t="str">
+        <x:v>https://venturewave.capital/get-in-touch/</x:v>
       </x:c>
       <x:c r="V53" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13680,13 +12992,11 @@
       <x:c r="K54" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L54" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaiangelinvestors.me","dubaiangelinvestors.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaiangelinvestors.me, friendlyName=dubaiangelinvestors.me</x:v>
-      </x:c>
-      <x:c r="M54" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiangelinvestors.me/application","dubaiangelinvestors.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiangelinvestors.me/application, friendlyName=dubaiangelinvestors.me</x:v>
+      <x:c r="L54" s="14" t="str">
+        <x:v>https://dubaiangelinvestors.me</x:v>
+      </x:c>
+      <x:c r="M54" s="14" t="str">
+        <x:v>https://www.dubaiangelinvestors.me/application</x:v>
       </x:c>
       <x:c r="N54" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13704,13 +13014,11 @@
       <x:c r="S54" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T54" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiangelinvestors.me/application","dubaiangelinvestors.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiangelinvestors.me/application, friendlyName=dubaiangelinvestors.me</x:v>
-      </x:c>
-      <x:c r="U54" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiangelinvestors.me/application","dubaiangelinvestors.me")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiangelinvestors.me/application, friendlyName=dubaiangelinvestors.me</x:v>
+      <x:c r="T54" s="14" t="str">
+        <x:v>https://www.dubaiangelinvestors.me/application</x:v>
+      </x:c>
+      <x:c r="U54" s="14" t="str">
+        <x:v>https://www.dubaiangelinvestors.me/application</x:v>
       </x:c>
       <x:c r="V54" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13756,13 +13064,11 @@
       <x:c r="K55" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L55" s="14" t="e">
-        <x:f>HYPERLINK("https://emiratesangels.org","emiratesangels.org")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emiratesangels.org, friendlyName=emiratesangels.org</x:v>
-      </x:c>
-      <x:c r="M55" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=com.emirates.angels","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=com.emirates.angels, friendlyName=play.google.com</x:v>
+      <x:c r="L55" s="14" t="str">
+        <x:v>https://emiratesangels.org</x:v>
+      </x:c>
+      <x:c r="M55" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=com.emirates.angels</x:v>
       </x:c>
       <x:c r="N55" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13782,13 +13088,11 @@
       <x:c r="S55" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T55" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=com.emirates.angels","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=com.emirates.angels, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="U55" s="14" t="e">
-        <x:f>HYPERLINK("https://www.setupinabudhabi.ae/wp-content/uploads/2025/08/ADSMEHubReport2021.pdf","setupinabudhabi.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.setupinabudhabi.ae/wp-content/uploads/2025/08/ADSMEHubReport2021.pdf, friendlyName=setupinabudhabi.ae</x:v>
+      <x:c r="T55" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=com.emirates.angels</x:v>
+      </x:c>
+      <x:c r="U55" s="14" t="str">
+        <x:v>https://www.setupinabudhabi.ae/wp-content/uploads/2025/08/ADSMEHubReport2021.pdf</x:v>
       </x:c>
       <x:c r="V55" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13834,13 +13138,11 @@
       <x:c r="K56" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L56" s="14" t="e">
-        <x:f>HYPERLINK("https://angelspark.net","angelspark.net")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://angelspark.net, friendlyName=angelspark.net</x:v>
-      </x:c>
-      <x:c r="M56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/angelspark","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/angelspark, friendlyName=crunchbase.com</x:v>
+      <x:c r="L56" s="14" t="str">
+        <x:v>https://angelspark.net</x:v>
+      </x:c>
+      <x:c r="M56" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/angelspark</x:v>
       </x:c>
       <x:c r="N56" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13858,13 +13160,11 @@
       <x:c r="S56" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/angelspark","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/angelspark, friendlyName=crunchbase.com</x:v>
-      </x:c>
-      <x:c r="U56" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crunchbase.com/organization/angelspark","crunchbase.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crunchbase.com/organization/angelspark, friendlyName=crunchbase.com</x:v>
+      <x:c r="T56" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/angelspark</x:v>
+      </x:c>
+      <x:c r="U56" s="14" t="str">
+        <x:v>https://www.crunchbase.com/organization/angelspark</x:v>
       </x:c>
       <x:c r="V56" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13910,13 +13210,11 @@
       <x:c r="K57" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L57" s="14" t="e">
-        <x:f>HYPERLINK("https://sandstorm.vc","sandstorm.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sandstorm.vc, friendlyName=sandstorm.vc</x:v>
-      </x:c>
-      <x:c r="M57" s="14" t="e">
-        <x:f>HYPERLINK("https://sandstorm.vc/sandstorm-vc","sandstorm.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sandstorm.vc/sandstorm-vc, friendlyName=sandstorm.vc</x:v>
+      <x:c r="L57" s="14" t="str">
+        <x:v>https://sandstorm.vc</x:v>
+      </x:c>
+      <x:c r="M57" s="14" t="str">
+        <x:v>https://sandstorm.vc/sandstorm-vc</x:v>
       </x:c>
       <x:c r="N57" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -13934,13 +13232,11 @@
       <x:c r="S57" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T57" s="14" t="e">
-        <x:f>HYPERLINK("https://sandstorm.vc/sandstorm-vc","sandstorm.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sandstorm.vc/sandstorm-vc, friendlyName=sandstorm.vc</x:v>
-      </x:c>
-      <x:c r="U57" s="14" t="e">
-        <x:f>HYPERLINK("https://sandstorm.vc/privacy-policy-1","sandstorm.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sandstorm.vc/privacy-policy-1, friendlyName=sandstorm.vc</x:v>
+      <x:c r="T57" s="14" t="str">
+        <x:v>https://sandstorm.vc/sandstorm-vc</x:v>
+      </x:c>
+      <x:c r="U57" s="14" t="str">
+        <x:v>https://sandstorm.vc/privacy-policy-1</x:v>
       </x:c>
       <x:c r="V57" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -13986,13 +13282,11 @@
       <x:c r="K58" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L58" s="14" t="e">
-        <x:f>HYPERLINK("https://keiretsumena.com","keiretsumena.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://keiretsumena.com, friendlyName=keiretsumena.com</x:v>
-      </x:c>
-      <x:c r="M58" s="14" t="e">
-        <x:f>HYPERLINK("https://keiretsu-forum-mena.odoo.com/contactus","keiretsu-forum-mena.odoo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://keiretsu-forum-mena.odoo.com/contactus, friendlyName=keiretsu-forum-mena.odoo.com</x:v>
+      <x:c r="L58" s="14" t="str">
+        <x:v>https://keiretsumena.com</x:v>
+      </x:c>
+      <x:c r="M58" s="14" t="str">
+        <x:v>https://keiretsu-forum-mena.odoo.com/contactus</x:v>
       </x:c>
       <x:c r="N58" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -14010,13 +13304,11 @@
       <x:c r="S58" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T58" s="14" t="e">
-        <x:f>HYPERLINK("https://keiretsu-forum-mena.odoo.com/contactus","keiretsu-forum-mena.odoo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://keiretsu-forum-mena.odoo.com/contactus, friendlyName=keiretsu-forum-mena.odoo.com</x:v>
-      </x:c>
-      <x:c r="U58" s="14" t="e">
-        <x:f>HYPERLINK("https://keiretsu-forum-mena.odoo.com/contactus","keiretsu-forum-mena.odoo.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://keiretsu-forum-mena.odoo.com/contactus, friendlyName=keiretsu-forum-mena.odoo.com</x:v>
+      <x:c r="T58" s="14" t="str">
+        <x:v>https://keiretsu-forum-mena.odoo.com/contactus</x:v>
+      </x:c>
+      <x:c r="U58" s="14" t="str">
+        <x:v>https://keiretsu-forum-mena.odoo.com/contactus</x:v>
       </x:c>
       <x:c r="V58" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14062,13 +13354,11 @@
       <x:c r="K59" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L59" s="14" t="e">
-        <x:f>HYPERLINK("https://srtip.ae","srtip.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://srtip.ae, friendlyName=srtip.ae</x:v>
-      </x:c>
-      <x:c r="M59" s="14" t="e">
-        <x:f>HYPERLINK("https://srtip.ae/sharjah-business-angels-network/","srtip.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://srtip.ae/sharjah-business-angels-network/, friendlyName=srtip.ae</x:v>
+      <x:c r="L59" s="14" t="str">
+        <x:v>https://srtip.ae</x:v>
+      </x:c>
+      <x:c r="M59" s="14" t="str">
+        <x:v>https://srtip.ae/sharjah-business-angels-network/</x:v>
       </x:c>
       <x:c r="N59" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -14088,9 +13378,8 @@
       <x:c r="S59" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T59" s="14" t="e">
-        <x:f>HYPERLINK("https://srtip.ae/sharjah-business-angels-network/","srtip.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://srtip.ae/sharjah-business-angels-network/, friendlyName=srtip.ae</x:v>
+      <x:c r="T59" s="14" t="str">
+        <x:v>https://srtip.ae/sharjah-business-angels-network/</x:v>
       </x:c>
       <x:c r="U59" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14139,13 +13428,11 @@
       <x:c r="K60" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L60" s="14" t="e">
-        <x:f>HYPERLINK("https://spade.ventures","spade.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://spade.ventures, friendlyName=spade.ventures</x:v>
-      </x:c>
-      <x:c r="M60" s="14" t="e">
-        <x:f>HYPERLINK("https://spade.ventures/","spade.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://spade.ventures/, friendlyName=spade.ventures</x:v>
+      <x:c r="L60" s="14" t="str">
+        <x:v>https://spade.ventures</x:v>
+      </x:c>
+      <x:c r="M60" s="14" t="str">
+        <x:v>https://spade.ventures/</x:v>
       </x:c>
       <x:c r="N60" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -14163,13 +13450,11 @@
       <x:c r="S60" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T60" s="14" t="e">
-        <x:f>HYPERLINK("https://spade.ventures/","spade.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://spade.ventures/, friendlyName=spade.ventures</x:v>
-      </x:c>
-      <x:c r="U60" s="14" t="e">
-        <x:f>HYPERLINK("https://spade.ventures/","spade.ventures")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://spade.ventures/, friendlyName=spade.ventures</x:v>
+      <x:c r="T60" s="14" t="str">
+        <x:v>https://spade.ventures/</x:v>
+      </x:c>
+      <x:c r="U60" s="14" t="str">
+        <x:v>https://spade.ventures/</x:v>
       </x:c>
       <x:c r="V60" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14215,13 +13500,11 @@
       <x:c r="K61" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L61" s="14" t="e">
-        <x:f>HYPERLINK("https://hub71.com","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://hub71.com, friendlyName=hub71.com</x:v>
-      </x:c>
-      <x:c r="M61" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hub71.com/contact","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hub71.com/contact, friendlyName=hub71.com</x:v>
+      <x:c r="L61" s="14" t="str">
+        <x:v>https://hub71.com</x:v>
+      </x:c>
+      <x:c r="M61" s="14" t="str">
+        <x:v>https://www.hub71.com/contact</x:v>
       </x:c>
       <x:c r="N61" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14239,13 +13522,11 @@
       <x:c r="S61" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T61" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hub71.com/contact","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hub71.com/contact, friendlyName=hub71.com</x:v>
-      </x:c>
-      <x:c r="U61" s="14" t="e">
-        <x:f>HYPERLINK("https://www.hub71.com/index.php/program/hub71-plus-digital-assets/form-content","hub71.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.hub71.com/index.php/program/hub71-plus-digital-assets/form-content, friendlyName=hub71.com</x:v>
+      <x:c r="T61" s="14" t="str">
+        <x:v>https://www.hub71.com/contact</x:v>
+      </x:c>
+      <x:c r="U61" s="14" t="str">
+        <x:v>https://www.hub71.com/index.php/program/hub71-plus-digital-assets/form-content</x:v>
       </x:c>
       <x:c r="V61" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14291,13 +13572,11 @@
       <x:c r="K62" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L62" s="14" t="e">
-        <x:f>HYPERLINK("https://sheraa.ae","sheraa.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sheraa.ae, friendlyName=sheraa.ae</x:v>
-      </x:c>
-      <x:c r="M62" s="14" t="e">
-        <x:f>HYPERLINK("https://www.sheraa.ae/contact-us","sheraa.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheraa.ae/contact-us, friendlyName=sheraa.ae</x:v>
+      <x:c r="L62" s="14" t="str">
+        <x:v>https://sheraa.ae</x:v>
+      </x:c>
+      <x:c r="M62" s="14" t="str">
+        <x:v>https://www.sheraa.ae/contact-us</x:v>
       </x:c>
       <x:c r="N62" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14315,17 +13594,14 @@
       <x:c r="S62" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T62" s="14" t="e">
-        <x:f>HYPERLINK("https://www.sheraa.ae/contact-us","sheraa.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheraa.ae/contact-us, friendlyName=sheraa.ae</x:v>
-      </x:c>
-      <x:c r="U62" s="14" t="e">
-        <x:f>HYPERLINK("https://sheraa.ae/meet-our-startups","sheraa.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sheraa.ae/meet-our-startups, friendlyName=sheraa.ae</x:v>
-      </x:c>
-      <x:c r="V62" s="14" t="e">
-        <x:f>HYPERLINK("https://www.sheraa.ae/contact-us","sheraa.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheraa.ae/contact-us, friendlyName=sheraa.ae</x:v>
+      <x:c r="T62" s="14" t="str">
+        <x:v>https://www.sheraa.ae/contact-us</x:v>
+      </x:c>
+      <x:c r="U62" s="14" t="str">
+        <x:v>https://sheraa.ae/meet-our-startups</x:v>
+      </x:c>
+      <x:c r="V62" s="14" t="str">
+        <x:v>https://www.sheraa.ae/contact-us</x:v>
       </x:c>
       <x:c r="W62" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -14368,13 +13644,11 @@
       <x:c r="K63" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L63" s="14" t="e">
-        <x:f>HYPERLINK("https://infive.ae","infive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://infive.ae, friendlyName=infive.ae</x:v>
-      </x:c>
-      <x:c r="M63" s="14" t="e">
-        <x:f>HYPERLINK("https://dic.ae/offerings/in5-centres","dic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dic.ae/offerings/in5-centres, friendlyName=dic.ae</x:v>
+      <x:c r="L63" s="14" t="str">
+        <x:v>https://infive.ae</x:v>
+      </x:c>
+      <x:c r="M63" s="14" t="str">
+        <x:v>https://dic.ae/offerings/in5-centres</x:v>
       </x:c>
       <x:c r="N63" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14392,17 +13666,14 @@
       <x:c r="S63" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T63" s="14" t="e">
-        <x:f>HYPERLINK("https://dic.ae/offerings/in5-centres","dic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dic.ae/offerings/in5-centres, friendlyName=dic.ae</x:v>
-      </x:c>
-      <x:c r="U63" s="14" t="e">
-        <x:f>HYPERLINK("https://dic.ae/offerings/in5-centres","dic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dic.ae/offerings/in5-centres, friendlyName=dic.ae</x:v>
-      </x:c>
-      <x:c r="V63" s="14" t="e">
-        <x:f>HYPERLINK("https://dic.ae/offerings/in5-centres","dic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dic.ae/offerings/in5-centres, friendlyName=dic.ae</x:v>
+      <x:c r="T63" s="14" t="str">
+        <x:v>https://dic.ae/offerings/in5-centres</x:v>
+      </x:c>
+      <x:c r="U63" s="14" t="str">
+        <x:v>https://dic.ae/offerings/in5-centres</x:v>
+      </x:c>
+      <x:c r="V63" s="14" t="str">
+        <x:v>https://dic.ae/offerings/in5-centres</x:v>
       </x:c>
       <x:c r="W63" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -14445,13 +13716,11 @@
       <x:c r="K64" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L64" s="14" t="e">
-        <x:f>HYPERLINK("https://intelak.com","intelak.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://intelak.com, friendlyName=intelak.com</x:v>
-      </x:c>
-      <x:c r="M64" s="14" t="e">
-        <x:f>HYPERLINK("https://intelak.com/contact-us/","intelak.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://intelak.com/contact-us/, friendlyName=intelak.com</x:v>
+      <x:c r="L64" s="14" t="str">
+        <x:v>https://intelak.com</x:v>
+      </x:c>
+      <x:c r="M64" s="14" t="str">
+        <x:v>https://intelak.com/contact-us/</x:v>
       </x:c>
       <x:c r="N64" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14469,13 +13738,11 @@
       <x:c r="S64" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T64" s="14" t="e">
-        <x:f>HYPERLINK("https://intelak.com/about-us/","intelak.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://intelak.com/about-us/, friendlyName=intelak.com</x:v>
-      </x:c>
-      <x:c r="U64" s="14" t="e">
-        <x:f>HYPERLINK("https://mindmaps.ai-ecosystem.org/profile-view/firm/632405290/","mindmaps.ai-ecosystem.org")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mindmaps.ai-ecosystem.org/profile-view/firm/632405290/, friendlyName=mindmaps.ai-ecosystem.org</x:v>
+      <x:c r="T64" s="14" t="str">
+        <x:v>https://intelak.com/about-us/</x:v>
+      </x:c>
+      <x:c r="U64" s="14" t="str">
+        <x:v>https://mindmaps.ai-ecosystem.org/profile-view/firm/632405290/</x:v>
       </x:c>
       <x:c r="V64" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14521,13 +13788,11 @@
       <x:c r="K65" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L65" s="14" t="e">
-        <x:f>HYPERLINK("https://catalyst.ae","catalyst.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://catalyst.ae, friendlyName=catalyst.ae</x:v>
-      </x:c>
-      <x:c r="M65" s="14" t="e">
-        <x:f>HYPERLINK("https://catalyst.ae/contact-us","catalyst.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://catalyst.ae/contact-us, friendlyName=catalyst.ae</x:v>
+      <x:c r="L65" s="14" t="str">
+        <x:v>https://catalyst.ae</x:v>
+      </x:c>
+      <x:c r="M65" s="14" t="str">
+        <x:v>https://catalyst.ae/contact-us</x:v>
       </x:c>
       <x:c r="N65" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14545,16 +13810,14 @@
       <x:c r="S65" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T65" s="14" t="e">
-        <x:f>HYPERLINK("https://catalyst.ae/contact-us","catalyst.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://catalyst.ae/contact-us, friendlyName=catalyst.ae</x:v>
+      <x:c r="T65" s="14" t="str">
+        <x:v>https://catalyst.ae/contact-us</x:v>
       </x:c>
       <x:c r="U65" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V65" s="14" t="e">
-        <x:f>HYPERLINK("https://catalyst.ae/contact-us","catalyst.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://catalyst.ae/contact-us, friendlyName=catalyst.ae</x:v>
+      <x:c r="V65" s="14" t="str">
+        <x:v>https://catalyst.ae/contact-us</x:v>
       </x:c>
       <x:c r="W65" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14597,13 +13860,11 @@
       <x:c r="K66" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L66" s="14" t="e">
-        <x:f>HYPERLINK("https://startad.ae","startad.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://startad.ae, friendlyName=startad.ae</x:v>
-      </x:c>
-      <x:c r="M66" s="14" t="e">
-        <x:f>HYPERLINK("https://startad.ae/contact/","startad.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://startad.ae/contact/, friendlyName=startad.ae</x:v>
+      <x:c r="L66" s="14" t="str">
+        <x:v>https://startad.ae</x:v>
+      </x:c>
+      <x:c r="M66" s="14" t="str">
+        <x:v>https://startad.ae/contact/</x:v>
       </x:c>
       <x:c r="N66" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14621,13 +13882,11 @@
       <x:c r="S66" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T66" s="14" t="e">
-        <x:f>HYPERLINK("https://startad.ae/contact/","startad.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://startad.ae/contact/, friendlyName=startad.ae</x:v>
-      </x:c>
-      <x:c r="U66" s="14" t="e">
-        <x:f>HYPERLINK("https://startad.ae/contact/","startad.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://startad.ae/contact/, friendlyName=startad.ae</x:v>
+      <x:c r="T66" s="14" t="str">
+        <x:v>https://startad.ae/contact/</x:v>
+      </x:c>
+      <x:c r="U66" s="14" t="str">
+        <x:v>https://startad.ae/contact/</x:v>
       </x:c>
       <x:c r="V66" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14673,13 +13932,11 @@
       <x:c r="K67" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L67" s="14" t="e">
-        <x:f>HYPERLINK("https://plugandplaytechcenter.com","plugandplaytechcenter.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://plugandplaytechcenter.com, friendlyName=plugandplaytechcenter.com</x:v>
-      </x:c>
-      <x:c r="M67" s="14" t="e">
-        <x:f>HYPERLINK("https://welcome.plugandplaytechcenter.com/innovation-smart-future-contact-us","welcome.plugandplaytechcenter.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://welcome.plugandplaytechcenter.com/innovation-smart-future-contact-us, friendlyName=welcome.plugandplaytechcenter.com</x:v>
+      <x:c r="L67" s="14" t="str">
+        <x:v>https://plugandplaytechcenter.com</x:v>
+      </x:c>
+      <x:c r="M67" s="14" t="str">
+        <x:v>https://welcome.plugandplaytechcenter.com/innovation-smart-future-contact-us</x:v>
       </x:c>
       <x:c r="N67" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14697,9 +13954,8 @@
       <x:c r="S67" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T67" s="14" t="e">
-        <x:f>HYPERLINK("https://welcome.plugandplaytechcenter.com/hubfs/Plug%20and%20Play%20Media%20Kit.pdf","welcome.plugandplaytechcenter.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://welcome.plugandplaytechcenter.com/hubfs/Plug%20and%20Play%20Media%20Kit.pdf, friendlyName=welcome.plugandplaytechcenter.com</x:v>
+      <x:c r="T67" s="14" t="str">
+        <x:v>https://welcome.plugandplaytechcenter.com/hubfs/Plug%20and%20Play%20Media%20Kit.pdf</x:v>
       </x:c>
       <x:c r="U67" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14748,13 +14004,11 @@
       <x:c r="K68" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L68" s="14" t="e">
-        <x:f>HYPERLINK("https://antler.co","antler.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://antler.co, friendlyName=antler.co</x:v>
-      </x:c>
-      <x:c r="M68" s="14" t="e">
-        <x:f>HYPERLINK("https://www.antler.co/location/menap","antler.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.antler.co/location/menap, friendlyName=antler.co</x:v>
+      <x:c r="L68" s="14" t="str">
+        <x:v>https://antler.co</x:v>
+      </x:c>
+      <x:c r="M68" s="14" t="str">
+        <x:v>https://www.antler.co/location/menap</x:v>
       </x:c>
       <x:c r="N68" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14772,9 +14026,8 @@
       <x:c r="S68" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T68" s="14" t="e">
-        <x:f>HYPERLINK("https://www.antler.co/location/menap","antler.co")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.antler.co/location/menap, friendlyName=antler.co</x:v>
+      <x:c r="T68" s="14" t="str">
+        <x:v>https://www.antler.co/location/menap</x:v>
       </x:c>
       <x:c r="U68" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14823,13 +14076,11 @@
       <x:c r="K69" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L69" s="14" t="e">
-        <x:f>HYPERLINK("https://flat6labs.com","flat6labs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flat6labs.com, friendlyName=flat6labs.com</x:v>
-      </x:c>
-      <x:c r="M69" s="14" t="e">
-        <x:f>HYPERLINK("https://flat6labs.com/ar/contact-us/","flat6labs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flat6labs.com/ar/contact-us/, friendlyName=flat6labs.com</x:v>
+      <x:c r="L69" s="14" t="str">
+        <x:v>https://flat6labs.com</x:v>
+      </x:c>
+      <x:c r="M69" s="14" t="str">
+        <x:v>https://flat6labs.com/ar/contact-us/</x:v>
       </x:c>
       <x:c r="N69" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14847,13 +14098,11 @@
       <x:c r="S69" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T69" s="14" t="e">
-        <x:f>HYPERLINK("https://flat6labs.com/stay-connected/","flat6labs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flat6labs.com/stay-connected/, friendlyName=flat6labs.com</x:v>
-      </x:c>
-      <x:c r="U69" s="14" t="e">
-        <x:f>HYPERLINK("https://flat6labs.com/stay-connected/","flat6labs.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://flat6labs.com/stay-connected/, friendlyName=flat6labs.com</x:v>
+      <x:c r="T69" s="14" t="str">
+        <x:v>https://flat6labs.com/stay-connected/</x:v>
+      </x:c>
+      <x:c r="U69" s="14" t="str">
+        <x:v>https://flat6labs.com/stay-connected/</x:v>
       </x:c>
       <x:c r="V69" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14899,13 +14148,11 @@
       <x:c r="K70" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L70" s="14" t="e">
-        <x:f>HYPERLINK("https://fastercapital.com","fastercapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fastercapital.com, friendlyName=fastercapital.com</x:v>
-      </x:c>
-      <x:c r="M70" s="14" t="e">
-        <x:f>HYPERLINK("https://fastercapital.com/contact.html","fastercapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fastercapital.com/contact.html, friendlyName=fastercapital.com</x:v>
+      <x:c r="L70" s="14" t="str">
+        <x:v>https://fastercapital.com</x:v>
+      </x:c>
+      <x:c r="M70" s="14" t="str">
+        <x:v>https://fastercapital.com/contact.html</x:v>
       </x:c>
       <x:c r="N70" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -14925,13 +14172,11 @@
       <x:c r="S70" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T70" s="14" t="e">
-        <x:f>HYPERLINK("https://fastercapital.com/contact.html","fastercapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fastercapital.com/contact.html, friendlyName=fastercapital.com</x:v>
-      </x:c>
-      <x:c r="U70" s="14" t="e">
-        <x:f>HYPERLINK("https://fastercapital.com/contact.html","fastercapital.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fastercapital.com/contact.html, friendlyName=fastercapital.com</x:v>
+      <x:c r="T70" s="14" t="str">
+        <x:v>https://fastercapital.com/contact.html</x:v>
+      </x:c>
+      <x:c r="U70" s="14" t="str">
+        <x:v>https://fastercapital.com/contact.html</x:v>
       </x:c>
       <x:c r="V70" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -14977,13 +14222,11 @@
       <x:c r="K71" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L71" s="14" t="e">
-        <x:f>HYPERLINK("https://dtec.ae","dtec.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dtec.ae, friendlyName=dtec.ae</x:v>
-      </x:c>
-      <x:c r="M71" s="14" t="e">
-        <x:f>HYPERLINK("https://dtec.ae/contact/","dtec.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dtec.ae/contact/, friendlyName=dtec.ae</x:v>
+      <x:c r="L71" s="14" t="str">
+        <x:v>https://dtec.ae</x:v>
+      </x:c>
+      <x:c r="M71" s="14" t="str">
+        <x:v>https://dtec.ae/contact/</x:v>
       </x:c>
       <x:c r="N71" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -15003,17 +14246,14 @@
       <x:c r="S71" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T71" s="14" t="e">
-        <x:f>HYPERLINK("https://dtec.ae/contact/","dtec.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dtec.ae/contact/, friendlyName=dtec.ae</x:v>
-      </x:c>
-      <x:c r="U71" s="14" t="e">
-        <x:f>HYPERLINK("https://dtec.ae/contact/","dtec.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dtec.ae/contact/, friendlyName=dtec.ae</x:v>
-      </x:c>
-      <x:c r="V71" s="14" t="e">
-        <x:f>HYPERLINK("https://dtec.ae/contact/","dtec.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dtec.ae/contact/, friendlyName=dtec.ae</x:v>
+      <x:c r="T71" s="14" t="str">
+        <x:v>https://dtec.ae/contact/</x:v>
+      </x:c>
+      <x:c r="U71" s="14" t="str">
+        <x:v>https://dtec.ae/contact/</x:v>
+      </x:c>
+      <x:c r="V71" s="14" t="str">
+        <x:v>https://dtec.ae/contact/</x:v>
       </x:c>
       <x:c r="W71" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15056,13 +14296,11 @@
       <x:c r="K72" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L72" s="14" t="e">
-        <x:f>HYPERLINK("https://innovationhub.difc.ae","innovationhub.difc.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://innovationhub.difc.ae, friendlyName=innovationhub.difc.ae</x:v>
-      </x:c>
-      <x:c r="M72" s="14" t="e">
-        <x:f>HYPERLINK("https://www.innovationhub.difc.ae/the-hub/about-innovation-hub","innovationhub.difc.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.innovationhub.difc.ae/the-hub/about-innovation-hub, friendlyName=innovationhub.difc.ae</x:v>
+      <x:c r="L72" s="14" t="str">
+        <x:v>https://innovationhub.difc.ae</x:v>
+      </x:c>
+      <x:c r="M72" s="14" t="str">
+        <x:v>https://www.innovationhub.difc.ae/the-hub/about-innovation-hub</x:v>
       </x:c>
       <x:c r="N72" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -15082,13 +14320,11 @@
       <x:c r="S72" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T72" s="14" t="e">
-        <x:f>HYPERLINK("https://www.innovationhub.difc.ae/the-hub/about-innovation-hub","innovationhub.difc.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.innovationhub.difc.ae/the-hub/about-innovation-hub, friendlyName=innovationhub.difc.ae</x:v>
-      </x:c>
-      <x:c r="U72" s="14" t="e">
-        <x:f>HYPERLINK("https://landing.difc.ae/innovation-license-thank-you","landing.difc.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://landing.difc.ae/innovation-license-thank-you, friendlyName=landing.difc.ae</x:v>
+      <x:c r="T72" s="14" t="str">
+        <x:v>https://www.innovationhub.difc.ae/the-hub/about-innovation-hub</x:v>
+      </x:c>
+      <x:c r="U72" s="14" t="str">
+        <x:v>https://landing.difc.ae/innovation-license-thank-you</x:v>
       </x:c>
       <x:c r="V72" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15134,13 +14370,11 @@
       <x:c r="K73" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L73" s="14" t="e">
-        <x:f>HYPERLINK("https://mbzuai.ac.ae","mbzuai.ac.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbzuai.ac.ae, friendlyName=mbzuai.ac.ae</x:v>
-      </x:c>
-      <x:c r="M73" s="14" t="e">
-        <x:f>HYPERLINK("https://mbzuai.ac.ae/about-us/contact-mbzuai","mbzuai.ac.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbzuai.ac.ae/about-us/contact-mbzuai, friendlyName=mbzuai.ac.ae</x:v>
+      <x:c r="L73" s="14" t="str">
+        <x:v>https://mbzuai.ac.ae</x:v>
+      </x:c>
+      <x:c r="M73" s="14" t="str">
+        <x:v>https://mbzuai.ac.ae/about-us/contact-mbzuai</x:v>
       </x:c>
       <x:c r="N73" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -15160,16 +14394,14 @@
       <x:c r="S73" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T73" s="14" t="e">
-        <x:f>HYPERLINK("https://mbzuai.ac.ae/about-us/contact-mbzuai","mbzuai.ac.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbzuai.ac.ae/about-us/contact-mbzuai, friendlyName=mbzuai.ac.ae</x:v>
+      <x:c r="T73" s="14" t="str">
+        <x:v>https://mbzuai.ac.ae/about-us/contact-mbzuai</x:v>
       </x:c>
       <x:c r="U73" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V73" s="14" t="e">
-        <x:f>HYPERLINK("https://mbzuai.ac.ae/about-us/contact-mbzuai","mbzuai.ac.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbzuai.ac.ae/about-us/contact-mbzuai, friendlyName=mbzuai.ac.ae</x:v>
+      <x:c r="V73" s="14" t="str">
+        <x:v>https://mbzuai.ac.ae/about-us/contact-mbzuai</x:v>
       </x:c>
       <x:c r="W73" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15212,13 +14444,11 @@
       <x:c r="K74" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L74" s="14" t="e">
-        <x:f>HYPERLINK("https://disrupt.com","disrupt.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://disrupt.com, friendlyName=disrupt.com</x:v>
-      </x:c>
-      <x:c r="M74" s="14" t="e">
-        <x:f>HYPERLINK("https://www.disrupt.com/contact-us","disrupt.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.disrupt.com/contact-us, friendlyName=disrupt.com</x:v>
+      <x:c r="L74" s="14" t="str">
+        <x:v>https://disrupt.com</x:v>
+      </x:c>
+      <x:c r="M74" s="14" t="str">
+        <x:v>https://www.disrupt.com/contact-us</x:v>
       </x:c>
       <x:c r="N74" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15236,9 +14466,8 @@
       <x:c r="S74" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T74" s="14" t="e">
-        <x:f>HYPERLINK("https://www.disrupt.com/","disrupt.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.disrupt.com/, friendlyName=disrupt.com</x:v>
+      <x:c r="T74" s="14" t="str">
+        <x:v>https://www.disrupt.com/</x:v>
       </x:c>
       <x:c r="U74" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15287,13 +14516,11 @@
       <x:c r="K75" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L75" s="14" t="e">
-        <x:f>HYPERLINK("https://presight.ai","presight.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://presight.ai, friendlyName=presight.ai</x:v>
-      </x:c>
-      <x:c r="M75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.presight.ai/contact-us","presight.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.presight.ai/contact-us, friendlyName=presight.ai</x:v>
+      <x:c r="L75" s="14" t="str">
+        <x:v>https://presight.ai</x:v>
+      </x:c>
+      <x:c r="M75" s="14" t="str">
+        <x:v>https://www.presight.ai/contact-us</x:v>
       </x:c>
       <x:c r="N75" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -15313,9 +14540,8 @@
       <x:c r="S75" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T75" s="14" t="e">
-        <x:f>HYPERLINK("https://www.presight.ai/accelerator","presight.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.presight.ai/accelerator, friendlyName=presight.ai</x:v>
+      <x:c r="T75" s="14" t="str">
+        <x:v>https://www.presight.ai/accelerator</x:v>
       </x:c>
       <x:c r="U75" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15364,13 +14590,11 @@
       <x:c r="K76" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L76" s="14" t="e">
-        <x:f>HYPERLINK("https://edb.gov.ae","edb.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://edb.gov.ae, friendlyName=edb.gov.ae</x:v>
-      </x:c>
-      <x:c r="M76" s="14" t="e">
-        <x:f>HYPERLINK("https://edb.gov.ae/contact","edb.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://edb.gov.ae/contact, friendlyName=edb.gov.ae</x:v>
+      <x:c r="L76" s="14" t="str">
+        <x:v>https://edb.gov.ae</x:v>
+      </x:c>
+      <x:c r="M76" s="14" t="str">
+        <x:v>https://edb.gov.ae/contact</x:v>
       </x:c>
       <x:c r="N76" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -15388,17 +14612,14 @@
       <x:c r="S76" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T76" s="14" t="e">
-        <x:f>HYPERLINK("https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf","edb.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf, friendlyName=edb.gov.ae</x:v>
-      </x:c>
-      <x:c r="U76" s="14" t="e">
-        <x:f>HYPERLINK("https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf","edb.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf, friendlyName=edb.gov.ae</x:v>
-      </x:c>
-      <x:c r="V76" s="14" t="e">
-        <x:f>HYPERLINK("https://edb.gov.ae/sme-customer-application","edb.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://edb.gov.ae/sme-customer-application, friendlyName=edb.gov.ae</x:v>
+      <x:c r="T76" s="14" t="str">
+        <x:v>https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf</x:v>
+      </x:c>
+      <x:c r="U76" s="14" t="str">
+        <x:v>https://edb.gov.ae/storage/460/9ecRSCdVrbQED8qEz0OHn2NUU37Cpz-metaRURCIFB1bHNlX0p1bmUgRWRpdGlvbl9FTi5wZGY%3D-.pdf</x:v>
+      </x:c>
+      <x:c r="V76" s="14" t="str">
+        <x:v>https://edb.gov.ae/sme-customer-application</x:v>
       </x:c>
       <x:c r="W76" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15441,13 +14662,11 @@
       <x:c r="K77" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L77" s="14" t="e">
-        <x:f>HYPERLINK("https://khalifafund.ae","khalifafund.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://khalifafund.ae, friendlyName=khalifafund.ae</x:v>
-      </x:c>
-      <x:c r="M77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.khalifafund.ae/contact/","khalifafund.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.khalifafund.ae/contact/, friendlyName=khalifafund.ae</x:v>
+      <x:c r="L77" s="14" t="str">
+        <x:v>https://khalifafund.ae</x:v>
+      </x:c>
+      <x:c r="M77" s="14" t="str">
+        <x:v>https://www.khalifafund.ae/contact/</x:v>
       </x:c>
       <x:c r="N77" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15467,17 +14686,14 @@
       <x:c r="S77" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.khalifafund.ae/contact/","khalifafund.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.khalifafund.ae/contact/, friendlyName=khalifafund.ae</x:v>
-      </x:c>
-      <x:c r="U77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.khalifafund.ae/faq/","khalifafund.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.khalifafund.ae/faq/, friendlyName=khalifafund.ae</x:v>
-      </x:c>
-      <x:c r="V77" s="14" t="e">
-        <x:f>HYPERLINK("https://www.khalifafund.ae/faq/","khalifafund.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.khalifafund.ae/faq/, friendlyName=khalifafund.ae</x:v>
+      <x:c r="T77" s="14" t="str">
+        <x:v>https://www.khalifafund.ae/contact/</x:v>
+      </x:c>
+      <x:c r="U77" s="14" t="str">
+        <x:v>https://www.khalifafund.ae/faq/</x:v>
+      </x:c>
+      <x:c r="V77" s="14" t="str">
+        <x:v>https://www.khalifafund.ae/faq/</x:v>
       </x:c>
       <x:c r="W77" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15520,13 +14736,11 @@
       <x:c r="K78" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L78" s="14" t="e">
-        <x:f>HYPERLINK("https://mbrif.ae","mbrif.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbrif.ae, friendlyName=mbrif.ae</x:v>
-      </x:c>
-      <x:c r="M78" s="14" t="e">
-        <x:f>HYPERLINK("https://mbrif.ae/contact-us/","mbrif.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbrif.ae/contact-us/, friendlyName=mbrif.ae</x:v>
+      <x:c r="L78" s="14" t="str">
+        <x:v>https://mbrif.ae</x:v>
+      </x:c>
+      <x:c r="M78" s="14" t="str">
+        <x:v>https://mbrif.ae/contact-us/</x:v>
       </x:c>
       <x:c r="N78" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -15544,13 +14758,11 @@
       <x:c r="S78" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T78" s="14" t="e">
-        <x:f>HYPERLINK("https://mbrif.ae/ar/faq/","mbrif.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbrif.ae/ar/faq/, friendlyName=mbrif.ae</x:v>
-      </x:c>
-      <x:c r="U78" s="14" t="e">
-        <x:f>HYPERLINK("https://mbrif.ae/contact-us/","mbrif.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mbrif.ae/contact-us/, friendlyName=mbrif.ae</x:v>
+      <x:c r="T78" s="14" t="str">
+        <x:v>https://mbrif.ae/ar/faq/</x:v>
+      </x:c>
+      <x:c r="U78" s="14" t="str">
+        <x:v>https://mbrif.ae/contact-us/</x:v>
       </x:c>
       <x:c r="V78" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15596,13 +14808,11 @@
       <x:c r="K79" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L79" s="14" t="e">
-        <x:f>HYPERLINK("https://dfdf.vc","dfdf.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dfdf.vc, friendlyName=dfdf.vc</x:v>
-      </x:c>
-      <x:c r="M79" s="14" t="e">
-        <x:f>HYPERLINK("https://dfdf.vc/","dfdf.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dfdf.vc/, friendlyName=dfdf.vc</x:v>
+      <x:c r="L79" s="14" t="str">
+        <x:v>https://dfdf.vc</x:v>
+      </x:c>
+      <x:c r="M79" s="14" t="str">
+        <x:v>https://dfdf.vc/</x:v>
       </x:c>
       <x:c r="N79" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15620,17 +14830,14 @@
       <x:c r="S79" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T79" s="14" t="e">
-        <x:f>HYPERLINK("https://dfdf.vc/","dfdf.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dfdf.vc/, friendlyName=dfdf.vc</x:v>
-      </x:c>
-      <x:c r="U79" s="14" t="e">
-        <x:f>HYPERLINK("https://dfdf.vc/","dfdf.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dfdf.vc/, friendlyName=dfdf.vc</x:v>
-      </x:c>
-      <x:c r="V79" s="14" t="e">
-        <x:f>HYPERLINK("https://dfdf.vc/","dfdf.vc")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dfdf.vc/, friendlyName=dfdf.vc</x:v>
+      <x:c r="T79" s="14" t="str">
+        <x:v>https://dfdf.vc/</x:v>
+      </x:c>
+      <x:c r="U79" s="14" t="str">
+        <x:v>https://dfdf.vc/</x:v>
+      </x:c>
+      <x:c r="V79" s="14" t="str">
+        <x:v>https://dfdf.vc/</x:v>
       </x:c>
       <x:c r="W79" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15673,13 +14880,11 @@
       <x:c r="K80" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L80" s="14" t="e">
-        <x:f>HYPERLINK("https://sme.ae","sme.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sme.ae, friendlyName=sme.ae</x:v>
-      </x:c>
-      <x:c r="M80" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mysme.ae/","mysme.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mysme.ae/, friendlyName=mysme.ae</x:v>
+      <x:c r="L80" s="14" t="str">
+        <x:v>https://sme.ae</x:v>
+      </x:c>
+      <x:c r="M80" s="14" t="str">
+        <x:v>https://www.mysme.ae/</x:v>
       </x:c>
       <x:c r="N80" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15699,17 +14904,14 @@
       <x:c r="S80" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T80" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mysme.ae/","mysme.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mysme.ae/, friendlyName=mysme.ae</x:v>
-      </x:c>
-      <x:c r="U80" s="14" t="e">
-        <x:f>HYPERLINK("https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf","sme.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf, friendlyName=sme.ae</x:v>
-      </x:c>
-      <x:c r="V80" s="14" t="e">
-        <x:f>HYPERLINK("https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf","sme.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf, friendlyName=sme.ae</x:v>
+      <x:c r="T80" s="14" t="str">
+        <x:v>https://www.mysme.ae/</x:v>
+      </x:c>
+      <x:c r="U80" s="14" t="str">
+        <x:v>https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf</x:v>
+      </x:c>
+      <x:c r="V80" s="14" t="str">
+        <x:v>https://sme.ae/SME_File/Files/Dubai_SME_2021_Brochure_ENGLIS.pdf</x:v>
       </x:c>
       <x:c r="W80" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15752,13 +14954,11 @@
       <x:c r="K81" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L81" s="14" t="e">
-        <x:f>HYPERLINK("https://investwithabudhabi.com","investwithabudhabi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investwithabudhabi.com, friendlyName=investwithabudhabi.com</x:v>
-      </x:c>
-      <x:c r="M81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.investwithabudhabi.com/en/contact?topic=scoping-call","investwithabudhabi.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.investwithabudhabi.com/en/contact?topic=scoping-call, friendlyName=investwithabudhabi.com</x:v>
+      <x:c r="L81" s="14" t="str">
+        <x:v>https://investwithabudhabi.com</x:v>
+      </x:c>
+      <x:c r="M81" s="14" t="str">
+        <x:v>https://www.investwithabudhabi.com/en/contact?topic=scoping-call</x:v>
       </x:c>
       <x:c r="N81" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15776,17 +14976,14 @@
       <x:c r="S81" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.investinabudhabi.ae/Get-In-Touch","investinabudhabi.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.investinabudhabi.ae/Get-In-Touch, friendlyName=investinabudhabi.ae</x:v>
-      </x:c>
-      <x:c r="U81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.investinabudhabi.ae/Privacy-Policy","investinabudhabi.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.investinabudhabi.ae/Privacy-Policy, friendlyName=investinabudhabi.ae</x:v>
-      </x:c>
-      <x:c r="V81" s="14" t="e">
-        <x:f>HYPERLINK("https://www.investinabudhabi.ae/Privacy-Policy","investinabudhabi.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.investinabudhabi.ae/Privacy-Policy, friendlyName=investinabudhabi.ae</x:v>
+      <x:c r="T81" s="14" t="str">
+        <x:v>https://www.investinabudhabi.ae/Get-In-Touch</x:v>
+      </x:c>
+      <x:c r="U81" s="14" t="str">
+        <x:v>https://www.investinabudhabi.ae/Privacy-Policy</x:v>
+      </x:c>
+      <x:c r="V81" s="14" t="str">
+        <x:v>https://www.investinabudhabi.ae/Privacy-Policy</x:v>
       </x:c>
       <x:c r="W81" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15829,13 +15026,11 @@
       <x:c r="K82" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L82" s="14" t="e">
-        <x:f>HYPERLINK("https://egf.gov.ae","egf.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://egf.gov.ae, friendlyName=egf.gov.ae</x:v>
-      </x:c>
-      <x:c r="M82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.egf.gov.ae/en/contact-us/","egf.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.egf.gov.ae/en/contact-us/, friendlyName=egf.gov.ae</x:v>
+      <x:c r="L82" s="14" t="str">
+        <x:v>https://egf.gov.ae</x:v>
+      </x:c>
+      <x:c r="M82" s="14" t="str">
+        <x:v>https://www.egf.gov.ae/en/contact-us/</x:v>
       </x:c>
       <x:c r="N82" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -15855,13 +15050,11 @@
       <x:c r="S82" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.egf.gov.ae/en/contact-us/","egf.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.egf.gov.ae/en/contact-us/, friendlyName=egf.gov.ae</x:v>
-      </x:c>
-      <x:c r="U82" s="14" t="e">
-        <x:f>HYPERLINK("https://www.egf.gov.ae/en/contact-us/","egf.gov.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.egf.gov.ae/en/contact-us/, friendlyName=egf.gov.ae</x:v>
+      <x:c r="T82" s="14" t="str">
+        <x:v>https://www.egf.gov.ae/en/contact-us/</x:v>
+      </x:c>
+      <x:c r="U82" s="14" t="str">
+        <x:v>https://www.egf.gov.ae/en/contact-us/</x:v>
       </x:c>
       <x:c r="V82" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -15907,13 +15100,11 @@
       <x:c r="K83" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L83" s="14" t="e">
-        <x:f>HYPERLINK("https://emiratesnbd.com","emiratesnbd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emiratesnbd.com, friendlyName=emiratesnbd.com</x:v>
-      </x:c>
-      <x:c r="M83" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesnbd.com/en/help-and-support/contact-us","emiratesnbd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesnbd.com/en/help-and-support/contact-us, friendlyName=emiratesnbd.com</x:v>
+      <x:c r="L83" s="14" t="str">
+        <x:v>https://emiratesnbd.com</x:v>
+      </x:c>
+      <x:c r="M83" s="14" t="str">
+        <x:v>https://www.emiratesnbd.com/en/help-and-support/contact-us</x:v>
       </x:c>
       <x:c r="N83" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -15931,17 +15122,14 @@
       <x:c r="S83" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T83" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesnbd.com/en/help-and-support/contact-us","emiratesnbd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesnbd.com/en/help-and-support/contact-us, friendlyName=emiratesnbd.com</x:v>
-      </x:c>
-      <x:c r="U83" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesnbd.com/en/help-and-support/contact-us","emiratesnbd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesnbd.com/en/help-and-support/contact-us, friendlyName=emiratesnbd.com</x:v>
-      </x:c>
-      <x:c r="V83" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesnbd.com/en/help-and-support/contact-us","emiratesnbd.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesnbd.com/en/help-and-support/contact-us, friendlyName=emiratesnbd.com</x:v>
+      <x:c r="T83" s="14" t="str">
+        <x:v>https://www.emiratesnbd.com/en/help-and-support/contact-us</x:v>
+      </x:c>
+      <x:c r="U83" s="14" t="str">
+        <x:v>https://www.emiratesnbd.com/en/help-and-support/contact-us</x:v>
+      </x:c>
+      <x:c r="V83" s="14" t="str">
+        <x:v>https://www.emiratesnbd.com/en/help-and-support/contact-us</x:v>
       </x:c>
       <x:c r="W83" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -15984,13 +15172,11 @@
       <x:c r="K84" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L84" s="14" t="e">
-        <x:f>HYPERLINK("https://mashreq.com","mashreq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mashreq.com, friendlyName=mashreq.com</x:v>
-      </x:c>
-      <x:c r="M84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mashreq.com/en/uae/customer-care/contact-us/","mashreq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mashreq.com/en/uae/customer-care/contact-us/, friendlyName=mashreq.com</x:v>
+      <x:c r="L84" s="14" t="str">
+        <x:v>https://mashreq.com</x:v>
+      </x:c>
+      <x:c r="M84" s="14" t="str">
+        <x:v>https://www.mashreq.com/en/uae/customer-care/contact-us/</x:v>
       </x:c>
       <x:c r="N84" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16008,16 +15194,14 @@
       <x:c r="S84" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mashreq.com/en/uae/customer-care/contact-us/","mashreq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mashreq.com/en/uae/customer-care/contact-us/, friendlyName=mashreq.com</x:v>
+      <x:c r="T84" s="14" t="str">
+        <x:v>https://www.mashreq.com/en/uae/customer-care/contact-us/</x:v>
       </x:c>
       <x:c r="U84" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V84" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mashreq.com/en/uae/customer-care/contact-us/","mashreq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mashreq.com/en/uae/customer-care/contact-us/, friendlyName=mashreq.com</x:v>
+      <x:c r="V84" s="14" t="str">
+        <x:v>https://www.mashreq.com/en/uae/customer-care/contact-us/</x:v>
       </x:c>
       <x:c r="W84" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -16060,13 +15244,11 @@
       <x:c r="K85" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L85" s="14" t="e">
-        <x:f>HYPERLINK("https://rakbank.ae","rakbank.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://rakbank.ae, friendlyName=rakbank.ae</x:v>
-      </x:c>
-      <x:c r="M85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.rakbank.ae/en/contact-us","rakbank.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.rakbank.ae/en/contact-us, friendlyName=rakbank.ae</x:v>
+      <x:c r="L85" s="14" t="str">
+        <x:v>https://rakbank.ae</x:v>
+      </x:c>
+      <x:c r="M85" s="14" t="str">
+        <x:v>https://www.rakbank.ae/en/contact-us</x:v>
       </x:c>
       <x:c r="N85" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16084,17 +15266,14 @@
       <x:c r="S85" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.rakbank.ae/en/contact-us","rakbank.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.rakbank.ae/en/contact-us, friendlyName=rakbank.ae</x:v>
-      </x:c>
-      <x:c r="U85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.rakbank.ae/en/contact-us","rakbank.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.rakbank.ae/en/contact-us, friendlyName=rakbank.ae</x:v>
-      </x:c>
-      <x:c r="V85" s="14" t="e">
-        <x:f>HYPERLINK("https://www.rakbank.ae/en/islamic/contact-us","rakbank.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.rakbank.ae/en/islamic/contact-us, friendlyName=rakbank.ae</x:v>
+      <x:c r="T85" s="14" t="str">
+        <x:v>https://www.rakbank.ae/en/contact-us</x:v>
+      </x:c>
+      <x:c r="U85" s="14" t="str">
+        <x:v>https://www.rakbank.ae/en/contact-us</x:v>
+      </x:c>
+      <x:c r="V85" s="14" t="str">
+        <x:v>https://www.rakbank.ae/en/islamic/contact-us</x:v>
       </x:c>
       <x:c r="W85" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -16137,13 +15316,11 @@
       <x:c r="K86" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L86" s="14" t="e">
-        <x:f>HYPERLINK("https://bankfab.com","bankfab.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bankfab.com, friendlyName=bankfab.com</x:v>
-      </x:c>
-      <x:c r="M86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bankfab.com/en-ae/contact-us","bankfab.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bankfab.com/en-ae/contact-us, friendlyName=bankfab.com</x:v>
+      <x:c r="L86" s="14" t="str">
+        <x:v>https://bankfab.com</x:v>
+      </x:c>
+      <x:c r="M86" s="14" t="str">
+        <x:v>https://www.bankfab.com/en-ae/contact-us</x:v>
       </x:c>
       <x:c r="N86" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16163,13 +15340,11 @@
       <x:c r="S86" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bankfab.com/en-ae/contact-us","bankfab.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bankfab.com/en-ae/contact-us, friendlyName=bankfab.com</x:v>
-      </x:c>
-      <x:c r="U86" s="14" t="e">
-        <x:f>HYPERLINK("https://www.bankfab.com/en-ae/contact-us","bankfab.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.bankfab.com/en-ae/contact-us, friendlyName=bankfab.com</x:v>
+      <x:c r="T86" s="14" t="str">
+        <x:v>https://www.bankfab.com/en-ae/contact-us</x:v>
+      </x:c>
+      <x:c r="U86" s="14" t="str">
+        <x:v>https://www.bankfab.com/en-ae/contact-us</x:v>
       </x:c>
       <x:c r="V86" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -16215,13 +15390,11 @@
       <x:c r="K87" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L87" s="14" t="e">
-        <x:f>HYPERLINK("https://adcb.com","adcb.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://adcb.com, friendlyName=adcb.com</x:v>
-      </x:c>
-      <x:c r="M87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adcb.com/en/get-in-touch/call-us/","adcb.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adcb.com/en/get-in-touch/call-us/, friendlyName=adcb.com</x:v>
+      <x:c r="L87" s="14" t="str">
+        <x:v>https://adcb.com</x:v>
+      </x:c>
+      <x:c r="M87" s="14" t="str">
+        <x:v>https://www.adcb.com/en/get-in-touch/call-us/</x:v>
       </x:c>
       <x:c r="N87" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16239,17 +15412,14 @@
       <x:c r="S87" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adcb.com/en/get-in-touch/call-us/","adcb.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adcb.com/en/get-in-touch/call-us/, friendlyName=adcb.com</x:v>
-      </x:c>
-      <x:c r="U87" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?hl=en_US&amp;id=com.adcb.business","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?hl=en_US&amp;id=com.adcb.business, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="V87" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adcb.com/en/get-in-touch/call-us/","adcb.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adcb.com/en/get-in-touch/call-us/, friendlyName=adcb.com</x:v>
+      <x:c r="T87" s="14" t="str">
+        <x:v>https://www.adcb.com/en/get-in-touch/call-us/</x:v>
+      </x:c>
+      <x:c r="U87" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?hl=en_US&amp;id=com.adcb.business</x:v>
+      </x:c>
+      <x:c r="V87" s="14" t="str">
+        <x:v>https://www.adcb.com/en/get-in-touch/call-us/</x:v>
       </x:c>
       <x:c r="W87" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -16292,13 +15462,11 @@
       <x:c r="K88" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L88" s="14" t="e">
-        <x:f>HYPERLINK("https://adib.ae","adib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://adib.ae, friendlyName=adib.ae</x:v>
-      </x:c>
-      <x:c r="M88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adib.ae/en/pages/contact-us","adib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adib.ae/en/pages/contact-us, friendlyName=adib.ae</x:v>
+      <x:c r="L88" s="14" t="str">
+        <x:v>https://adib.ae</x:v>
+      </x:c>
+      <x:c r="M88" s="14" t="str">
+        <x:v>https://www.adib.ae/en/pages/contact-us</x:v>
       </x:c>
       <x:c r="N88" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16316,17 +15484,14 @@
       <x:c r="S88" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adib.ae/en/pages/contact-us","adib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adib.ae/en/pages/contact-us, friendlyName=adib.ae</x:v>
-      </x:c>
-      <x:c r="U88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adib.ae/en/pages/contact-us","adib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adib.ae/en/pages/contact-us, friendlyName=adib.ae</x:v>
-      </x:c>
-      <x:c r="V88" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adib.ae/en/pages/contact-us","adib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adib.ae/en/pages/contact-us, friendlyName=adib.ae</x:v>
+      <x:c r="T88" s="14" t="str">
+        <x:v>https://www.adib.ae/en/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="U88" s="14" t="str">
+        <x:v>https://www.adib.ae/en/pages/contact-us</x:v>
+      </x:c>
+      <x:c r="V88" s="14" t="str">
+        <x:v>https://www.adib.ae/en/pages/contact-us</x:v>
       </x:c>
       <x:c r="W88" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -16369,13 +15534,11 @@
       <x:c r="K89" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L89" s="14" t="e">
-        <x:f>HYPERLINK("https://dib.ae","dib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dib.ae, friendlyName=dib.ae</x:v>
-      </x:c>
-      <x:c r="M89" s="14" t="e">
-        <x:f>HYPERLINK("https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html","online.dib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html, friendlyName=online.dib.ae</x:v>
+      <x:c r="L89" s="14" t="str">
+        <x:v>https://dib.ae</x:v>
+      </x:c>
+      <x:c r="M89" s="14" t="str">
+        <x:v>https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html</x:v>
       </x:c>
       <x:c r="N89" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16393,17 +15556,14 @@
       <x:c r="S89" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T89" s="14" t="e">
-        <x:f>HYPERLINK("https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html","online.dib.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html, friendlyName=online.dib.ae</x:v>
-      </x:c>
-      <x:c r="U89" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=ae.dib.smartapp","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=ae.dib.smartapp, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="V89" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?id=ae.dib.smartapp","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?id=ae.dib.smartapp, friendlyName=play.google.com</x:v>
+      <x:c r="T89" s="14" t="str">
+        <x:v>https://online.dib.ae/StaticContents/BankingServicesAgreement-enUs.html</x:v>
+      </x:c>
+      <x:c r="U89" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=ae.dib.smartapp</x:v>
+      </x:c>
+      <x:c r="V89" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?id=ae.dib.smartapp</x:v>
       </x:c>
       <x:c r="W89" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -16446,13 +15606,11 @@
       <x:c r="K90" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L90" s="14" t="e">
-        <x:f>HYPERLINK("https://emiratesislamic.ae","emiratesislamic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://emiratesislamic.ae, friendlyName=emiratesislamic.ae</x:v>
-      </x:c>
-      <x:c r="M90" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesislamic.ae/en/help-and-support/contact-us","emiratesislamic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesislamic.ae/en/help-and-support/contact-us, friendlyName=emiratesislamic.ae</x:v>
+      <x:c r="L90" s="14" t="str">
+        <x:v>https://emiratesislamic.ae</x:v>
+      </x:c>
+      <x:c r="M90" s="14" t="str">
+        <x:v>https://www.emiratesislamic.ae/en/help-and-support/contact-us</x:v>
       </x:c>
       <x:c r="N90" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16470,17 +15628,14 @@
       <x:c r="S90" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T90" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesislamic.ae/en/help-and-support/contact-us","emiratesislamic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesislamic.ae/en/help-and-support/contact-us, friendlyName=emiratesislamic.ae</x:v>
-      </x:c>
-      <x:c r="U90" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesislamic.ae/en/business-banking/locations","emiratesislamic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesislamic.ae/en/business-banking/locations, friendlyName=emiratesislamic.ae</x:v>
-      </x:c>
-      <x:c r="V90" s="14" t="e">
-        <x:f>HYPERLINK("https://www.emiratesislamic.ae/en/help-and-support/contact-us","emiratesislamic.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.emiratesislamic.ae/en/help-and-support/contact-us, friendlyName=emiratesislamic.ae</x:v>
+      <x:c r="T90" s="14" t="str">
+        <x:v>https://www.emiratesislamic.ae/en/help-and-support/contact-us</x:v>
+      </x:c>
+      <x:c r="U90" s="14" t="str">
+        <x:v>https://www.emiratesislamic.ae/en/business-banking/locations</x:v>
+      </x:c>
+      <x:c r="V90" s="14" t="str">
+        <x:v>https://www.emiratesislamic.ae/en/help-and-support/contact-us</x:v>
       </x:c>
       <x:c r="W90" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -16523,13 +15678,11 @@
       <x:c r="K91" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L91" s="14" t="e">
-        <x:f>HYPERLINK("https://cbd.ae","cbd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://cbd.ae, friendlyName=cbd.ae</x:v>
-      </x:c>
-      <x:c r="M91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cbd.ae/home/contact-us/careers","cbd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cbd.ae/home/contact-us/careers, friendlyName=cbd.ae</x:v>
+      <x:c r="L91" s="14" t="str">
+        <x:v>https://cbd.ae</x:v>
+      </x:c>
+      <x:c r="M91" s="14" t="str">
+        <x:v>https://www.cbd.ae/home/contact-us/careers</x:v>
       </x:c>
       <x:c r="N91" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16547,17 +15700,14 @@
       <x:c r="S91" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2","cbd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2, friendlyName=cbd.ae</x:v>
-      </x:c>
-      <x:c r="U91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2","cbd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2, friendlyName=cbd.ae</x:v>
-      </x:c>
-      <x:c r="V91" s="14" t="e">
-        <x:f>HYPERLINK("https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2","cbd.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2, friendlyName=cbd.ae</x:v>
+      <x:c r="T91" s="14" t="str">
+        <x:v>https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2</x:v>
+      </x:c>
+      <x:c r="U91" s="14" t="str">
+        <x:v>https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2</x:v>
+      </x:c>
+      <x:c r="V91" s="14" t="str">
+        <x:v>https://www.cbd.ae/docs/default-source/default-document-library/customer-service-charter--5th-oct-2021.pdf?Status=Temp&amp;sfvrsn=f83f466b_2</x:v>
       </x:c>
       <x:c r="W91" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -16600,13 +15750,11 @@
       <x:c r="K92" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L92" s="14" t="e">
-        <x:f>HYPERLINK("https://wio.io","wio.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wio.io, friendlyName=wio.io</x:v>
-      </x:c>
-      <x:c r="M92" s="14" t="e">
-        <x:f>HYPERLINK("https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide","desk.wio.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide, friendlyName=desk.wio.io</x:v>
+      <x:c r="L92" s="14" t="str">
+        <x:v>https://wio.io</x:v>
+      </x:c>
+      <x:c r="M92" s="14" t="str">
+        <x:v>https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide</x:v>
       </x:c>
       <x:c r="N92" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16624,17 +15772,14 @@
       <x:c r="S92" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T92" s="14" t="e">
-        <x:f>HYPERLINK("https://wio.io/business","wio.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wio.io/business, friendlyName=wio.io</x:v>
-      </x:c>
-      <x:c r="U92" s="14" t="e">
-        <x:f>HYPERLINK("https://downloads.ctfassets.net/l65m9bcr2nac/4IOMAncr4kcfGjIIOwHumC/6ca32c2c59434b23b0fc38467f842b67/KFS-v4-personal-EN.pdf","downloads.ctfassets.net")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://downloads.ctfassets.net/l65m9bcr2nac/4IOMAncr4kcfGjIIOwHumC/6ca32c2c59434b23b0fc38467f842b67/KFS-v4-personal-EN.pdf, friendlyName=downloads.ctfassets.net</x:v>
-      </x:c>
-      <x:c r="V92" s="14" t="e">
-        <x:f>HYPERLINK("https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide","desk.wio.io")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide, friendlyName=desk.wio.io</x:v>
+      <x:c r="T92" s="14" t="str">
+        <x:v>https://wio.io/business</x:v>
+      </x:c>
+      <x:c r="U92" s="14" t="str">
+        <x:v>https://downloads.ctfassets.net/l65m9bcr2nac/4IOMAncr4kcfGjIIOwHumC/6ca32c2c59434b23b0fc38467f842b67/KFS-v4-personal-EN.pdf</x:v>
+      </x:c>
+      <x:c r="V92" s="14" t="str">
+        <x:v>https://desk.wio.io/support/solutions/articles/501000414626-wio-business-wiopay-online-payments-payment-links-guide</x:v>
       </x:c>
       <x:c r="W92" s="6" t="str">
         <x:v>مصدر ثانوي؛ يلزم تأكيد مباشر</x:v>
@@ -16677,13 +15822,11 @@
       <x:c r="K93" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L93" s="14" t="e">
-        <x:f>HYPERLINK("https://zand.ae","zand.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://zand.ae, friendlyName=zand.ae</x:v>
-      </x:c>
-      <x:c r="M93" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zand.ae/en/contact-us","zand.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zand.ae/en/contact-us, friendlyName=zand.ae</x:v>
+      <x:c r="L93" s="14" t="str">
+        <x:v>https://zand.ae</x:v>
+      </x:c>
+      <x:c r="M93" s="14" t="str">
+        <x:v>https://www.zand.ae/en/contact-us</x:v>
       </x:c>
       <x:c r="N93" s="6" t="str">
         <x:v>رخصة ونشاط ومستندات مالية وتقييم ائتماني بحسب المنتج</x:v>
@@ -16701,17 +15844,14 @@
       <x:c r="S93" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T93" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zand.ae/en/contact-us","zand.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zand.ae/en/contact-us, friendlyName=zand.ae</x:v>
-      </x:c>
-      <x:c r="U93" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zand.ae/en/contact-us","zand.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zand.ae/en/contact-us, friendlyName=zand.ae</x:v>
-      </x:c>
-      <x:c r="V93" s="14" t="e">
-        <x:f>HYPERLINK("https://www.zand.ae/en/contact-us","zand.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.zand.ae/en/contact-us, friendlyName=zand.ae</x:v>
+      <x:c r="T93" s="14" t="str">
+        <x:v>https://www.zand.ae/en/contact-us</x:v>
+      </x:c>
+      <x:c r="U93" s="14" t="str">
+        <x:v>https://www.zand.ae/en/contact-us</x:v>
+      </x:c>
+      <x:c r="V93" s="14" t="str">
+        <x:v>https://www.zand.ae/en/contact-us</x:v>
       </x:c>
       <x:c r="W93" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -16754,13 +15894,11 @@
       <x:c r="K94" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L94" s="14" t="e">
-        <x:f>HYPERLINK("https://eand.com","eand.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://eand.com, friendlyName=eand.com</x:v>
-      </x:c>
-      <x:c r="M94" s="14" t="e">
-        <x:f>HYPERLINK("https://www.eand.com/en/capital.html","eand.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.eand.com/en/capital.html, friendlyName=eand.com</x:v>
+      <x:c r="L94" s="14" t="str">
+        <x:v>https://eand.com</x:v>
+      </x:c>
+      <x:c r="M94" s="14" t="str">
+        <x:v>https://www.eand.com/en/capital.html</x:v>
       </x:c>
       <x:c r="N94" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -16780,9 +15918,8 @@
       <x:c r="S94" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T94" s="14" t="e">
-        <x:f>HYPERLINK("https://www.eand.com/en/capital.html","eand.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.eand.com/en/capital.html, friendlyName=eand.com</x:v>
+      <x:c r="T94" s="14" t="str">
+        <x:v>https://www.eand.com/en/capital.html</x:v>
       </x:c>
       <x:c r="U94" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -16831,13 +15968,11 @@
       <x:c r="K95" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L95" s="14" t="e">
-        <x:f>HYPERLINK("https://du.ae","du.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://du.ae, friendlyName=du.ae</x:v>
-      </x:c>
-      <x:c r="M95" s="14" t="e">
-        <x:f>HYPERLINK("https://investors.du.ae/","investors.du.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investors.du.ae/, friendlyName=investors.du.ae</x:v>
+      <x:c r="L95" s="14" t="str">
+        <x:v>https://du.ae</x:v>
+      </x:c>
+      <x:c r="M95" s="14" t="str">
+        <x:v>https://investors.du.ae/</x:v>
       </x:c>
       <x:c r="N95" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -16857,9 +15992,8 @@
       <x:c r="S95" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T95" s="14" t="e">
-        <x:f>HYPERLINK("https://investors.du.ae/","investors.du.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://investors.du.ae/, friendlyName=investors.du.ae</x:v>
+      <x:c r="T95" s="14" t="str">
+        <x:v>https://investors.du.ae/</x:v>
       </x:c>
       <x:c r="U95" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -16908,13 +16042,11 @@
       <x:c r="K96" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L96" s="14" t="e">
-        <x:f>HYPERLINK("https://mubadala.com","mubadala.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mubadala.com, friendlyName=mubadala.com</x:v>
-      </x:c>
-      <x:c r="M96" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadala.com/en/contact-us","mubadala.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadala.com/en/contact-us, friendlyName=mubadala.com</x:v>
+      <x:c r="L96" s="14" t="str">
+        <x:v>https://mubadala.com</x:v>
+      </x:c>
+      <x:c r="M96" s="14" t="str">
+        <x:v>https://www.mubadala.com/en/contact-us</x:v>
       </x:c>
       <x:c r="N96" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -16934,16 +16066,14 @@
       <x:c r="S96" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T96" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadala.com/en/contact-us","mubadala.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadala.com/en/contact-us, friendlyName=mubadala.com</x:v>
+      <x:c r="T96" s="14" t="str">
+        <x:v>https://www.mubadala.com/en/contact-us</x:v>
       </x:c>
       <x:c r="U96" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V96" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mubadala.com/en/contact-us","mubadala.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mubadala.com/en/contact-us, friendlyName=mubadala.com</x:v>
+      <x:c r="V96" s="14" t="str">
+        <x:v>https://www.mubadala.com/en/contact-us</x:v>
       </x:c>
       <x:c r="W96" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -16986,13 +16116,11 @@
       <x:c r="K97" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L97" s="14" t="e">
-        <x:f>HYPERLINK("https://adq.ae","adq.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://adq.ae, friendlyName=adq.ae</x:v>
-      </x:c>
-      <x:c r="M97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adq.ae/","adq.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adq.ae/, friendlyName=adq.ae</x:v>
+      <x:c r="L97" s="14" t="str">
+        <x:v>https://adq.ae</x:v>
+      </x:c>
+      <x:c r="M97" s="14" t="str">
+        <x:v>https://www.adq.ae/</x:v>
       </x:c>
       <x:c r="N97" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17012,9 +16140,8 @@
       <x:c r="S97" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T97" s="14" t="e">
-        <x:f>HYPERLINK("https://www.adq.ae/","adq.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.adq.ae/, friendlyName=adq.ae</x:v>
+      <x:c r="T97" s="14" t="str">
+        <x:v>https://www.adq.ae/</x:v>
       </x:c>
       <x:c r="U97" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -17063,13 +16190,11 @@
       <x:c r="K98" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L98" s="14" t="e">
-        <x:f>HYPERLINK("https://mgx.ae","mgx.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://mgx.ae, friendlyName=mgx.ae</x:v>
-      </x:c>
-      <x:c r="M98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mgx.ae/contact","mgx.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mgx.ae/contact, friendlyName=mgx.ae</x:v>
+      <x:c r="L98" s="14" t="str">
+        <x:v>https://mgx.ae</x:v>
+      </x:c>
+      <x:c r="M98" s="14" t="str">
+        <x:v>https://www.mgx.ae/contact</x:v>
       </x:c>
       <x:c r="N98" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17089,9 +16214,8 @@
       <x:c r="S98" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T98" s="14" t="e">
-        <x:f>HYPERLINK("https://www.mgx.ae/contact","mgx.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.mgx.ae/contact, friendlyName=mgx.ae</x:v>
+      <x:c r="T98" s="14" t="str">
+        <x:v>https://www.mgx.ae/contact</x:v>
       </x:c>
       <x:c r="U98" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -17140,13 +16264,11 @@
       <x:c r="K99" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L99" s="14" t="e">
-        <x:f>HYPERLINK("https://g42.ai","g42.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://g42.ai, friendlyName=g42.ai</x:v>
-      </x:c>
-      <x:c r="M99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.g42.ai/contact","g42.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.g42.ai/contact, friendlyName=g42.ai</x:v>
+      <x:c r="L99" s="14" t="str">
+        <x:v>https://g42.ai</x:v>
+      </x:c>
+      <x:c r="M99" s="14" t="str">
+        <x:v>https://www.g42.ai/contact</x:v>
       </x:c>
       <x:c r="N99" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17166,13 +16288,11 @@
       <x:c r="S99" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.g42.ai/contact","g42.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.g42.ai/contact, friendlyName=g42.ai</x:v>
-      </x:c>
-      <x:c r="U99" s="14" t="e">
-        <x:f>HYPERLINK("https://www.g42.ai/contact","g42.ai")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.g42.ai/contact, friendlyName=g42.ai</x:v>
+      <x:c r="T99" s="14" t="str">
+        <x:v>https://www.g42.ai/contact</x:v>
+      </x:c>
+      <x:c r="U99" s="14" t="str">
+        <x:v>https://www.g42.ai/contact</x:v>
       </x:c>
       <x:c r="V99" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -17218,13 +16338,11 @@
       <x:c r="K100" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L100" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaicultiv8.com","dubaicultiv8.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaicultiv8.com, friendlyName=dubaicultiv8.com</x:v>
-      </x:c>
-      <x:c r="M100" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaicultiv8.com/","dubaicultiv8.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaicultiv8.com/, friendlyName=dubaicultiv8.com</x:v>
+      <x:c r="L100" s="14" t="str">
+        <x:v>https://dubaicultiv8.com</x:v>
+      </x:c>
+      <x:c r="M100" s="14" t="str">
+        <x:v>https://dubaicultiv8.com/</x:v>
       </x:c>
       <x:c r="N100" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17244,17 +16362,14 @@
       <x:c r="S100" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T100" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaicultiv8.com/","dubaicultiv8.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaicultiv8.com/, friendlyName=dubaicultiv8.com</x:v>
-      </x:c>
-      <x:c r="U100" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaicultiv8.com/","dubaicultiv8.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaicultiv8.com/, friendlyName=dubaicultiv8.com</x:v>
-      </x:c>
-      <x:c r="V100" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaicultiv8.com/","dubaicultiv8.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaicultiv8.com/, friendlyName=dubaicultiv8.com</x:v>
+      <x:c r="T100" s="14" t="str">
+        <x:v>https://dubaicultiv8.com/</x:v>
+      </x:c>
+      <x:c r="U100" s="14" t="str">
+        <x:v>https://dubaicultiv8.com/</x:v>
+      </x:c>
+      <x:c r="V100" s="14" t="str">
+        <x:v>https://dubaicultiv8.com/</x:v>
       </x:c>
       <x:c r="W100" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -17297,13 +16412,11 @@
       <x:c r="K101" s="6" t="str">
         <x:v>استفسارات عامة</x:v>
       </x:c>
-      <x:c r="L101" s="14" t="e">
-        <x:f>HYPERLINK("https://crescententerprises.com","crescententerprises.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://crescententerprises.com, friendlyName=crescententerprises.com</x:v>
-      </x:c>
-      <x:c r="M101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crescententerprises.com/contact-us/","crescententerprises.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crescententerprises.com/contact-us/, friendlyName=crescententerprises.com</x:v>
+      <x:c r="L101" s="14" t="str">
+        <x:v>https://crescententerprises.com</x:v>
+      </x:c>
+      <x:c r="M101" s="14" t="str">
+        <x:v>https://www.crescententerprises.com/contact-us/</x:v>
       </x:c>
       <x:c r="N101" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17321,17 +16434,14 @@
       <x:c r="S101" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crescententerprises.com/contact-us/","crescententerprises.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crescententerprises.com/contact-us/, friendlyName=crescententerprises.com</x:v>
-      </x:c>
-      <x:c r="U101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crescententerprises.com/contact-us/","crescententerprises.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crescententerprises.com/contact-us/, friendlyName=crescententerprises.com</x:v>
-      </x:c>
-      <x:c r="V101" s="14" t="e">
-        <x:f>HYPERLINK("https://www.crescententerprises.com/contact-us/","crescententerprises.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.crescententerprises.com/contact-us/, friendlyName=crescententerprises.com</x:v>
+      <x:c r="T101" s="14" t="str">
+        <x:v>https://www.crescententerprises.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="U101" s="14" t="str">
+        <x:v>https://www.crescententerprises.com/contact-us/</x:v>
+      </x:c>
+      <x:c r="V101" s="14" t="str">
+        <x:v>https://www.crescententerprises.com/contact-us/</x:v>
       </x:c>
       <x:c r="W101" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -17374,13 +16484,11 @@
       <x:c r="K102" s="6" t="str">
         <x:v>دعم / خدمة عملاء؛ اطلب التحويل</x:v>
       </x:c>
-      <x:c r="L102" s="14" t="e">
-        <x:f>HYPERLINK("https://fundingsouq.com","fundingsouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fundingsouq.com, friendlyName=fundingsouq.com</x:v>
-      </x:c>
-      <x:c r="M102" s="14" t="e">
-        <x:f>HYPERLINK("https://fundingsouq.com/ae/en/contact-us/","fundingsouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fundingsouq.com/ae/en/contact-us/, friendlyName=fundingsouq.com</x:v>
+      <x:c r="L102" s="14" t="str">
+        <x:v>https://fundingsouq.com</x:v>
+      </x:c>
+      <x:c r="M102" s="14" t="str">
+        <x:v>https://fundingsouq.com/ae/en/contact-us/</x:v>
       </x:c>
       <x:c r="N102" s="6" t="str">
         <x:v>شركة قائمة مستوفية لشروط المنصة</x:v>
@@ -17400,17 +16508,14 @@
       <x:c r="S102" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T102" s="14" t="e">
-        <x:f>HYPERLINK("https://fundingsouq.com/ae/en/contact-us/","fundingsouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fundingsouq.com/ae/en/contact-us/, friendlyName=fundingsouq.com</x:v>
-      </x:c>
-      <x:c r="U102" s="14" t="e">
-        <x:f>HYPERLINK("https://play.google.com/store/apps/details?hl=en_US&amp;id=com.fundingsouq","play.google.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://play.google.com/store/apps/details?hl=en_US&amp;id=com.fundingsouq, friendlyName=play.google.com</x:v>
-      </x:c>
-      <x:c r="V102" s="14" t="e">
-        <x:f>HYPERLINK("https://fundingsouq.com/ae/en/contact-us/","fundingsouq.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://fundingsouq.com/ae/en/contact-us/, friendlyName=fundingsouq.com</x:v>
+      <x:c r="T102" s="14" t="str">
+        <x:v>https://fundingsouq.com/ae/en/contact-us/</x:v>
+      </x:c>
+      <x:c r="U102" s="14" t="str">
+        <x:v>https://play.google.com/store/apps/details?hl=en_US&amp;id=com.fundingsouq</x:v>
+      </x:c>
+      <x:c r="V102" s="14" t="str">
+        <x:v>https://fundingsouq.com/ae/en/contact-us/</x:v>
       </x:c>
       <x:c r="W102" s="6" t="str">
         <x:v>قائمة تطبيق ينشرها المطور</x:v>
@@ -17453,13 +16558,11 @@
       <x:c r="K103" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L103" s="14" t="e">
-        <x:f>HYPERLINK("https://majidalfuttaim.com","majidalfuttaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://majidalfuttaim.com, friendlyName=majidalfuttaim.com</x:v>
-      </x:c>
-      <x:c r="M103" s="14" t="e">
-        <x:f>HYPERLINK("https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2","majidalfuttaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2, friendlyName=majidalfuttaim.com</x:v>
+      <x:c r="L103" s="14" t="str">
+        <x:v>https://majidalfuttaim.com</x:v>
+      </x:c>
+      <x:c r="M103" s="14" t="str">
+        <x:v>https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2</x:v>
       </x:c>
       <x:c r="N103" s="6" t="str">
         <x:v>بحسب الدورة والبرنامج ومرحلة الشركة</x:v>
@@ -17479,9 +16582,8 @@
       <x:c r="S103" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T103" s="14" t="e">
-        <x:f>HYPERLINK("https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2","majidalfuttaim.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2, friendlyName=majidalfuttaim.com</x:v>
+      <x:c r="T103" s="14" t="str">
+        <x:v>https://www.majidalfuttaim.com/docs/default-source/press-releases/majid-al-futtaim-rolls-out-launchpad-x-to-connect-leading-mena-startups-with-global-market-opportunities_en.pdf?sfvrsn=a3fc5f39_2</x:v>
       </x:c>
       <x:c r="U103" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -17530,13 +16632,11 @@
       <x:c r="K104" s="6" t="str">
         <x:v>أعمال / مبيعات / تمويل</x:v>
       </x:c>
-      <x:c r="L104" s="14" t="e">
-        <x:f>HYPERLINK("https://beehive.ae","beehive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://beehive.ae, friendlyName=beehive.ae</x:v>
-      </x:c>
-      <x:c r="M104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.beehive.ae/contact-us","beehive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.beehive.ae/contact-us, friendlyName=beehive.ae</x:v>
+      <x:c r="L104" s="14" t="str">
+        <x:v>https://beehive.ae</x:v>
+      </x:c>
+      <x:c r="M104" s="14" t="str">
+        <x:v>https://www.beehive.ae/contact-us</x:v>
       </x:c>
       <x:c r="N104" s="6" t="str">
         <x:v>شركة قائمة مستوفية لشروط المنصة</x:v>
@@ -17556,17 +16656,14 @@
       <x:c r="S104" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.beehive.ae/","beehive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.beehive.ae/, friendlyName=beehive.ae</x:v>
-      </x:c>
-      <x:c r="U104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.beehive.ae/contact-us","beehive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.beehive.ae/contact-us, friendlyName=beehive.ae</x:v>
-      </x:c>
-      <x:c r="V104" s="14" t="e">
-        <x:f>HYPERLINK("https://www.beehive.ae/contact-us","beehive.ae")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.beehive.ae/contact-us, friendlyName=beehive.ae</x:v>
+      <x:c r="T104" s="14" t="str">
+        <x:v>https://www.beehive.ae/</x:v>
+      </x:c>
+      <x:c r="U104" s="14" t="str">
+        <x:v>https://www.beehive.ae/contact-us</x:v>
+      </x:c>
+      <x:c r="V104" s="14" t="str">
+        <x:v>https://www.beehive.ae/contact-us</x:v>
       </x:c>
       <x:c r="W104" s="6" t="str">
         <x:v>موقع الجهة أو قناة مرتبطة بها</x:v>
@@ -17609,13 +16706,11 @@
       <x:c r="K105" s="6" t="str">
         <x:v>نموذج / موقع الجهة</x:v>
       </x:c>
-      <x:c r="L105" s="14" t="e">
-        <x:f>HYPERLINK("https://dubaiholding.com","dubaiholding.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://dubaiholding.com, friendlyName=dubaiholding.com</x:v>
-      </x:c>
-      <x:c r="M105" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiholding.com/en/contact-us","dubaiholding.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiholding.com/en/contact-us, friendlyName=dubaiholding.com</x:v>
+      <x:c r="L105" s="14" t="str">
+        <x:v>https://dubaiholding.com</x:v>
+      </x:c>
+      <x:c r="M105" s="14" t="str">
+        <x:v>https://www.dubaiholding.com/en/contact-us</x:v>
       </x:c>
       <x:c r="N105" s="6" t="str">
         <x:v>ملاءمة القطاع والمرحلة والنطاق الجغرافي؛ تأكيد مباشر</x:v>
@@ -17635,16 +16730,14 @@
       <x:c r="S105" s="11" t="d">
         <x:v>2026-10-22T06:00:00.000Z</x:v>
       </x:c>
-      <x:c r="T105" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiholding.com/en/contact-us","dubaiholding.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiholding.com/en/contact-us, friendlyName=dubaiholding.com</x:v>
+      <x:c r="T105" s="14" t="str">
+        <x:v>https://www.dubaiholding.com/en/contact-us</x:v>
       </x:c>
       <x:c r="U105" s="14" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
       </x:c>
-      <x:c r="V105" s="14" t="e">
-        <x:f>HYPERLINK("https://www.dubaiholding.com/en/contact-us","dubaiholding.com")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.dubaiholding.com/en/contact-us, friendlyName=dubaiholding.com</x:v>
+      <x:c r="V105" s="14" t="str">
+        <x:v>https://www.dubaiholding.com/en/contact-us</x:v>
       </x:c>
       <x:c r="W105" s="6" t="str">
         <x:v>غير متاح في المصادر المراجعة</x:v>
@@ -17667,7 +16760,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57c8a3ab97e64562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re30346bac46f4f2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
